--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE126"/>
+  <dimension ref="A1:AH132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -587,11 +587,26 @@
           <t>TW esp</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Grado SV solido</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura amplia</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura estricta</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aceleración y fuerza centrípeta</t>
+          <t>Aceleración</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -605,11 +620,54 @@
       <c r="D2" t="n">
         <v>5</v>
       </c>
+      <c r="G2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -647,6 +705,19 @@
       <c r="S3" t="n">
         <v>1</v>
       </c>
+      <c r="AF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -660,10 +731,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -707,6 +778,19 @@
       <c r="V4" t="n">
         <v>1</v>
       </c>
+      <c r="AF4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -779,6 +863,19 @@
       <c r="V5" t="n">
         <v>1</v>
       </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -845,6 +942,22 @@
       <c r="V6" t="n">
         <v>1</v>
       </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -893,11 +1006,24 @@
       <c r="V7" t="n">
         <v>1</v>
       </c>
+      <c r="AF7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -906,34 +1032,80 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="K8" t="n">
-        <v>8</v>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Densidad</t>
+          <t>Disipación de energía y eficiencia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -946,31 +1118,37 @@
       </c>
       <c r="D9" t="n">
         <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
@@ -994,12 +1172,28 @@
       </c>
       <c r="V9" t="n">
         <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Disipación de energía y eficiencia</t>
+          <t>Energía cinética</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,38 +1208,26 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>8</v>
       </c>
       <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
         <v>4.5</v>
       </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>7</v>
-      </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
@@ -1058,20 +1240,27 @@
       <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
       <c r="V10" t="n">
         <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>Energía potencial gravitatoria y elástica</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1100,8 +1289,11 @@
       <c r="J11" t="n">
         <v>7</v>
       </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1118,14 +1310,30 @@
       <c r="S11" t="n">
         <v>1</v>
       </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
       <c r="V11" t="n">
         <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,58 +1342,77 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
       </c>
       <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
         <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
       <c r="V12" t="n">
         <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1194,28 +1421,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
       </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1226,60 +1459,82 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
       </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
@@ -1288,17 +1543,30 @@
       </c>
       <c r="V14" t="n">
         <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1314,22 +1582,25 @@
         <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
@@ -1343,6 +1614,9 @@
       <c r="Q15" t="n">
         <v>1</v>
       </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
@@ -1354,45 +1628,61 @@
       </c>
       <c r="V15" t="n">
         <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>2.5</v>
@@ -1421,59 +1711,124 @@
       <c r="V16" t="n">
         <v>1</v>
       </c>
+      <c r="AF16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Movimiento circular y variables angulares</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
         <v>5</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="G17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
+      <c r="L17" t="n">
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
       <c r="V17" t="n">
         <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -1482,57 +1837,73 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
         <v>7</v>
       </c>
       <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
         <v>5</v>
       </c>
-      <c r="L18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1545,68 +1916,111 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
       </c>
       <c r="J19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="L19" t="n">
-        <v>7.5</v>
-      </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" t="n">
         <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" t="n">
         <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
       </c>
       <c r="H20" t="n">
         <v>7</v>
       </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
       <c r="J20" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P20" t="n">
+        <v>7</v>
+      </c>
+      <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
@@ -1618,12 +2032,25 @@
       </c>
       <c r="V20" t="n">
         <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1632,28 +2059,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1661,23 +2094,36 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
         <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aceleración</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1692,19 +2138,16 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
       </c>
-      <c r="L22" t="n">
-        <v>4.5</v>
+      <c r="K22" t="n">
+        <v>2</v>
       </c>
       <c r="M22" t="n">
         <v>4.5</v>
@@ -1712,26 +2155,36 @@
       <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
+      <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1755,13 +2208,16 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>4</v>
@@ -1787,17 +2243,36 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1806,10 +2281,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -1821,19 +2296,16 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
         <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
         <v>2.5</v>
@@ -1850,9 +2322,6 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
@@ -1864,12 +2333,25 @@
       </c>
       <c r="V24" t="n">
         <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1878,28 +2360,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
       </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -1910,6 +2395,9 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
@@ -1918,12 +2406,25 @@
       </c>
       <c r="V25" t="n">
         <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1932,35 +2433,41 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
         <v>3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>7</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5</v>
       </c>
       <c r="M26" t="n">
         <v>2.5</v>
       </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -1984,12 +2491,25 @@
       </c>
       <c r="V26" t="n">
         <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colisiones elásticas e inelásticas</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1998,22 +2518,71 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7</v>
+      </c>
+      <c r="I27" t="n">
         <v>8</v>
       </c>
-      <c r="D27" t="n">
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
         <v>8</v>
       </c>
-      <c r="G27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2022,40 +2591,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
         <v>7</v>
       </c>
-      <c r="K28" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
       <c r="M28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2063,29 +2614,33 @@
       <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
       <c r="V28" t="n">
         <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2094,41 +2649,50 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
       </c>
       <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
         <v>7</v>
       </c>
-      <c r="F29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>7</v>
+      <c r="J29" t="n">
+        <v>2.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
@@ -2137,12 +2701,25 @@
       </c>
       <c r="V29" t="n">
         <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2151,34 +2728,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -2195,20 +2769,30 @@
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
       <c r="U30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2217,58 +2801,62 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
         <v>6</v>
-      </c>
-      <c r="D31" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
       </c>
-      <c r="I31" t="n">
-        <v>3</v>
-      </c>
       <c r="J31" t="n">
         <v>7</v>
       </c>
-      <c r="K31" t="n">
-        <v>6</v>
-      </c>
-      <c r="L31" t="n">
-        <v>4</v>
-      </c>
       <c r="M31" t="n">
         <v>7</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
       <c r="V31" t="n">
         <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2277,27 +2865,27 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="I32" t="n">
-        <v>4</v>
-      </c>
       <c r="J32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K32" t="n">
         <v>3</v>
       </c>
       <c r="M32" t="n">
@@ -2318,17 +2906,30 @@
       <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="U32" t="n">
+      <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2337,16 +2938,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
@@ -2358,23 +2953,14 @@
         <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L33" t="n">
         <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>4</v>
       </c>
       <c r="M33" t="n">
         <v>2.5</v>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
@@ -2387,20 +2973,30 @@
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
       <c r="U33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2409,29 +3005,44 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
@@ -2441,14 +3052,30 @@
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
       <c r="V34" t="n">
         <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2466,23 +3093,17 @@
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>2.5</v>
       </c>
-      <c r="K35" t="n">
-        <v>4</v>
-      </c>
       <c r="L35" t="n">
         <v>4</v>
       </c>
@@ -2501,26 +3122,33 @@
       <c r="Q35" t="n">
         <v>1</v>
       </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
       <c r="V35" t="n">
         <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2529,10 +3157,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -2544,43 +3175,68 @@
         <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
       <c r="L36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
         <v>6</v>
       </c>
-      <c r="M36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2589,40 +3245,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -2630,29 +3265,27 @@
       <c r="P37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
+      <c r="AF37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2661,32 +3294,32 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="I38" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" t="n">
-        <v>7</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
@@ -2707,12 +3340,25 @@
       </c>
       <c r="V38" t="n">
         <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2721,7 +3367,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2729,14 +3378,20 @@
       <c r="G39" t="n">
         <v>6</v>
       </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
       <c r="I39" t="n">
+        <v>8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K39" t="n">
         <v>7</v>
       </c>
-      <c r="J39" t="n">
-        <v>7</v>
-      </c>
       <c r="M39" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -2744,20 +3399,39 @@
       <c r="P39" t="n">
         <v>1</v>
       </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" t="n">
         <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2766,36 +3440,33 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" t="n">
         <v>3</v>
       </c>
-      <c r="D40" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M40" t="n">
         <v>2.5</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>1</v>
       </c>
       <c r="P40" t="n">
@@ -2807,9 +3478,6 @@
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
@@ -2818,12 +3486,28 @@
       </c>
       <c r="V40" t="n">
         <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2832,25 +3516,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
       </c>
       <c r="H41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" t="n">
         <v>7</v>
       </c>
-      <c r="J41" t="n">
-        <v>7</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2</v>
+      <c r="L41" t="n">
+        <v>7.5</v>
       </c>
       <c r="M41" t="n">
         <v>2.5</v>
@@ -2864,20 +3548,33 @@
       <c r="Q41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" t="n">
         <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2886,10 +3583,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
@@ -2898,10 +3595,22 @@
         <v>6</v>
       </c>
       <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
         <v>7</v>
       </c>
-      <c r="J42" t="n">
-        <v>4.5</v>
+      <c r="K42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -2912,14 +3621,39 @@
       <c r="Q42" t="n">
         <v>1</v>
       </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
       <c r="S42" t="n">
         <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gravedad: atracción hacia la Tierra</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2928,34 +3662,34 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
       </c>
       <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K43" t="n">
         <v>3</v>
       </c>
-      <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" t="n">
-        <v>5</v>
-      </c>
       <c r="L43" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
         <v>2.5</v>
@@ -2987,11 +3721,24 @@
       <c r="V43" t="n">
         <v>1</v>
       </c>
+      <c r="AF43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3000,28 +3747,83 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
         <v>8</v>
       </c>
-      <c r="D44" t="n">
-        <v>8</v>
+      <c r="G44" t="n">
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" t="n">
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
       <c r="V44" t="n">
         <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3030,32 +3832,38 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
       </c>
       <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7</v>
+      </c>
+      <c r="I45" t="n">
         <v>8</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>2.5</v>
       </c>
-      <c r="L45" t="n">
-        <v>3</v>
+      <c r="K45" t="n">
+        <v>4</v>
       </c>
       <c r="M45" t="n">
         <v>2.5</v>
       </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
@@ -3071,17 +3879,30 @@
       <c r="S45" t="n">
         <v>1</v>
       </c>
-      <c r="U45" t="n">
+      <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Inducción electromagnética: Faraday y Lenz</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3090,22 +3911,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3113,17 +3943,39 @@
       <c r="P46" t="n">
         <v>1</v>
       </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
       <c r="R46" t="n">
         <v>1</v>
       </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
       <c r="V46" t="n">
         <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Magnitudes escalares y vectoriales</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3132,26 +3984,41 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K47" t="n">
         <v>3</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6</v>
-      </c>
-      <c r="K47" t="n">
-        <v>6</v>
       </c>
       <c r="M47" t="n">
         <v>2.5</v>
       </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
@@ -3161,17 +4028,33 @@
       <c r="R47" t="n">
         <v>1</v>
       </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="V47" t="n">
         <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3180,25 +4063,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -3209,17 +4098,39 @@
       <c r="Q48" t="n">
         <v>1</v>
       </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
       <c r="S48" t="n">
         <v>1</v>
       </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
       <c r="V48" t="n">
         <v>1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3228,31 +4139,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="L49" t="n">
+        <v>7.5</v>
       </c>
       <c r="M49" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -3260,9 +4171,6 @@
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
       <c r="R49" t="n">
         <v>1</v>
       </c>
@@ -3272,224 +4180,192 @@
       <c r="T49" t="n">
         <v>1</v>
       </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
       <c r="V49" t="n">
         <v>1</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Masa y peso</t>
+          <t>Aplicaciones de las leyes de Newton</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
-      <c r="F50" t="n">
         <v>4</v>
       </c>
-      <c r="G50" t="n">
-        <v>6</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K50" t="n">
-        <v>5</v>
-      </c>
-      <c r="L50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1</v>
+      <c r="AF50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" t="n">
-        <v>6</v>
-      </c>
-      <c r="K52" t="n">
-        <v>3</v>
-      </c>
-      <c r="L52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Calor latente</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K53" t="n">
-        <v>6</v>
-      </c>
-      <c r="L53" t="n">
-        <v>4</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -3500,31 +4376,29 @@
       <c r="Q53" t="n">
         <v>1</v>
       </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1</v>
+      <c r="AF53" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3537,7 +4411,7 @@
         <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G54" t="n">
         <v>6</v>
@@ -3546,13 +4420,16 @@
         <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
@@ -3569,22 +4446,38 @@
       <c r="S54" t="n">
         <v>1</v>
       </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
       <c r="U54" t="n">
         <v>1</v>
       </c>
       <c r="V54" t="n">
         <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Campo eléctrico</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3593,310 +4486,372 @@
       <c r="D55" t="n">
         <v>6</v>
       </c>
-      <c r="E55" t="n">
-        <v>4</v>
-      </c>
       <c r="F55" t="n">
         <v>8</v>
       </c>
       <c r="G55" t="n">
         <v>6</v>
       </c>
-      <c r="H55" t="n">
-        <v>7</v>
-      </c>
-      <c r="I55" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7</v>
-      </c>
-      <c r="K55" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M55" t="n">
-        <v>7</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
+      <c r="AF55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" t="n">
-        <v>8</v>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="G56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Movimiento armónico simple</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>8</v>
       </c>
-      <c r="I57" t="n">
+      <c r="G57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
+      <c r="L57" t="n">
         <v>4</v>
       </c>
+      <c r="M57" t="n">
+        <v>7</v>
+      </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cinemática en dos dimensiones y proyectiles</t>
+          <t>Capacitancia y condensadores</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
-      </c>
-      <c r="G58" t="n">
-        <v>6</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
-      </c>
-      <c r="G59" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H59" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Colisiones elásticas e inelásticas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" t="n">
-        <v>2</v>
-      </c>
-      <c r="I60" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>3</v>
-      </c>
-      <c r="M60" t="n">
-        <v>7</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="P60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="n">
-        <v>1</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1</v>
+      <c r="AF60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Niveles de energía atómicos y espectros</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
+      <c r="K61" t="n">
         <v>8</v>
       </c>
-      <c r="D61" t="n">
-        <v>8</v>
-      </c>
-      <c r="G61" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1</v>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ondas estacionarias y armónicos</t>
+          <t>Cuantización de la energía</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
-      </c>
-      <c r="H62" t="n">
         <v>7</v>
       </c>
-      <c r="M62" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
+      <c r="AF62" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3905,99 +4860,116 @@
       <c r="D63" t="n">
         <v>8</v>
       </c>
-      <c r="E63" t="n">
-        <v>8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>6</v>
-      </c>
-      <c r="M63" t="n">
-        <v>7</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1</v>
+      <c r="AF63" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
-      </c>
-      <c r="F64" t="n">
-        <v>8</v>
-      </c>
-      <c r="I64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6</v>
+      </c>
+      <c r="K64" t="n">
         <v>4</v>
       </c>
-      <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
+      <c r="M64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
       <c r="G65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>4.5</v>
       </c>
       <c r="K65" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="L65" t="n">
+        <v>4</v>
       </c>
       <c r="M65" t="n">
         <v>2.5</v>
       </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
@@ -4016,97 +4988,132 @@
       <c r="T65" t="n">
         <v>1</v>
       </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
       <c r="V65" t="n">
         <v>1</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="n">
         <v>8</v>
       </c>
-      <c r="D66" t="n">
-        <v>8</v>
-      </c>
       <c r="G66" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I66" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="H66" t="n">
+        <v>7</v>
+      </c>
+      <c r="J66" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L66" t="n">
+        <v>4</v>
       </c>
       <c r="M66" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
       </c>
-      <c r="R66" t="n">
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
         <v>1</v>
       </c>
       <c r="V66" t="n">
         <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Espejos esféricos</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
-      </c>
-      <c r="D67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F67" t="n">
         <v>8</v>
       </c>
-      <c r="G67" t="n">
-        <v>6</v>
-      </c>
       <c r="H67" t="n">
-        <v>4</v>
-      </c>
-      <c r="I67" t="n">
-        <v>3</v>
-      </c>
-      <c r="K67" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>7</v>
       </c>
       <c r="L67" t="n">
         <v>7.5</v>
       </c>
       <c r="M67" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T67" t="n">
+      <c r="S67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
@@ -4114,42 +5121,55 @@
       </c>
       <c r="V67" t="n">
         <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G68" t="n">
         <v>6</v>
       </c>
       <c r="H68" t="n">
-        <v>4</v>
-      </c>
-      <c r="I68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="n">
         <v>7</v>
       </c>
       <c r="L68" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M68" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -4160,7 +5180,7 @@
       <c r="Q68" t="n">
         <v>1</v>
       </c>
-      <c r="R68" t="n">
+      <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
@@ -4168,17 +5188,30 @@
       </c>
       <c r="V68" t="n">
         <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4187,8 +5220,8 @@
       <c r="D69" t="n">
         <v>5</v>
       </c>
-      <c r="E69" t="n">
-        <v>6</v>
+      <c r="F69" t="n">
+        <v>8</v>
       </c>
       <c r="G69" t="n">
         <v>6</v>
@@ -4196,56 +5229,63 @@
       <c r="H69" t="n">
         <v>7</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
         <v>8</v>
       </c>
-      <c r="J69" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K69" t="n">
-        <v>5</v>
-      </c>
-      <c r="M69" t="n">
-        <v>7</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>1</v>
-      </c>
-      <c r="T69" t="n">
-        <v>1</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1</v>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
         <v>8</v>
@@ -4254,100 +5294,147 @@
         <v>6</v>
       </c>
       <c r="H70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I70" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
         <v>8</v>
       </c>
-      <c r="J70" t="n">
-        <v>7</v>
-      </c>
-      <c r="K70" t="n">
-        <v>7</v>
-      </c>
-      <c r="L70" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M70" t="n">
-        <v>7</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" t="n">
-        <v>1</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1</v>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3</v>
       </c>
       <c r="H71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
         <v>7</v>
       </c>
       <c r="K71" t="n">
         <v>5</v>
       </c>
+      <c r="L71" t="n">
+        <v>6</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
       <c r="T71" t="n">
         <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Inducción electromagnética: Faraday y Lenz</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F72" t="n">
         <v>8</v>
       </c>
-      <c r="K72" t="n">
-        <v>7</v>
+      <c r="G72" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5</v>
       </c>
       <c r="M72" t="n">
         <v>7</v>
@@ -4355,63 +5442,61 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="T72" t="n">
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
         <v>1</v>
       </c>
       <c r="V72" t="n">
         <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Magnitudes escalares y vectoriales</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>4</v>
-      </c>
-      <c r="F73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
-      </c>
-      <c r="L73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M73" t="n">
         <v>2.5</v>
       </c>
-      <c r="N73" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" t="n">
-        <v>1</v>
-      </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
@@ -4421,38 +5506,48 @@
       <c r="R73" t="n">
         <v>1</v>
       </c>
-      <c r="S73" t="n">
-        <v>1</v>
-      </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
-      <c r="U73" t="n">
-        <v>1</v>
-      </c>
       <c r="V73" t="n">
         <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Masa y peso</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G74" t="n">
         <v>6</v>
@@ -4461,16 +5556,22 @@
         <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6</v>
       </c>
       <c r="M74" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -4490,59 +5591,57 @@
       <c r="T74" t="n">
         <v>1</v>
       </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
       <c r="V74" t="n">
         <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
-      </c>
-      <c r="E75" t="n">
-        <v>4</v>
-      </c>
-      <c r="F75" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
         <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
         <v>3</v>
       </c>
       <c r="L75" t="n">
-        <v>4</v>
-      </c>
-      <c r="M75" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -4553,284 +5652,226 @@
       <c r="R75" t="n">
         <v>1</v>
       </c>
-      <c r="S75" t="n">
-        <v>1</v>
-      </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
         <v>1</v>
       </c>
-      <c r="V75" t="n">
-        <v>1</v>
+      <c r="Z75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Modelo estándar de partículas</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
-      </c>
-      <c r="E76" t="n">
-        <v>6</v>
-      </c>
-      <c r="F76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G76" t="n">
-        <v>6</v>
-      </c>
-      <c r="H76" t="n">
         <v>7</v>
       </c>
-      <c r="I76" t="n">
-        <v>8</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K76" t="n">
-        <v>4</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
-        <v>1</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1</v>
+      <c r="AF76" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Movimiento circular y variables angulares</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" t="n">
-        <v>2</v>
-      </c>
-      <c r="I77" t="n">
-        <v>6</v>
-      </c>
-      <c r="J77" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="K77" t="n">
         <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
-        <v>1</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
-      <c r="S77" t="n">
-        <v>1</v>
-      </c>
       <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="V77" t="n">
         <v>1</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>8</v>
+      </c>
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+      <c r="G78" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C78" t="n">
-        <v>2</v>
-      </c>
-      <c r="D78" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" t="n">
-        <v>8</v>
-      </c>
-      <c r="G78" t="n">
-        <v>2</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K78" t="n">
-        <v>3</v>
-      </c>
-      <c r="M78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Niveles de energía atómicos y espectros</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>6</v>
-      </c>
-      <c r="H79" t="n">
-        <v>7</v>
-      </c>
-      <c r="I79" t="n">
-        <v>8</v>
-      </c>
-      <c r="J79" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>1</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>1</v>
+      <c r="AF79" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>El ojo y los instrumentos ópticos</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J80" t="n">
         <v>4.5</v>
       </c>
-      <c r="L80" t="n">
-        <v>4</v>
+      <c r="K80" t="n">
+        <v>3</v>
       </c>
       <c r="M80" t="n">
         <v>2.5</v>
@@ -4847,197 +5888,235 @@
       <c r="S80" t="n">
         <v>1</v>
       </c>
-      <c r="U80" t="n">
+      <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="V80" t="n">
         <v>1</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad</t>
+          <t>Ondas electromagnéticas y espectro</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8</v>
+      </c>
+      <c r="G81" t="n">
         <v>6</v>
       </c>
-      <c r="D81" t="n">
-        <v>6</v>
+      <c r="H81" t="n">
+        <v>7</v>
+      </c>
+      <c r="L81" t="n">
+        <v>7.5</v>
       </c>
       <c r="M81" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>1</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E82" t="n">
+        <v>8</v>
       </c>
       <c r="G82" t="n">
         <v>6</v>
       </c>
-      <c r="H82" t="n">
-        <v>4</v>
-      </c>
       <c r="M82" t="n">
         <v>7</v>
       </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
       <c r="P82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>1</v>
-      </c>
       <c r="V82" t="n">
         <v>1</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>Órbitas y satélites</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
-      </c>
-      <c r="F83" t="n">
-        <v>4</v>
-      </c>
-      <c r="G83" t="n">
-        <v>2</v>
-      </c>
-      <c r="H83" t="n">
-        <v>2</v>
-      </c>
-      <c r="I83" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K83" t="n">
-        <v>3</v>
-      </c>
-      <c r="M83" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>1</v>
-      </c>
-      <c r="R83" t="n">
-        <v>1</v>
-      </c>
-      <c r="S83" t="n">
-        <v>1</v>
-      </c>
-      <c r="T83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4</v>
+      </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C84" t="n">
-        <v>4</v>
-      </c>
-      <c r="D84" t="n">
-        <v>4</v>
-      </c>
-      <c r="G84" t="n">
-        <v>6</v>
-      </c>
-      <c r="H84" t="n">
-        <v>5</v>
-      </c>
-      <c r="I84" t="n">
-        <v>5</v>
-      </c>
-      <c r="K84" t="n">
-        <v>6</v>
-      </c>
-      <c r="M84" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1</v>
-      </c>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
-      <c r="T84" t="n">
-        <v>1</v>
-      </c>
-      <c r="V84" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>8</v>
@@ -5045,14 +6124,17 @@
       <c r="G85" t="n">
         <v>6</v>
       </c>
+      <c r="H85" t="n">
+        <v>5</v>
+      </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>7</v>
       </c>
       <c r="K85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L85" t="n">
         <v>7.5</v>
@@ -5066,6 +6148,9 @@
       <c r="P85" t="n">
         <v>1</v>
       </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
       <c r="R85" t="n">
         <v>1</v>
       </c>
@@ -5080,164 +6165,155 @@
       </c>
       <c r="V85" t="n">
         <v>1</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>8</v>
+      </c>
+      <c r="M86" t="n">
+        <v>7</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C86" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" t="n">
-        <v>5</v>
-      </c>
-      <c r="F86" t="n">
-        <v>4</v>
-      </c>
-      <c r="G86" t="n">
-        <v>2</v>
-      </c>
-      <c r="H86" t="n">
-        <v>2</v>
-      </c>
-      <c r="I86" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K86" t="n">
-        <v>3</v>
-      </c>
-      <c r="L86" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M86" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>1</v>
-      </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
-      <c r="S86" t="n">
-        <v>1</v>
-      </c>
-      <c r="T86" t="n">
-        <v>1</v>
-      </c>
-      <c r="U86" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Energía potencial y potencial eléctrico</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
-      </c>
-      <c r="F87" t="n">
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
-      </c>
-      <c r="I87" t="n">
-        <v>5</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K87" t="n">
-        <v>3</v>
-      </c>
-      <c r="M87" t="n">
         <v>7</v>
       </c>
-      <c r="O87" t="n">
-        <v>1</v>
-      </c>
       <c r="P87" t="n">
         <v>1</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
-      <c r="R87" t="n">
-        <v>1</v>
-      </c>
-      <c r="S87" t="n">
-        <v>1</v>
-      </c>
-      <c r="T87" t="n">
-        <v>1</v>
-      </c>
-      <c r="V87" t="n">
-        <v>1</v>
+      <c r="AF87" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Calor latente</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
-      </c>
-      <c r="F88" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
       </c>
       <c r="G88" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H88" t="n">
         <v>7</v>
       </c>
-      <c r="O88" t="n">
+      <c r="I88" t="n">
+        <v>8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="M88" t="n">
+        <v>7</v>
+      </c>
+      <c r="N88" t="n">
         <v>1</v>
       </c>
       <c r="P88" t="n">
@@ -5245,105 +6321,211 @@
       </c>
       <c r="Q88" t="n">
         <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Campo eléctrico</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D89" t="n">
+        <v>6</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
-      <c r="G89" t="n">
-        <v>6</v>
+      <c r="K89" t="n">
+        <v>7</v>
+      </c>
+      <c r="M89" t="n">
+        <v>7</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="P89" t="n">
-        <v>1</v>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8</v>
+      </c>
+      <c r="G90" t="n">
+        <v>6</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>8</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4.5</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M90" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
       </c>
       <c r="T90" t="n">
         <v>1</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Reflexión interna total</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
           <t>posterior</t>
         </is>
-      </c>
-      <c r="C91" t="n">
-        <v>9</v>
-      </c>
-      <c r="G91" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I91" t="n">
-        <v>7</v>
-      </c>
-      <c r="M91" t="n">
-        <v>7</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Desintegración radiactiva</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D92" t="n">
+        <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
@@ -5351,6 +6533,24 @@
       <c r="G92" t="n">
         <v>8.5</v>
       </c>
+      <c r="H92" t="n">
+        <v>5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M92" t="n">
+        <v>4.5</v>
+      </c>
       <c r="N92" t="n">
         <v>1</v>
       </c>
@@ -5359,107 +6559,240 @@
       </c>
       <c r="P92" t="n">
         <v>1</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>9</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H93" t="n">
+        <v>7</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
+      </c>
+      <c r="K93" t="n">
+        <v>7</v>
+      </c>
+      <c r="M93" t="n">
+        <v>7</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
           <t>posterior</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="n">
-        <v>8</v>
-      </c>
-      <c r="N93" t="n">
-        <v>1</v>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8</v>
       </c>
       <c r="G94" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J94" t="n">
+        <v>7</v>
+      </c>
+      <c r="L94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="n">
         <v>6</v>
       </c>
-      <c r="K94" t="n">
-        <v>4</v>
-      </c>
-      <c r="M94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
-      <c r="T94" t="n">
-        <v>1</v>
-      </c>
-      <c r="V94" t="n">
-        <v>1</v>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Defecto de masa y energía de enlace nuclear</t>
+          <t>Segunda ley de la termodinámica</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
           <t>posterior</t>
         </is>
-      </c>
-      <c r="C95" t="n">
-        <v>11</v>
-      </c>
-      <c r="F95" t="n">
-        <v>8</v>
-      </c>
-      <c r="O95" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fisión y fusión nuclear</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
-      </c>
-      <c r="F96" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>6</v>
+      </c>
+      <c r="H96" t="n">
+        <v>7</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K96" t="n">
         <v>8</v>
       </c>
       <c r="L96" t="n">
         <v>7.5</v>
       </c>
       <c r="M96" t="n">
-        <v>7</v>
-      </c>
-      <c r="O96" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
         <v>1</v>
       </c>
       <c r="U96" t="n">
@@ -5467,63 +6800,110 @@
       </c>
       <c r="V96" t="n">
         <v>1</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fotón y efecto fotoeléctrico</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
-      </c>
-      <c r="E97" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
       </c>
       <c r="G97" t="n">
         <v>6</v>
       </c>
-      <c r="N97" t="n">
-        <v>1</v>
+      <c r="H97" t="n">
+        <v>7</v>
+      </c>
+      <c r="I97" t="n">
+        <v>8</v>
+      </c>
+      <c r="J97" t="n">
+        <v>7</v>
       </c>
       <c r="P97" t="n">
         <v>1</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ley de Coulomb</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G98" t="n">
-        <v>6</v>
-      </c>
-      <c r="I98" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="L98" t="n">
+        <v>4</v>
       </c>
       <c r="M98" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
@@ -5531,110 +6911,249 @@
       <c r="P98" t="n">
         <v>1</v>
       </c>
-      <c r="R98" t="n">
+      <c r="Q98" t="n">
         <v>1</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
       </c>
+      <c r="U98" t="n">
+        <v>1</v>
+      </c>
       <c r="V98" t="n">
         <v>1</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Leyes de Kepler</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>8</v>
+      </c>
+      <c r="G99" t="n">
+        <v>6</v>
+      </c>
+      <c r="H99" t="n">
+        <v>7</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M99" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
           <t>posterior</t>
         </is>
-      </c>
-      <c r="C99" t="n">
-        <v>4</v>
-      </c>
-      <c r="D99" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="D100" t="n">
+        <v>5</v>
       </c>
       <c r="G100" t="n">
         <v>6</v>
       </c>
-      <c r="I100" t="n">
+      <c r="H100" t="n">
+        <v>4</v>
+      </c>
+      <c r="M100" t="n">
         <v>7</v>
       </c>
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="R100" t="n">
-        <v>1</v>
+      <c r="Q100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Núcleo atómico e isótopos</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
-      </c>
-      <c r="F101" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4</v>
       </c>
       <c r="G101" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O101" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H101" t="n">
+        <v>5</v>
+      </c>
+      <c r="I101" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" t="n">
+        <v>6</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.5</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ondas de radio y telecomunicaciones</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>11</v>
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" t="n">
+        <v>4.5</v>
       </c>
       <c r="M102" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
@@ -5642,41 +7161,112 @@
       <c r="Q102" t="n">
         <v>1</v>
       </c>
+      <c r="R102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>1</v>
+      </c>
       <c r="V102" t="n">
         <v>1</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Energía potencial y potencial eléctrico</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" t="n">
+        <v>8</v>
       </c>
       <c r="G103" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H103" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3</v>
+      </c>
+      <c r="M103" t="n">
         <v>7</v>
       </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
       <c r="P103" t="n">
         <v>1</v>
       </c>
       <c r="Q103" t="n">
         <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5685,37 +7275,44 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
-      </c>
-      <c r="F104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G104" t="n">
         <v>8.5</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>7</v>
       </c>
-      <c r="L104" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O104" t="n">
-        <v>1</v>
+      <c r="M104" t="n">
+        <v>7</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" t="n">
-        <v>1</v>
+      <c r="R104" t="n">
+        <v>1</v>
+      </c>
+      <c r="V104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Radiación térmica y cuerpo negro</t>
+          <t>Desintegración radiactiva</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5726,35 +7323,42 @@
       <c r="C105" t="n">
         <v>10</v>
       </c>
-      <c r="H105" t="n">
-        <v>7</v>
-      </c>
-      <c r="J105" t="n">
-        <v>7</v>
-      </c>
-      <c r="K105" t="n">
-        <v>6</v>
-      </c>
-      <c r="L105" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>1</v>
-      </c>
-      <c r="S105" t="n">
-        <v>1</v>
-      </c>
-      <c r="T105" t="n">
-        <v>1</v>
-      </c>
-      <c r="U105" t="n">
-        <v>1</v>
+      <c r="E105" t="n">
+        <v>8</v>
+      </c>
+      <c r="F105" t="n">
+        <v>8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Rapidez de la luz</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5763,37 +7367,32 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
-      </c>
-      <c r="G106" t="n">
-        <v>6</v>
-      </c>
-      <c r="H106" t="n">
-        <v>7</v>
-      </c>
-      <c r="L106" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M106" t="n">
-        <v>7</v>
-      </c>
-      <c r="P106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" t="n">
-        <v>1</v>
-      </c>
-      <c r="V106" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="E106" t="n">
+        <v>8</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Reflexión interna total</t>
+          <t>Defecto de masa y energía de enlace nuclear</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5802,19 +7401,32 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
-      </c>
-      <c r="H107" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="F107" t="n">
+        <v>8</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Segunda ley de la termodinámica</t>
+          <t>Fisión y fusión nuclear</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5825,17 +7437,42 @@
       <c r="C108" t="n">
         <v>9</v>
       </c>
-      <c r="G108" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P108" t="n">
-        <v>1</v>
+      <c r="F108" t="n">
+        <v>8</v>
+      </c>
+      <c r="L108" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M108" t="n">
+        <v>7</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Semiconductores y electrónica básica</t>
+          <t>Fotón y efecto fotoeléctrico</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5844,19 +7481,38 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
-      </c>
-      <c r="J109" t="n">
-        <v>7</v>
-      </c>
-      <c r="S109" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="E109" t="n">
+        <v>8</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Superposición e interferencia de ondas</t>
+          <t>Ley de Coulomb</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5865,19 +7521,59 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" t="n">
+        <v>8</v>
       </c>
       <c r="G110" t="n">
         <v>6</v>
       </c>
+      <c r="I110" t="n">
+        <v>7</v>
+      </c>
+      <c r="J110" t="n">
+        <v>7</v>
+      </c>
+      <c r="M110" t="n">
+        <v>7</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
       <c r="P110" t="n">
         <v>1</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Leyes de Kepler</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5886,37 +7582,29 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
-      </c>
-      <c r="G111" t="n">
-        <v>6</v>
-      </c>
-      <c r="H111" t="n">
-        <v>7</v>
-      </c>
-      <c r="J111" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M111" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>1</v>
-      </c>
-      <c r="S111" t="n">
-        <v>1</v>
-      </c>
-      <c r="V111" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D111" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Viscosidad y régimen de flujo</t>
+          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5925,118 +7613,203 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
-      </c>
-      <c r="K112" t="n">
+        <v>11</v>
+      </c>
+      <c r="G112" t="n">
+        <v>6</v>
+      </c>
+      <c r="I112" t="n">
         <v>7</v>
       </c>
-      <c r="T112" t="n">
-        <v>1</v>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Núcleo atómico e isótopos</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C113" t="n">
+        <v>11</v>
+      </c>
+      <c r="F113" t="n">
         <v>8</v>
       </c>
-      <c r="D113" t="n">
-        <v>8</v>
+      <c r="G113" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
-      </c>
-      <c r="D114" t="n">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="G114" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>7</v>
+      </c>
+      <c r="M114" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Órbitas y satélites</t>
+          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C115" t="n">
+        <v>11</v>
+      </c>
+      <c r="F115" t="n">
         <v>8</v>
       </c>
-      <c r="D115" t="n">
-        <v>8</v>
+      <c r="G115" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>7</v>
+      </c>
+      <c r="L115" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Radiación térmica y cuerpo negro</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C116" t="n">
+        <v>10</v>
+      </c>
+      <c r="H116" t="n">
+        <v>7</v>
+      </c>
+      <c r="J116" t="n">
+        <v>7</v>
+      </c>
+      <c r="K116" t="n">
         <v>6</v>
       </c>
-      <c r="D116" t="n">
-        <v>6</v>
-      </c>
-      <c r="E116" t="n">
-        <v>2</v>
-      </c>
-      <c r="F116" t="n">
-        <v>8</v>
-      </c>
-      <c r="G116" t="n">
-        <v>6</v>
-      </c>
-      <c r="H116" t="n">
-        <v>2</v>
-      </c>
-      <c r="J116" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K116" t="n">
-        <v>4</v>
-      </c>
       <c r="L116" t="n">
-        <v>4</v>
-      </c>
-      <c r="M116" t="n">
-        <v>7</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
@@ -6050,56 +7823,45 @@
       <c r="U116" t="n">
         <v>1</v>
       </c>
-      <c r="V116" t="n">
-        <v>1</v>
+      <c r="AF116" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Rapidez de la luz</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
-      </c>
-      <c r="D117" t="n">
-        <v>5</v>
-      </c>
-      <c r="E117" t="n">
-        <v>3</v>
-      </c>
-      <c r="F117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H117" t="n">
-        <v>2</v>
-      </c>
-      <c r="I117" t="n">
-        <v>2</v>
-      </c>
-      <c r="J117" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L117" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M117" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N117" t="n">
-        <v>1</v>
-      </c>
-      <c r="O117" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P117" t="n">
         <v>1</v>
@@ -6107,485 +7869,666 @@
       <c r="Q117" t="n">
         <v>1</v>
       </c>
-      <c r="R117" t="n">
-        <v>1</v>
-      </c>
-      <c r="S117" t="n">
-        <v>1</v>
-      </c>
       <c r="U117" t="n">
         <v>1</v>
       </c>
       <c r="V117" t="n">
         <v>1</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Espejos esféricos</t>
+          <t>Semiconductores y electrónica básica</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>10</v>
-      </c>
-      <c r="F118" t="n">
-        <v>8</v>
-      </c>
-      <c r="H118" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J118" t="n">
         <v>7</v>
       </c>
-      <c r="L118" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M118" t="n">
-        <v>7</v>
-      </c>
-      <c r="O118" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>1</v>
-      </c>
       <c r="S118" t="n">
         <v>1</v>
       </c>
-      <c r="U118" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" t="n">
-        <v>1</v>
+      <c r="AF118" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Espejos planos e imágenes</t>
+          <t>Superposición e interferencia de ondas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>10</v>
       </c>
-      <c r="H119" t="n">
-        <v>3</v>
-      </c>
-      <c r="J119" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L119" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M119" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>1</v>
-      </c>
-      <c r="S119" t="n">
-        <v>1</v>
-      </c>
-      <c r="U119" t="n">
-        <v>1</v>
-      </c>
-      <c r="V119" t="n">
-        <v>1</v>
+      <c r="G119" t="n">
+        <v>6</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Fricción y resistencia del aire</t>
+          <t>Viscosidad y régimen de flujo</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>9</v>
       </c>
-      <c r="E120" t="n">
-        <v>2</v>
-      </c>
-      <c r="F120" t="n">
-        <v>8</v>
-      </c>
-      <c r="G120" t="n">
-        <v>2</v>
-      </c>
-      <c r="H120" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" t="n">
+      <c r="K120" t="n">
         <v>7</v>
       </c>
-      <c r="K120" t="n">
-        <v>5</v>
-      </c>
-      <c r="L120" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M120" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N120" t="n">
-        <v>1</v>
-      </c>
-      <c r="O120" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>1</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1</v>
-      </c>
       <c r="T120" t="n">
         <v>1</v>
       </c>
-      <c r="U120" t="n">
-        <v>1</v>
-      </c>
-      <c r="V120" t="n">
-        <v>1</v>
+      <c r="AF120" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>Aceleración y fuerza centrípeta</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
-      </c>
-      <c r="F121" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" t="n">
+        <v>5</v>
+      </c>
+      <c r="M121" t="n">
+        <v>7</v>
+      </c>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="n">
         <v>8</v>
       </c>
-      <c r="H121" t="n">
-        <v>5</v>
-      </c>
-      <c r="I121" t="n">
-        <v>6</v>
-      </c>
-      <c r="J121" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M121" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>1</v>
-      </c>
-      <c r="R121" t="n">
-        <v>1</v>
-      </c>
-      <c r="S121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1</v>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
-      </c>
-      <c r="F122" t="n">
         <v>8</v>
       </c>
-      <c r="G122" t="n">
-        <v>6</v>
-      </c>
-      <c r="H122" t="n">
-        <v>7</v>
-      </c>
-      <c r="I122" t="n">
-        <v>7</v>
-      </c>
-      <c r="J122" t="n">
-        <v>7</v>
-      </c>
-      <c r="K122" t="n">
+      <c r="D122" t="n">
         <v>8</v>
       </c>
-      <c r="L122" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M122" t="n">
-        <v>7</v>
-      </c>
-      <c r="O122" t="n">
-        <v>1</v>
-      </c>
-      <c r="P122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>1</v>
-      </c>
-      <c r="R122" t="n">
-        <v>1</v>
-      </c>
-      <c r="S122" t="n">
-        <v>1</v>
-      </c>
-      <c r="T122" t="n">
-        <v>1</v>
-      </c>
-      <c r="U122" t="n">
-        <v>1</v>
-      </c>
-      <c r="V122" t="n">
-        <v>1</v>
+      <c r="AF122" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>El ojo y los instrumentos ópticos</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
-      </c>
-      <c r="F123" t="n">
-        <v>8</v>
-      </c>
-      <c r="G123" t="n">
-        <v>6</v>
-      </c>
-      <c r="H123" t="n">
         <v>5</v>
       </c>
-      <c r="J123" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K123" t="n">
-        <v>3</v>
-      </c>
-      <c r="M123" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O123" t="n">
-        <v>1</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>1</v>
-      </c>
-      <c r="S123" t="n">
-        <v>1</v>
-      </c>
-      <c r="T123" t="n">
-        <v>1</v>
-      </c>
-      <c r="V123" t="n">
-        <v>1</v>
+      <c r="D123" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
-      </c>
-      <c r="F124" t="n">
         <v>8</v>
       </c>
-      <c r="G124" t="n">
-        <v>6</v>
+      <c r="D124" t="n">
+        <v>8</v>
       </c>
       <c r="H124" t="n">
         <v>7</v>
       </c>
-      <c r="L124" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M124" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O124" t="n">
-        <v>1</v>
-      </c>
-      <c r="P124" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q124" t="n">
         <v>1</v>
       </c>
-      <c r="U124" t="n">
-        <v>1</v>
-      </c>
       <c r="V124" t="n">
         <v>1</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>Movimiento armónico simple</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
-      </c>
-      <c r="E125" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125" t="n">
         <v>8</v>
       </c>
-      <c r="G125" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H125" t="n">
-        <v>5</v>
-      </c>
       <c r="I125" t="n">
-        <v>6</v>
-      </c>
-      <c r="J125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K125" t="n">
-        <v>3</v>
-      </c>
-      <c r="L125" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="P125" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>1</v>
-      </c>
       <c r="R125" t="n">
         <v>1</v>
       </c>
-      <c r="S125" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" t="n">
-        <v>1</v>
-      </c>
-      <c r="U125" t="n">
-        <v>1</v>
-      </c>
-      <c r="V125" t="n">
-        <v>1</v>
+      <c r="AF125" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Cinemática en dos dimensiones y proyectiles</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>8</v>
+      </c>
+      <c r="G126" t="n">
+        <v>6</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Ondas estacionarias y armónicos</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>8</v>
+      </c>
+      <c r="D127" t="n">
+        <v>8</v>
+      </c>
+      <c r="H127" t="n">
+        <v>7</v>
+      </c>
+      <c r="M127" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1</v>
+      </c>
+      <c r="V127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Hidrodinámica: continuidad y Bernoulli</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>6</v>
+      </c>
+      <c r="D128" t="n">
+        <v>6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>7</v>
+      </c>
+      <c r="K128" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Tensión superficial y capilaridad</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>6</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6</v>
+      </c>
+      <c r="M129" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Espejos planos e imágenes</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>tardio</t>
         </is>
       </c>
-      <c r="C126" t="n">
+      <c r="C130" t="n">
+        <v>7</v>
+      </c>
+      <c r="D130" t="n">
+        <v>7</v>
+      </c>
+      <c r="H130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L130" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M130" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>1</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1</v>
+      </c>
+      <c r="U130" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF130" t="n">
         <v>10</v>
       </c>
-      <c r="G126" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H126" t="n">
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Lentes delgadas e imágenes</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>10</v>
+      </c>
+      <c r="F131" t="n">
+        <v>8</v>
+      </c>
+      <c r="H131" t="n">
+        <v>5</v>
+      </c>
+      <c r="I131" t="n">
+        <v>6</v>
+      </c>
+      <c r="J131" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M131" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1</v>
+      </c>
+      <c r="R131" t="n">
+        <v>1</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ley de Ohm</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>9</v>
+      </c>
+      <c r="F132" t="n">
+        <v>8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>6</v>
+      </c>
+      <c r="H132" t="n">
         <v>7</v>
       </c>
-      <c r="I126" t="n">
-        <v>3</v>
-      </c>
-      <c r="K126" t="n">
+      <c r="I132" t="n">
         <v>7</v>
       </c>
-      <c r="M126" t="n">
+      <c r="J132" t="n">
         <v>7</v>
       </c>
-      <c r="P126" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>1</v>
-      </c>
-      <c r="R126" t="n">
-        <v>1</v>
-      </c>
-      <c r="T126" t="n">
-        <v>1</v>
-      </c>
-      <c r="V126" t="n">
-        <v>1</v>
+      <c r="K132" t="n">
+        <v>8</v>
+      </c>
+      <c r="L132" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M132" t="n">
+        <v>7</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" t="n">
+        <v>1</v>
+      </c>
+      <c r="V132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6599,7 +8542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -11904,6 +13847,258 @@
       </c>
       <c r="J126">
         <f>Datos!B126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <f>Datos!A127</f>
+        <v/>
+      </c>
+      <c r="B127">
+        <f>IF(Datos!C127="","",Datos!C127)</f>
+        <v/>
+      </c>
+      <c r="C127">
+        <f>COUNT(Datos!E127:M127)</f>
+        <v/>
+      </c>
+      <c r="D127">
+        <f>IF(C127=0,"",MEDIAN(Datos!E127:M127))</f>
+        <v/>
+      </c>
+      <c r="E127">
+        <f>COUNT(Datos!W127:AE127)</f>
+        <v/>
+      </c>
+      <c r="F127">
+        <f>IF(OR(B127="",D127=""),"",B127-D127)</f>
+        <v/>
+      </c>
+      <c r="G127">
+        <f>IF(Datos!D127="","",Datos!D127)</f>
+        <v/>
+      </c>
+      <c r="H127">
+        <f>COUNT(Datos!N127:V127)</f>
+        <v/>
+      </c>
+      <c r="I127">
+        <f>IF(B127="",IF(C127&gt;=5,"falta en SV",""),IF(G127="",IF(B127&gt;8,IF(C127&gt;=5,"SV tarde","despues del tramo"),IF(H127&gt;=5,"no retomado en 2-8","previo")),IF(B127&lt;2,"retomado",IF(AND(C127&lt;=1,E127&gt;=3),"solo especializacion",IF(F127="","coherente",IF(F127&lt;=-1.5,"SV adelantado",IF(F127&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J127">
+        <f>Datos!B127</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <f>Datos!A128</f>
+        <v/>
+      </c>
+      <c r="B128">
+        <f>IF(Datos!C128="","",Datos!C128)</f>
+        <v/>
+      </c>
+      <c r="C128">
+        <f>COUNT(Datos!E128:M128)</f>
+        <v/>
+      </c>
+      <c r="D128">
+        <f>IF(C128=0,"",MEDIAN(Datos!E128:M128))</f>
+        <v/>
+      </c>
+      <c r="E128">
+        <f>COUNT(Datos!W128:AE128)</f>
+        <v/>
+      </c>
+      <c r="F128">
+        <f>IF(OR(B128="",D128=""),"",B128-D128)</f>
+        <v/>
+      </c>
+      <c r="G128">
+        <f>IF(Datos!D128="","",Datos!D128)</f>
+        <v/>
+      </c>
+      <c r="H128">
+        <f>COUNT(Datos!N128:V128)</f>
+        <v/>
+      </c>
+      <c r="I128">
+        <f>IF(B128="",IF(C128&gt;=5,"falta en SV",""),IF(G128="",IF(B128&gt;8,IF(C128&gt;=5,"SV tarde","despues del tramo"),IF(H128&gt;=5,"no retomado en 2-8","previo")),IF(B128&lt;2,"retomado",IF(AND(C128&lt;=1,E128&gt;=3),"solo especializacion",IF(F128="","coherente",IF(F128&lt;=-1.5,"SV adelantado",IF(F128&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J128">
+        <f>Datos!B128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <f>Datos!A129</f>
+        <v/>
+      </c>
+      <c r="B129">
+        <f>IF(Datos!C129="","",Datos!C129)</f>
+        <v/>
+      </c>
+      <c r="C129">
+        <f>COUNT(Datos!E129:M129)</f>
+        <v/>
+      </c>
+      <c r="D129">
+        <f>IF(C129=0,"",MEDIAN(Datos!E129:M129))</f>
+        <v/>
+      </c>
+      <c r="E129">
+        <f>COUNT(Datos!W129:AE129)</f>
+        <v/>
+      </c>
+      <c r="F129">
+        <f>IF(OR(B129="",D129=""),"",B129-D129)</f>
+        <v/>
+      </c>
+      <c r="G129">
+        <f>IF(Datos!D129="","",Datos!D129)</f>
+        <v/>
+      </c>
+      <c r="H129">
+        <f>COUNT(Datos!N129:V129)</f>
+        <v/>
+      </c>
+      <c r="I129">
+        <f>IF(B129="",IF(C129&gt;=5,"falta en SV",""),IF(G129="",IF(B129&gt;8,IF(C129&gt;=5,"SV tarde","despues del tramo"),IF(H129&gt;=5,"no retomado en 2-8","previo")),IF(B129&lt;2,"retomado",IF(AND(C129&lt;=1,E129&gt;=3),"solo especializacion",IF(F129="","coherente",IF(F129&lt;=-1.5,"SV adelantado",IF(F129&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J129">
+        <f>Datos!B129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <f>Datos!A130</f>
+        <v/>
+      </c>
+      <c r="B130">
+        <f>IF(Datos!C130="","",Datos!C130)</f>
+        <v/>
+      </c>
+      <c r="C130">
+        <f>COUNT(Datos!E130:M130)</f>
+        <v/>
+      </c>
+      <c r="D130">
+        <f>IF(C130=0,"",MEDIAN(Datos!E130:M130))</f>
+        <v/>
+      </c>
+      <c r="E130">
+        <f>COUNT(Datos!W130:AE130)</f>
+        <v/>
+      </c>
+      <c r="F130">
+        <f>IF(OR(B130="",D130=""),"",B130-D130)</f>
+        <v/>
+      </c>
+      <c r="G130">
+        <f>IF(Datos!D130="","",Datos!D130)</f>
+        <v/>
+      </c>
+      <c r="H130">
+        <f>COUNT(Datos!N130:V130)</f>
+        <v/>
+      </c>
+      <c r="I130">
+        <f>IF(B130="",IF(C130&gt;=5,"falta en SV",""),IF(G130="",IF(B130&gt;8,IF(C130&gt;=5,"SV tarde","despues del tramo"),IF(H130&gt;=5,"no retomado en 2-8","previo")),IF(B130&lt;2,"retomado",IF(AND(C130&lt;=1,E130&gt;=3),"solo especializacion",IF(F130="","coherente",IF(F130&lt;=-1.5,"SV adelantado",IF(F130&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J130">
+        <f>Datos!B130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <f>Datos!A131</f>
+        <v/>
+      </c>
+      <c r="B131">
+        <f>IF(Datos!C131="","",Datos!C131)</f>
+        <v/>
+      </c>
+      <c r="C131">
+        <f>COUNT(Datos!E131:M131)</f>
+        <v/>
+      </c>
+      <c r="D131">
+        <f>IF(C131=0,"",MEDIAN(Datos!E131:M131))</f>
+        <v/>
+      </c>
+      <c r="E131">
+        <f>COUNT(Datos!W131:AE131)</f>
+        <v/>
+      </c>
+      <c r="F131">
+        <f>IF(OR(B131="",D131=""),"",B131-D131)</f>
+        <v/>
+      </c>
+      <c r="G131">
+        <f>IF(Datos!D131="","",Datos!D131)</f>
+        <v/>
+      </c>
+      <c r="H131">
+        <f>COUNT(Datos!N131:V131)</f>
+        <v/>
+      </c>
+      <c r="I131">
+        <f>IF(B131="",IF(C131&gt;=5,"falta en SV",""),IF(G131="",IF(B131&gt;8,IF(C131&gt;=5,"SV tarde","despues del tramo"),IF(H131&gt;=5,"no retomado en 2-8","previo")),IF(B131&lt;2,"retomado",IF(AND(C131&lt;=1,E131&gt;=3),"solo especializacion",IF(F131="","coherente",IF(F131&lt;=-1.5,"SV adelantado",IF(F131&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J131">
+        <f>Datos!B131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <f>Datos!A132</f>
+        <v/>
+      </c>
+      <c r="B132">
+        <f>IF(Datos!C132="","",Datos!C132)</f>
+        <v/>
+      </c>
+      <c r="C132">
+        <f>COUNT(Datos!E132:M132)</f>
+        <v/>
+      </c>
+      <c r="D132">
+        <f>IF(C132=0,"",MEDIAN(Datos!E132:M132))</f>
+        <v/>
+      </c>
+      <c r="E132">
+        <f>COUNT(Datos!W132:AE132)</f>
+        <v/>
+      </c>
+      <c r="F132">
+        <f>IF(OR(B132="",D132=""),"",B132-D132)</f>
+        <v/>
+      </c>
+      <c r="G132">
+        <f>IF(Datos!D132="","",Datos!D132)</f>
+        <v/>
+      </c>
+      <c r="H132">
+        <f>COUNT(Datos!N132:V132)</f>
+        <v/>
+      </c>
+      <c r="I132">
+        <f>IF(B132="",IF(C132&gt;=5,"falta en SV",""),IF(G132="",IF(B132&gt;8,IF(C132&gt;=5,"SV tarde","despues del tramo"),IF(H132&gt;=5,"no retomado en 2-8","previo")),IF(B132&lt;2,"retomado",IF(AND(C132&lt;=1,E132&gt;=3),"solo especializacion",IF(F132="","coherente",IF(F132&lt;=-1.5,"SV adelantado",IF(F132&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J132">
+        <f>Datos!B132</f>
         <v/>
       </c>
     </row>
@@ -11918,7 +14113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -11943,7 +14138,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B126,A2)</f>
+        <f>COUNTIF(Datos!B2:B132,A2)</f>
         <v/>
       </c>
     </row>
@@ -11954,7 +14149,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B126,A3)</f>
+        <f>COUNTIF(Datos!B2:B132,A3)</f>
         <v/>
       </c>
     </row>
@@ -11965,7 +14160,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B126,A4)</f>
+        <f>COUNTIF(Datos!B2:B132,A4)</f>
         <v/>
       </c>
     </row>
@@ -11976,7 +14171,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B126,A5)</f>
+        <f>COUNTIF(Datos!B2:B132,A5)</f>
         <v/>
       </c>
     </row>
@@ -11987,7 +14182,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B126,A6)</f>
+        <f>COUNTIF(Datos!B2:B132,A6)</f>
         <v/>
       </c>
     </row>
@@ -11998,18 +14193,29 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B126,A7)</f>
+        <f>COUNTIF(Datos!B2:B132,A7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(Datos!B2:B132,A8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8">
-        <f>SUM(B2:B7)</f>
+      <c r="B9">
+        <f>SUM(B2:B8)</f>
         <v/>
       </c>
     </row>

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,9 +1345,6 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
@@ -1359,20 +1356,14 @@
       <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
       <c r="M12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1383,9 +1374,6 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
@@ -1400,7 +1388,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1412,7 +1400,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1426,29 +1414,32 @@
       <c r="D13" t="n">
         <v>2</v>
       </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
       </c>
       <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
         <v>4.5</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.5</v>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1459,9 +1450,6 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
@@ -1472,9 +1460,6 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
@@ -1494,37 +1479,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1532,6 +1526,9 @@
       <c r="Q14" t="n">
         <v>1</v>
       </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
@@ -1544,66 +1541,51 @@
       <c r="V14" t="n">
         <v>1</v>
       </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
         <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1614,30 +1596,15 @@
       <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -1649,74 +1616,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>6</v>
-      </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -1728,49 +1689,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J17" t="n">
         <v>7</v>
       </c>
-      <c r="K17" t="n">
-        <v>5</v>
-      </c>
       <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1778,47 +1721,35 @@
       <c r="P17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1827,46 +1758,28 @@
       <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8</v>
-      </c>
       <c r="G18" t="n">
         <v>6</v>
       </c>
       <c r="H18" t="n">
         <v>7</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K18" t="n">
         <v>8</v>
       </c>
-      <c r="J18" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
@@ -1886,7 +1799,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -1898,28 +1811,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -1928,13 +1844,16 @@
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1961,11 +1880,11 @@
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -1977,7 +1896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1986,41 +1905,35 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
         <v>6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8</v>
       </c>
       <c r="H20" t="n">
         <v>7</v>
       </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
       <c r="J20" t="n">
         <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
         <v>7</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
@@ -2034,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -2050,7 +1963,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Calor latente</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2068,22 +1981,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -2094,36 +1995,24 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2132,30 +2021,45 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
-      <c r="I22" t="n">
-        <v>5</v>
+      <c r="H22" t="n">
+        <v>2</v>
       </c>
       <c r="J22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
         <v>7</v>
       </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.5</v>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
@@ -2164,27 +2068,30 @@
       <c r="T22" t="n">
         <v>1</v>
       </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2272,7 +2179,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fricción y resistencia del aire</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,65 +2188,65 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
         <v>5</v>
       </c>
-      <c r="L24" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>10</v>
-      </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -2351,7 +2258,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2360,59 +2267,53 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
       </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
       <c r="L25" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
         <v>6</v>
       </c>
-      <c r="M25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>5</v>
-      </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -2424,7 +2325,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2433,41 +2334,35 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
         <v>2.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2493,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2509,7 +2404,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2518,28 +2413,34 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
         <v>5</v>
       </c>
-      <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>6</v>
+      <c r="F27" t="n">
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5</v>
       </c>
       <c r="M27" t="n">
         <v>2.5</v>
@@ -2547,6 +2448,9 @@
       <c r="N27" t="n">
         <v>1</v>
       </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
@@ -2562,11 +2466,14 @@
       <c r="T27" t="n">
         <v>1</v>
       </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
       <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2582,7 +2489,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2591,7 +2498,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
@@ -2599,14 +2512,26 @@
       <c r="G28" t="n">
         <v>6</v>
       </c>
+      <c r="H28" t="n">
+        <v>7</v>
+      </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
         <v>7</v>
       </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2614,33 +2539,42 @@
       <c r="P28" t="n">
         <v>1</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2649,36 +2583,36 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" t="n">
         <v>3</v>
       </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
         <v>7</v>
       </c>
-      <c r="J29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>1</v>
       </c>
       <c r="P29" t="n">
@@ -2703,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2719,7 +2653,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2728,38 +2662,35 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
@@ -2769,6 +2700,9 @@
       <c r="S30" t="n">
         <v>1</v>
       </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
       <c r="U30" t="n">
         <v>1</v>
       </c>
@@ -2776,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2792,7 +2726,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2801,25 +2735,31 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
         <v>8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" t="n">
-        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2830,17 +2770,20 @@
       <c r="Q31" t="n">
         <v>1</v>
       </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1</v>
-      </c>
       <c r="AF31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2856,7 +2799,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2868,28 +2811,37 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
+      <c r="L32" t="n">
+        <v>4</v>
+      </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2909,15 +2861,21 @@
       <c r="T32" t="n">
         <v>1</v>
       </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
       <c r="AF32" t="n">
         <v>2</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -2929,7 +2887,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2943,23 +2901,26 @@
       <c r="D33" t="n">
         <v>3</v>
       </c>
+      <c r="F33" t="n">
+        <v>8</v>
+      </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2967,9 +2928,6 @@
       <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
@@ -2980,23 +2938,23 @@
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3005,44 +2963,29 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
         <v>4.5</v>
       </c>
-      <c r="K34" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
@@ -3052,30 +2995,27 @@
       <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3093,17 +3033,23 @@
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>2.5</v>
       </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
       <c r="L35" t="n">
         <v>4</v>
       </c>
@@ -3122,13 +3068,22 @@
       <c r="Q35" t="n">
         <v>1</v>
       </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
       <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1</v>
       </c>
       <c r="AF35" t="n">
@@ -3148,7 +3103,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3157,37 +3112,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
-      </c>
-      <c r="I36" t="n">
         <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
@@ -3201,9 +3153,6 @@
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
@@ -3216,27 +3165,24 @@
       <c r="V36" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" t="n">
-        <v>1</v>
-      </c>
       <c r="AF36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3245,19 +3191,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -3265,11 +3223,23 @@
       <c r="P37" t="n">
         <v>1</v>
       </c>
-      <c r="T37" t="n">
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -3285,7 +3255,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3302,8 +3272,11 @@
       <c r="E38" t="n">
         <v>2</v>
       </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
@@ -3312,17 +3285,23 @@
         <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
         <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
@@ -3336,6 +3315,9 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="n">
@@ -3358,7 +3340,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3372,28 +3354,28 @@
       <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="F39" t="n">
-        <v>8</v>
+      <c r="E39" t="n">
+        <v>6</v>
       </c>
       <c r="G39" t="n">
         <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I39" t="n">
         <v>8</v>
       </c>
       <c r="J39" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
         <v>2.5</v>
       </c>
-      <c r="O39" t="n">
+      <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="P39" t="n">
@@ -3415,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3431,7 +3413,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3440,10 +3422,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
-      </c>
-      <c r="D40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
         <v>8</v>
@@ -3451,20 +3430,14 @@
       <c r="G40" t="n">
         <v>6</v>
       </c>
-      <c r="H40" t="n">
-        <v>4</v>
-      </c>
       <c r="I40" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" t="n">
-        <v>7.5</v>
+        <v>7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7</v>
       </c>
       <c r="M40" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3472,30 +3445,21 @@
       <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
-      <c r="Z40" t="n">
-        <v>1</v>
-      </c>
       <c r="AF40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3507,7 +3471,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3516,30 +3480,36 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
-      </c>
-      <c r="F41" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
         <v>7</v>
       </c>
+      <c r="J41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
       <c r="L41" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
         <v>2.5</v>
       </c>
-      <c r="O41" t="n">
+      <c r="N41" t="n">
         <v>1</v>
       </c>
       <c r="P41" t="n">
@@ -3551,6 +3521,12 @@
       <c r="R41" t="n">
         <v>1</v>
       </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
@@ -3558,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -3574,7 +3550,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3583,10 +3559,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
@@ -3595,22 +3571,16 @@
         <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L42" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3621,27 +3591,21 @@
       <c r="Q42" t="n">
         <v>1</v>
       </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -3653,7 +3617,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3662,13 +3626,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -3683,20 +3644,14 @@
         <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L43" t="n">
         <v>3</v>
-      </c>
-      <c r="L43" t="n">
-        <v>4</v>
       </c>
       <c r="M43" t="n">
         <v>2.5</v>
       </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
@@ -3712,9 +3667,6 @@
       <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
@@ -3722,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3738,7 +3690,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Magnitudes escalares y vectoriales</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3747,44 +3699,26 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
-      </c>
-      <c r="L44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
       </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
@@ -3794,24 +3728,18 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="n">
-        <v>1</v>
-      </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -3823,7 +3751,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3832,13 +3760,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -3849,44 +3774,32 @@
       <c r="H45" t="n">
         <v>7</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
         <v>8</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>5</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3902,7 +3815,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3911,22 +3824,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
         <v>5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" t="n">
-        <v>6</v>
       </c>
       <c r="J46" t="n">
         <v>2.5</v>
@@ -3935,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3959,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3975,7 +3888,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3984,16 +3897,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
@@ -4007,18 +3914,12 @@
       <c r="J47" t="n">
         <v>2.5</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>3</v>
       </c>
       <c r="M47" t="n">
         <v>2.5</v>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
@@ -4031,14 +3932,14 @@
       <c r="S47" t="n">
         <v>1</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>1</v>
       </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -4054,7 +3955,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4068,9 +3969,6 @@
       <c r="D48" t="n">
         <v>2</v>
       </c>
-      <c r="F48" t="n">
-        <v>5</v>
-      </c>
       <c r="G48" t="n">
         <v>2</v>
       </c>
@@ -4078,19 +3976,13 @@
         <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
         <v>3</v>
       </c>
-      <c r="M48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
+      <c r="L48" t="n">
+        <v>3</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -4101,13 +3993,10 @@
       <c r="R48" t="n">
         <v>1</v>
       </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
-      <c r="V48" t="n">
+      <c r="U48" t="n">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
@@ -4118,7 +4007,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -4130,7 +4019,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4139,10 +4028,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>8</v>
@@ -4150,20 +4039,23 @@
       <c r="G49" t="n">
         <v>6</v>
       </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -4171,6 +4063,9 @@
       <c r="P49" t="n">
         <v>1</v>
       </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
       <c r="R49" t="n">
         <v>1</v>
       </c>
@@ -4187,152 +4082,221 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Aplicaciones de las leyes de Newton</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L50" t="n">
         <v>4</v>
       </c>
-      <c r="D50" t="n">
-        <v>4</v>
+      <c r="M50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Observación astronómica en distintas longitudes de onda</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>7</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4</v>
+      </c>
+      <c r="L51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F52" t="n">
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" t="n">
-        <v>7</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K52" t="n">
         <v>4</v>
       </c>
-      <c r="M52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="n">
+      <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -4344,21 +4308,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Calor latente</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
-      </c>
-      <c r="F53" t="n">
         <v>8</v>
       </c>
       <c r="G53" t="n">
@@ -4367,8 +4328,8 @@
       <c r="H53" t="n">
         <v>7</v>
       </c>
-      <c r="O53" t="n">
-        <v>1</v>
+      <c r="J53" t="n">
+        <v>7</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4376,29 +4337,32 @@
       <c r="Q53" t="n">
         <v>1</v>
       </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
       <c r="AF53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4410,23 +4374,20 @@
       <c r="E54" t="n">
         <v>2</v>
       </c>
-      <c r="F54" t="n">
-        <v>8</v>
-      </c>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
         <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>4.5</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
-      </c>
-      <c r="L54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
         <v>7</v>
@@ -4434,72 +4395,75 @@
       <c r="N54" t="n">
         <v>1</v>
       </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
       <c r="S54" t="n">
         <v>1</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
       <c r="V54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Campo eléctrico</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
-      </c>
-      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
         <v>8</v>
       </c>
       <c r="G55" t="n">
         <v>6</v>
       </c>
-      <c r="O55" t="n">
+      <c r="M55" t="n">
+        <v>7</v>
+      </c>
+      <c r="N55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
       <c r="AF55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4508,19 +4472,19 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4529,32 +4493,26 @@
       <c r="D56" t="n">
         <v>5</v>
       </c>
-      <c r="E56" t="n">
-        <v>3</v>
-      </c>
       <c r="F56" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
         <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J56" t="n">
         <v>4.5</v>
       </c>
-      <c r="L56" t="n">
-        <v>3</v>
+      <c r="K56" t="n">
+        <v>7</v>
       </c>
       <c r="M56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4571,7 +4529,7 @@
       <c r="S56" t="n">
         <v>1</v>
       </c>
-      <c r="U56" t="n">
+      <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
@@ -4587,69 +4545,51 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
         <v>8.5</v>
       </c>
-      <c r="H57" t="n">
-        <v>7</v>
-      </c>
-      <c r="J57" t="n">
-        <v>7</v>
-      </c>
-      <c r="L57" t="n">
-        <v>4</v>
+      <c r="I57" t="n">
+        <v>8</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
       </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
+      <c r="R57" t="n">
         <v>1</v>
       </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -4661,307 +4601,553 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Capacitancia y condensadores</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2</v>
-      </c>
-      <c r="T59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Colisiones elásticas e inelásticas</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="n">
         <v>8</v>
       </c>
-      <c r="D60" t="n">
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" t="n">
         <v>8</v>
       </c>
-      <c r="G60" t="n">
-        <v>8.5</v>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
+      <c r="K60" t="n">
+        <v>7</v>
+      </c>
+      <c r="L60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
       </c>
       <c r="P60" t="n">
         <v>1</v>
       </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
       <c r="AF60" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4</v>
-      </c>
-      <c r="J61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="K61" t="n">
         <v>7</v>
       </c>
-      <c r="K61" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
+      <c r="M61" t="n">
+        <v>7</v>
+      </c>
+      <c r="O61" t="n">
         <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
       <c r="AF61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cuantización de la energía</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3</v>
+      </c>
+      <c r="L62" t="n">
+        <v>4</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="n">
         <v>8</v>
       </c>
-      <c r="D63" t="n">
+      <c r="G63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" t="n">
         <v>8</v>
       </c>
+      <c r="J63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
       <c r="AF63" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>4.5</v>
       </c>
       <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" t="n">
         <v>4</v>
       </c>
       <c r="M64" t="n">
         <v>2.5</v>
       </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
       <c r="P64" t="n">
         <v>1</v>
       </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
       <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>7</v>
+      </c>
+      <c r="I65" t="n">
         <v>8</v>
       </c>
-      <c r="G65" t="n">
-        <v>2</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" t="n">
-        <v>2</v>
-      </c>
       <c r="J65" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K65" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" t="n">
         <v>4</v>
       </c>
       <c r="M65" t="n">
@@ -4988,21 +5174,15 @@
       <c r="T65" t="n">
         <v>1</v>
       </c>
-      <c r="U65" t="n">
-        <v>1</v>
-      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
-      <c r="Z65" t="n">
-        <v>1</v>
-      </c>
       <c r="AF65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
@@ -5014,137 +5194,164 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K66" t="n">
         <v>3</v>
       </c>
-      <c r="D66" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" t="n">
-        <v>6</v>
-      </c>
-      <c r="H66" t="n">
-        <v>7</v>
-      </c>
-      <c r="J66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
         <v>4</v>
       </c>
-      <c r="M66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>9</v>
-      </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Espejos esféricos</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>8</v>
       </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>7</v>
-      </c>
-      <c r="L67" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
       <c r="S67" t="n">
         <v>1</v>
       </c>
-      <c r="U67" t="n">
+      <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="V67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5154,22 +5361,22 @@
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>2</v>
       </c>
-      <c r="K68" t="n">
-        <v>7</v>
+      <c r="J68" t="n">
+        <v>4.5</v>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -5180,7 +5387,7 @@
       <c r="Q68" t="n">
         <v>1</v>
       </c>
-      <c r="T68" t="n">
+      <c r="S68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
@@ -5189,54 +5396,60 @@
       <c r="V68" t="n">
         <v>1</v>
       </c>
+      <c r="Z68" t="n">
+        <v>1</v>
+      </c>
       <c r="AF68" t="n">
         <v>2</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="n">
         <v>5</v>
       </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="F69" t="n">
-        <v>8</v>
-      </c>
       <c r="G69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M69" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
@@ -5247,6 +5460,9 @@
       <c r="Q69" t="n">
         <v>1</v>
       </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
       <c r="S69" t="n">
         <v>1</v>
       </c>
@@ -5256,12 +5472,15 @@
       <c r="V69" t="n">
         <v>1</v>
       </c>
+      <c r="Z69" t="n">
+        <v>1</v>
+      </c>
       <c r="AF69" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
@@ -5273,34 +5492,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
-      </c>
-      <c r="F70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
         <v>6</v>
       </c>
       <c r="H70" t="n">
-        <v>7</v>
-      </c>
-      <c r="J70" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>6</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2.5</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -5308,11 +5527,17 @@
       <c r="Q70" t="n">
         <v>1</v>
       </c>
-      <c r="S70" t="n">
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
         <v>1</v>
       </c>
       <c r="AF70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5328,49 +5553,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Gravedad: atracción hacia la Tierra</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J71" t="n">
         <v>7</v>
       </c>
       <c r="K71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L71" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -5378,9 +5594,6 @@
       <c r="P71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>1</v>
-      </c>
       <c r="R71" t="n">
         <v>1</v>
       </c>
@@ -5397,28 +5610,28 @@
         <v>1</v>
       </c>
       <c r="AF71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Inducción electromagnética: Faraday y Lenz</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -5431,11 +5644,20 @@
         <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>8.5</v>
+        <v>3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
       </c>
       <c r="I72" t="n">
         <v>5</v>
       </c>
+      <c r="J72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3</v>
+      </c>
       <c r="M72" t="n">
         <v>7</v>
       </c>
@@ -5445,30 +5667,39 @@
       <c r="P72" t="n">
         <v>1</v>
       </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
       <c r="R72" t="n">
         <v>1</v>
       </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
       <c r="V72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Magnitudes escalares y vectoriales</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5477,26 +5708,41 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="n">
+        <v>8</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
-      </c>
-      <c r="K73" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4</v>
       </c>
       <c r="M73" t="n">
         <v>2.5</v>
       </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
@@ -5506,14 +5752,17 @@
       <c r="R73" t="n">
         <v>1</v>
       </c>
-      <c r="T73" t="n">
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
         <v>1</v>
       </c>
       <c r="V73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -5529,7 +5778,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Masa y peso</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5542,58 +5791,22 @@
       </c>
       <c r="D74" t="n">
         <v>2</v>
-      </c>
-      <c r="E74" t="n">
-        <v>2</v>
-      </c>
-      <c r="F74" t="n">
-        <v>2.5</v>
       </c>
       <c r="G74" t="n">
         <v>6</v>
       </c>
-      <c r="H74" t="n">
-        <v>2</v>
-      </c>
-      <c r="I74" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K74" t="n">
-        <v>5</v>
-      </c>
-      <c r="L74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
         <v>2.5</v>
       </c>
-      <c r="N74" t="n">
-        <v>1</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1</v>
-      </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>1</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
-      <c r="S74" t="n">
-        <v>1</v>
-      </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
-      <c r="U74" t="n">
-        <v>1</v>
-      </c>
       <c r="V74" t="n">
         <v>1</v>
       </c>
@@ -5602,19 +5815,19 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5623,25 +5836,43 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
         <v>2</v>
       </c>
       <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
         <v>6</v>
       </c>
-      <c r="K75" t="n">
-        <v>3</v>
-      </c>
-      <c r="L75" t="n">
-        <v>3</v>
+      <c r="M75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -5652,17 +5883,20 @@
       <c r="R75" t="n">
         <v>1</v>
       </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
         <v>1</v>
       </c>
-      <c r="Z75" t="n">
+      <c r="V75" t="n">
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -5671,14 +5905,14 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Modelo estándar de partículas</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5687,13 +5921,31 @@
         </is>
       </c>
       <c r="C76" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" t="n">
+        <v>8</v>
+      </c>
+      <c r="F76" t="n">
+        <v>8</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" t="n">
         <v>7</v>
       </c>
-      <c r="D76" t="n">
-        <v>7</v>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -5702,14 +5954,14 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Movimiento circular y variables angulares</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5724,10 +5976,10 @@
         <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K77" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4</v>
       </c>
       <c r="M77" t="n">
         <v>7</v>
@@ -5735,7 +5987,7 @@
       <c r="P77" t="n">
         <v>1</v>
       </c>
-      <c r="T77" t="n">
+      <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="V77" t="n">
@@ -5746,52 +5998,34 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Aplicaciones de las leyes de Newton</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
-      </c>
-      <c r="G78" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" t="n">
-        <v>7</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
@@ -5800,19 +6034,19 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Niveles de energía atómicos y espectros</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -5821,14 +6055,8 @@
       <c r="D79" t="n">
         <v>5</v>
       </c>
-      <c r="G79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
       <c r="AF79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -5844,19 +6072,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>El ojo y los instrumentos ópticos</t>
+          <t>Campo eléctrico</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F80" t="n">
         <v>8</v>
@@ -5864,123 +6092,66 @@
       <c r="G80" t="n">
         <v>6</v>
       </c>
-      <c r="H80" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K80" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>1</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
-      <c r="V80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1</v>
-      </c>
       <c r="AF80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro</t>
+          <t>Capacitancia y condensadores</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
-      </c>
-      <c r="F81" t="n">
-        <v>8</v>
-      </c>
-      <c r="G81" t="n">
-        <v>6</v>
-      </c>
-      <c r="H81" t="n">
-        <v>7</v>
-      </c>
-      <c r="L81" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M81" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>5</v>
       </c>
       <c r="AF81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
           <t>posterior</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -5989,26 +6160,14 @@
       <c r="D82" t="n">
         <v>2</v>
       </c>
-      <c r="E82" t="n">
-        <v>8</v>
-      </c>
-      <c r="G82" t="n">
-        <v>6</v>
-      </c>
-      <c r="M82" t="n">
-        <v>7</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="n">
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="T82" t="n">
         <v>1</v>
       </c>
       <c r="AF82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6017,33 +6176,48 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Órbitas y satélites</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
-      </c>
-      <c r="D83" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I83" t="n">
+        <v>7</v>
+      </c>
+      <c r="M83" t="n">
+        <v>7</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1</v>
       </c>
       <c r="AF83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -6055,40 +6229,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Cuantización de la energía</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>8</v>
-      </c>
-      <c r="F84" t="n">
-        <v>8</v>
-      </c>
-      <c r="I84" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" t="n">
         <v>7</v>
       </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
-      <c r="S84" t="n">
-        <v>1</v>
-      </c>
       <c r="AF84" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6097,50 +6253,35 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Desintegración radiactiva</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>8</v>
       </c>
       <c r="F85" t="n">
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
-      </c>
-      <c r="H85" t="n">
-        <v>5</v>
-      </c>
-      <c r="I85" t="n">
-        <v>5</v>
-      </c>
-      <c r="J85" t="n">
-        <v>7</v>
-      </c>
-      <c r="K85" t="n">
-        <v>5</v>
-      </c>
-      <c r="L85" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M85" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -6148,99 +6289,63 @@
       <c r="P85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>1</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1</v>
-      </c>
-      <c r="S85" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" t="n">
-        <v>1</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>1</v>
-      </c>
       <c r="AF85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
-      </c>
-      <c r="D86" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
         <v>8</v>
       </c>
-      <c r="M86" t="n">
-        <v>7</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1</v>
-      </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" t="n">
+      <c r="N86" t="n">
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Energía potencial y potencial eléctrico</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -6249,18 +6354,6 @@
       <c r="D87" t="n">
         <v>8</v>
       </c>
-      <c r="G87" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H87" t="n">
-        <v>7</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>1</v>
-      </c>
       <c r="AF87" t="n">
         <v>11</v>
       </c>
@@ -6278,98 +6371,62 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Defecto de masa y energía de enlace nuclear</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
-      </c>
-      <c r="D88" t="n">
-        <v>5</v>
-      </c>
-      <c r="E88" t="n">
-        <v>6</v>
-      </c>
-      <c r="G88" t="n">
-        <v>6</v>
-      </c>
-      <c r="H88" t="n">
-        <v>7</v>
-      </c>
-      <c r="I88" t="n">
+        <v>11</v>
+      </c>
+      <c r="F88" t="n">
         <v>8</v>
       </c>
-      <c r="J88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K88" t="n">
-        <v>5</v>
-      </c>
-      <c r="M88" t="n">
-        <v>7</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="P88" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="S88" t="n">
-        <v>1</v>
-      </c>
-      <c r="T88" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" t="n">
+      <c r="O88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Espejos esféricos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
-      </c>
-      <c r="D89" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
-      <c r="K89" t="n">
+      <c r="H89" t="n">
+        <v>5</v>
+      </c>
+      <c r="J89" t="n">
         <v>7</v>
+      </c>
+      <c r="L89" t="n">
+        <v>7.5</v>
       </c>
       <c r="M89" t="n">
         <v>7</v>
@@ -6377,120 +6434,102 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="T89" t="n">
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
         <v>1</v>
       </c>
       <c r="V89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Fisión y fusión nuclear</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
-      <c r="G90" t="n">
-        <v>6</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2</v>
-      </c>
-      <c r="I90" t="n">
-        <v>8</v>
-      </c>
-      <c r="J90" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3</v>
+      <c r="L90" t="n">
+        <v>7.5</v>
       </c>
       <c r="M90" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="P90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>1</v>
-      </c>
-      <c r="R90" t="n">
-        <v>1</v>
-      </c>
-      <c r="S90" t="n">
-        <v>1</v>
-      </c>
-      <c r="T90" t="n">
+      <c r="U90" t="n">
         <v>1</v>
       </c>
       <c r="V90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Reflexión interna total</t>
+          <t>Fotón y efecto fotoeléctrico</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="n">
         <v>8</v>
       </c>
-      <c r="D91" t="n">
-        <v>8</v>
-      </c>
-      <c r="H91" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q91" t="n">
+      <c r="G91" t="n">
+        <v>6</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
@@ -6498,7 +6537,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
@@ -6510,21 +6549,18 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>Inducción electromagnética: Faraday y Lenz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
-      </c>
-      <c r="E92" t="n">
         <v>4</v>
       </c>
       <c r="F92" t="n">
@@ -6533,26 +6569,11 @@
       <c r="G92" t="n">
         <v>8.5</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>5</v>
       </c>
-      <c r="I92" t="n">
-        <v>6</v>
-      </c>
-      <c r="J92" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K92" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M92" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -6560,145 +6581,106 @@
       <c r="P92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>1</v>
-      </c>
       <c r="R92" t="n">
         <v>1</v>
       </c>
-      <c r="S92" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" t="n">
-        <v>1</v>
-      </c>
-      <c r="U92" t="n">
-        <v>1</v>
-      </c>
       <c r="V92" t="n">
         <v>1</v>
       </c>
-      <c r="Z92" t="n">
-        <v>1</v>
-      </c>
       <c r="AF92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Ley de Coulomb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H93" t="n">
+        <v>6</v>
+      </c>
+      <c r="I93" t="n">
         <v>7</v>
       </c>
-      <c r="I93" t="n">
-        <v>3</v>
-      </c>
-      <c r="K93" t="n">
+      <c r="J93" t="n">
         <v>7</v>
       </c>
       <c r="M93" t="n">
         <v>7</v>
       </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
       <c r="P93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>1</v>
-      </c>
       <c r="R93" t="n">
         <v>1</v>
       </c>
-      <c r="T93" t="n">
+      <c r="S93" t="n">
         <v>1</v>
       </c>
       <c r="V93" t="n">
         <v>1</v>
       </c>
-      <c r="Z93" t="n">
-        <v>1</v>
-      </c>
       <c r="AF93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Leyes de Kepler</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
-      </c>
-      <c r="F94" t="n">
-        <v>8</v>
-      </c>
-      <c r="G94" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J94" t="n">
-        <v>7</v>
-      </c>
-      <c r="L94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
-      <c r="S94" t="n">
-        <v>1</v>
-      </c>
-      <c r="U94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF94" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -6707,39 +6689,42 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Segunda ley de la termodinámica</t>
+          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
-      </c>
-      <c r="D95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G95" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I95" t="n">
+        <v>7</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
       <c r="AF95" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
@@ -6751,160 +6736,103 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Modelo estándar de partículas</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
-      </c>
-      <c r="G96" t="n">
-        <v>6</v>
-      </c>
-      <c r="H96" t="n">
         <v>7</v>
       </c>
-      <c r="J96" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K96" t="n">
-        <v>8</v>
-      </c>
-      <c r="L96" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M96" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>1</v>
-      </c>
-      <c r="S96" t="n">
-        <v>1</v>
-      </c>
-      <c r="T96" t="n">
-        <v>1</v>
-      </c>
-      <c r="U96" t="n">
-        <v>1</v>
-      </c>
-      <c r="V96" t="n">
-        <v>1</v>
-      </c>
       <c r="AF96" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Núcleo atómico e isótopos</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
-      </c>
-      <c r="D97" t="n">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F97" t="n">
+        <v>8</v>
       </c>
       <c r="G97" t="n">
-        <v>6</v>
-      </c>
-      <c r="H97" t="n">
-        <v>7</v>
-      </c>
-      <c r="I97" t="n">
-        <v>8</v>
-      </c>
-      <c r="J97" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
       </c>
       <c r="P97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>1</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1</v>
-      </c>
-      <c r="S97" t="n">
-        <v>1</v>
-      </c>
       <c r="AF97" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Ondas electromagnéticas y espectro</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D98" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" t="n">
+        <v>7</v>
+      </c>
+      <c r="L98" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M98" t="n">
         <v>4.5</v>
       </c>
-      <c r="L98" t="n">
-        <v>4</v>
-      </c>
-      <c r="M98" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O98" t="n">
         <v>1</v>
       </c>
@@ -6914,9 +6842,6 @@
       <c r="Q98" t="n">
         <v>1</v>
       </c>
-      <c r="S98" t="n">
-        <v>1</v>
-      </c>
       <c r="U98" t="n">
         <v>1</v>
       </c>
@@ -6927,45 +6852,39 @@
         <v>1</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H99" t="n">
         <v>7</v>
       </c>
-      <c r="J99" t="n">
-        <v>2.5</v>
-      </c>
       <c r="M99" t="n">
         <v>4.5</v>
       </c>
@@ -6975,18 +6894,18 @@
       <c r="Q99" t="n">
         <v>1</v>
       </c>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
       <c r="V99" t="n">
         <v>1</v>
       </c>
+      <c r="Z99" t="n">
+        <v>1</v>
+      </c>
       <c r="AF99" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
@@ -6998,27 +6917,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Energía potencial y potencial eléctrico</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H100" t="n">
-        <v>4</v>
-      </c>
-      <c r="M100" t="n">
         <v>7</v>
       </c>
       <c r="P100" t="n">
@@ -7027,54 +6943,48 @@
       <c r="Q100" t="n">
         <v>1</v>
       </c>
-      <c r="V100" t="n">
-        <v>1</v>
-      </c>
       <c r="AF100" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
-      </c>
-      <c r="D101" t="n">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
-      </c>
-      <c r="I101" t="n">
-        <v>5</v>
-      </c>
-      <c r="K101" t="n">
-        <v>6</v>
-      </c>
-      <c r="M101" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="L101" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
@@ -7082,88 +6992,55 @@
       <c r="Q101" t="n">
         <v>1</v>
       </c>
-      <c r="R101" t="n">
-        <v>1</v>
-      </c>
-      <c r="T101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z101" t="n">
         <v>1</v>
       </c>
       <c r="AF101" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Radiación térmica y cuerpo negro</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" t="n">
-        <v>5</v>
-      </c>
-      <c r="F102" t="n">
-        <v>5</v>
-      </c>
-      <c r="G102" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
-      </c>
-      <c r="I102" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J102" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L102" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M102" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N102" t="n">
-        <v>1</v>
-      </c>
-      <c r="O102" t="n">
-        <v>1</v>
-      </c>
-      <c r="P102" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="Q102" t="n">
         <v>1</v>
       </c>
-      <c r="R102" t="n">
-        <v>1</v>
-      </c>
       <c r="S102" t="n">
         <v>1</v>
       </c>
@@ -7173,100 +7050,79 @@
       <c r="U102" t="n">
         <v>1</v>
       </c>
-      <c r="V102" t="n">
-        <v>1</v>
-      </c>
       <c r="AF102" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Rapidez de la luz</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
-      </c>
-      <c r="D103" t="n">
-        <v>4</v>
-      </c>
-      <c r="F103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
-      </c>
-      <c r="I103" t="n">
-        <v>5</v>
-      </c>
-      <c r="J103" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K103" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="L103" t="n">
+        <v>7.5</v>
       </c>
       <c r="M103" t="n">
         <v>7</v>
       </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
       <c r="P103" t="n">
         <v>1</v>
       </c>
       <c r="Q103" t="n">
         <v>1</v>
       </c>
-      <c r="R103" t="n">
-        <v>1</v>
-      </c>
-      <c r="S103" t="n">
-        <v>1</v>
-      </c>
-      <c r="T103" t="n">
+      <c r="U103" t="n">
         <v>1</v>
       </c>
       <c r="V103" t="n">
         <v>1</v>
       </c>
+      <c r="Z103" t="n">
+        <v>1</v>
+      </c>
       <c r="AF103" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Reflexión interna total</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7275,32 +7131,23 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
-      </c>
-      <c r="G104" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I104" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" t="n">
+        <v>8</v>
+      </c>
+      <c r="H104" t="n">
         <v>7</v>
       </c>
-      <c r="M104" t="n">
-        <v>7</v>
-      </c>
-      <c r="P104" t="n">
-        <v>1</v>
-      </c>
-      <c r="R104" t="n">
-        <v>1</v>
-      </c>
-      <c r="V104" t="n">
+      <c r="Q104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
@@ -7312,7 +7159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Desintegración radiactiva</t>
+          <t>Segunda ley de la termodinámica</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7321,32 +7168,23 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
-      </c>
-      <c r="E105" t="n">
-        <v>8</v>
-      </c>
-      <c r="F105" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>5</v>
       </c>
       <c r="G105" t="n">
         <v>8.5</v>
       </c>
-      <c r="N105" t="n">
-        <v>1</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1</v>
-      </c>
       <c r="P105" t="n">
         <v>1</v>
       </c>
       <c r="AF105" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
@@ -7358,7 +7196,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Semiconductores y electrónica básica</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7367,16 +7205,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
-      </c>
-      <c r="E106" t="n">
-        <v>8</v>
-      </c>
-      <c r="N106" t="n">
+        <v>9</v>
+      </c>
+      <c r="J106" t="n">
+        <v>7</v>
+      </c>
+      <c r="S106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
@@ -7392,7 +7230,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Defecto de masa y energía de enlace nuclear</t>
+          <t>Superposición e interferencia de ondas</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7401,12 +7239,12 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
-      </c>
-      <c r="F107" t="n">
-        <v>8</v>
-      </c>
-      <c r="O107" t="n">
+        <v>10</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6</v>
+      </c>
+      <c r="P107" t="n">
         <v>1</v>
       </c>
       <c r="AF107" t="n">
@@ -7426,7 +7264,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Fisión y fusión nuclear</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7435,32 +7273,41 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
-      </c>
-      <c r="F108" t="n">
         <v>8</v>
       </c>
-      <c r="L108" t="n">
-        <v>7.5</v>
+      <c r="D108" t="n">
+        <v>8</v>
+      </c>
+      <c r="G108" t="n">
+        <v>6</v>
+      </c>
+      <c r="H108" t="n">
+        <v>7</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2.5</v>
       </c>
       <c r="M108" t="n">
-        <v>7</v>
-      </c>
-      <c r="O108" t="n">
-        <v>1</v>
-      </c>
-      <c r="U108" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
         <v>1</v>
       </c>
       <c r="V108" t="n">
         <v>1</v>
       </c>
       <c r="AF108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
@@ -7472,7 +7319,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Fotón y efecto fotoeléctrico</t>
+          <t>Viscosidad y régimen de flujo</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7481,22 +7328,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
-      </c>
-      <c r="E109" t="n">
-        <v>8</v>
-      </c>
-      <c r="G109" t="n">
-        <v>6</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1</v>
-      </c>
-      <c r="P109" t="n">
+        <v>9</v>
+      </c>
+      <c r="K109" t="n">
+        <v>7</v>
+      </c>
+      <c r="T109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
@@ -7512,52 +7353,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ley de Coulomb</t>
+          <t>Aceleración y fuerza centrípeta</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
-      </c>
-      <c r="F110" t="n">
-        <v>8</v>
-      </c>
-      <c r="G110" t="n">
-        <v>6</v>
-      </c>
-      <c r="I110" t="n">
-        <v>7</v>
-      </c>
-      <c r="J110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M110" t="n">
         <v>7</v>
       </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="R110" t="n">
-        <v>1</v>
-      </c>
-      <c r="S110" t="n">
-        <v>1</v>
-      </c>
       <c r="V110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
@@ -7566,29 +7383,35 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Leyes de Kepler</t>
+          <t>Colisiones elásticas e inelásticas</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
       </c>
       <c r="AF111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -7604,261 +7427,222 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
-      </c>
-      <c r="G112" t="n">
-        <v>6</v>
-      </c>
-      <c r="I112" t="n">
-        <v>7</v>
-      </c>
-      <c r="P112" t="n">
-        <v>1</v>
-      </c>
-      <c r="R112" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D112" t="n">
+        <v>8</v>
       </c>
       <c r="AF112" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Núcleo atómico e isótopos</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>11</v>
-      </c>
-      <c r="F113" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" t="n">
+        <v>5</v>
+      </c>
+      <c r="H113" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" t="n">
+        <v>7</v>
+      </c>
+      <c r="K113" t="n">
         <v>8</v>
       </c>
-      <c r="G113" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O113" t="n">
-        <v>1</v>
-      </c>
-      <c r="P113" t="n">
+      <c r="Q113" t="n">
+        <v>1</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="n">
         <v>1</v>
       </c>
       <c r="AF113" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ondas de radio y telecomunicaciones</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>11</v>
-      </c>
-      <c r="G114" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H114" t="n">
-        <v>7</v>
-      </c>
-      <c r="M114" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>1</v>
-      </c>
-      <c r="V114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
       </c>
       <c r="AF114" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11</v>
-      </c>
-      <c r="F115" t="n">
         <v>8</v>
       </c>
-      <c r="G115" t="n">
-        <v>8.5</v>
+      <c r="D115" t="n">
+        <v>8</v>
       </c>
       <c r="H115" t="n">
         <v>7</v>
       </c>
-      <c r="L115" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O115" t="n">
-        <v>1</v>
-      </c>
-      <c r="P115" t="n">
-        <v>1</v>
+      <c r="M115" t="n">
+        <v>7</v>
       </c>
       <c r="Q115" t="n">
         <v>1</v>
       </c>
-      <c r="U115" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z115" t="n">
+      <c r="V115" t="n">
         <v>1</v>
       </c>
       <c r="AF115" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Radiación térmica y cuerpo negro</t>
+          <t>Movimiento armónico simple</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>10</v>
-      </c>
-      <c r="H116" t="n">
-        <v>7</v>
-      </c>
-      <c r="J116" t="n">
-        <v>7</v>
-      </c>
-      <c r="K116" t="n">
-        <v>6</v>
-      </c>
-      <c r="L116" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>1</v>
-      </c>
-      <c r="S116" t="n">
-        <v>1</v>
-      </c>
-      <c r="T116" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8</v>
+      </c>
+      <c r="I116" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="R116" t="n">
         <v>1</v>
       </c>
       <c r="AF116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Rapidez de la luz</t>
+          <t>Movimiento circular y variables angulares</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D117" t="n">
+        <v>5</v>
       </c>
       <c r="G117" t="n">
-        <v>6</v>
-      </c>
-      <c r="H117" t="n">
-        <v>7</v>
-      </c>
-      <c r="L117" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3</v>
       </c>
       <c r="M117" t="n">
         <v>7</v>
@@ -7866,92 +7650,92 @@
       <c r="P117" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" t="n">
-        <v>1</v>
-      </c>
-      <c r="U117" t="n">
+      <c r="T117" t="n">
         <v>1</v>
       </c>
       <c r="V117" t="n">
         <v>1</v>
       </c>
-      <c r="Z117" t="n">
-        <v>1</v>
-      </c>
       <c r="AF117" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Semiconductores y electrónica básica</t>
+          <t>Cinemática en dos dimensiones y proyectiles</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>9</v>
-      </c>
-      <c r="J118" t="n">
-        <v>7</v>
-      </c>
-      <c r="S118" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" t="n">
+        <v>8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>6</v>
+      </c>
+      <c r="P118" t="n">
         <v>1</v>
       </c>
       <c r="AF118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Superposición e interferencia de ondas</t>
+          <t>Niveles de energía atómicos y espectros</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C119" t="n">
+        <v>5</v>
+      </c>
+      <c r="D119" t="n">
+        <v>5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF119" t="n">
         <v>10</v>
       </c>
-      <c r="G119" t="n">
-        <v>6</v>
-      </c>
-      <c r="P119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF119" t="n">
-        <v>11</v>
-      </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
@@ -7963,41 +7747,50 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Viscosidad y régimen de flujo</t>
+          <t>Ondas estacionarias y armónicos</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
-      </c>
-      <c r="K120" t="n">
+        <v>8</v>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+      <c r="H120" t="n">
         <v>7</v>
       </c>
-      <c r="T120" t="n">
+      <c r="M120" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="n">
         <v>1</v>
       </c>
       <c r="AF120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Aceleración y fuerza centrípeta</t>
+          <t>Órbitas y satélites</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8006,19 +7799,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D121" t="n">
-        <v>5</v>
-      </c>
-      <c r="M121" t="n">
-        <v>7</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AF121" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -8027,14 +7814,14 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Hidrodinámica: continuidad y Bernoulli</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8043,13 +7830,25 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>7</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1</v>
       </c>
       <c r="AF122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
@@ -8065,7 +7864,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8079,8 +7878,32 @@
       <c r="D123" t="n">
         <v>5</v>
       </c>
+      <c r="G123" t="n">
+        <v>6</v>
+      </c>
+      <c r="H123" t="n">
+        <v>7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>8</v>
+      </c>
+      <c r="J123" t="n">
+        <v>7</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1</v>
+      </c>
       <c r="AF123" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -8089,14 +7912,14 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8105,25 +7928,19 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D124" t="n">
-        <v>8</v>
-      </c>
-      <c r="H124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M124" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="V124" t="n">
         <v>1</v>
       </c>
       <c r="AF124" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
@@ -8139,210 +7956,354 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Movimiento armónico simple</t>
+          <t>Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D125" t="n">
-        <v>8</v>
-      </c>
-      <c r="F125" t="n">
-        <v>8</v>
-      </c>
-      <c r="I125" t="n">
-        <v>4</v>
-      </c>
-      <c r="O125" t="n">
-        <v>1</v>
-      </c>
-      <c r="R125" t="n">
+        <v>7</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L125" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M125" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" t="n">
         <v>1</v>
       </c>
       <c r="AF125" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cinemática en dos dimensiones y proyectiles</t>
+          <t>Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C126" t="n">
+        <v>10</v>
+      </c>
+      <c r="F126" t="n">
         <v>8</v>
       </c>
-      <c r="D126" t="n">
-        <v>8</v>
-      </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
+        <v>5</v>
+      </c>
+      <c r="I126" t="n">
         <v>6</v>
       </c>
-      <c r="P126" t="n">
+      <c r="J126" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
+      <c r="V126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z126" t="n">
         <v>1</v>
       </c>
       <c r="AF126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ondas estacionarias y armónicos</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C127" t="n">
+        <v>9</v>
+      </c>
+      <c r="F127" t="n">
         <v>8</v>
       </c>
-      <c r="D127" t="n">
-        <v>8</v>
+      <c r="G127" t="n">
+        <v>6</v>
       </c>
       <c r="H127" t="n">
         <v>7</v>
       </c>
+      <c r="I127" t="n">
+        <v>7</v>
+      </c>
+      <c r="J127" t="n">
+        <v>7</v>
+      </c>
+      <c r="K127" t="n">
+        <v>8</v>
+      </c>
+      <c r="L127" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M127" t="n">
         <v>7</v>
       </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
       <c r="Q127" t="n">
         <v>1</v>
       </c>
+      <c r="R127" t="n">
+        <v>1</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" t="n">
+        <v>1</v>
+      </c>
       <c r="V127" t="n">
         <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Masa y peso</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G128" t="n">
         <v>6</v>
       </c>
-      <c r="D128" t="n">
-        <v>6</v>
-      </c>
       <c r="H128" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2.5</v>
       </c>
       <c r="K128" t="n">
         <v>5</v>
       </c>
+      <c r="L128" t="n">
+        <v>6</v>
+      </c>
+      <c r="M128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
       <c r="Q128" t="n">
         <v>1</v>
       </c>
+      <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1</v>
+      </c>
       <c r="T128" t="n">
         <v>1</v>
       </c>
+      <c r="U128" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" t="n">
+        <v>1</v>
+      </c>
       <c r="AF128" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad</t>
+          <t>El ojo y los instrumentos ópticos</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C129" t="n">
+        <v>3</v>
+      </c>
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" t="n">
+        <v>8</v>
+      </c>
+      <c r="G129" t="n">
         <v>6</v>
       </c>
-      <c r="D129" t="n">
-        <v>6</v>
+      <c r="H129" t="n">
+        <v>5</v>
+      </c>
+      <c r="J129" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3</v>
       </c>
       <c r="M129" t="n">
         <v>2.5</v>
       </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
       <c r="V129" t="n">
         <v>1</v>
       </c>
+      <c r="Z129" t="n">
+        <v>1</v>
+      </c>
       <c r="AF129" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Espejos planos e imágenes</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8351,16 +8312,28 @@
         </is>
       </c>
       <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="F130" t="n">
+        <v>8</v>
+      </c>
+      <c r="G130" t="n">
+        <v>6</v>
+      </c>
+      <c r="H130" t="n">
+        <v>5</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5</v>
+      </c>
+      <c r="J130" t="n">
         <v>7</v>
       </c>
-      <c r="D130" t="n">
-        <v>7</v>
-      </c>
-      <c r="H130" t="n">
-        <v>3</v>
-      </c>
-      <c r="J130" t="n">
-        <v>4.5</v>
+      <c r="K130" t="n">
+        <v>5</v>
       </c>
       <c r="L130" t="n">
         <v>7.5</v>
@@ -8368,36 +8341,51 @@
       <c r="M130" t="n">
         <v>7</v>
       </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>1</v>
+      </c>
       <c r="Q130" t="n">
         <v>1</v>
       </c>
+      <c r="R130" t="n">
+        <v>1</v>
+      </c>
       <c r="S130" t="n">
         <v>1</v>
       </c>
+      <c r="T130" t="n">
+        <v>1</v>
+      </c>
       <c r="U130" t="n">
         <v>1</v>
       </c>
       <c r="V130" t="n">
         <v>1</v>
       </c>
+      <c r="Z130" t="n">
+        <v>1</v>
+      </c>
       <c r="AF130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8406,11 +8394,20 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D131" t="n">
+        <v>7</v>
+      </c>
+      <c r="E131" t="n">
+        <v>4</v>
       </c>
       <c r="F131" t="n">
         <v>8</v>
       </c>
+      <c r="G131" t="n">
+        <v>8.5</v>
+      </c>
       <c r="H131" t="n">
         <v>5</v>
       </c>
@@ -8420,12 +8417,24 @@
       <c r="J131" t="n">
         <v>4.5</v>
       </c>
+      <c r="K131" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M131" t="n">
         <v>4.5</v>
       </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
       <c r="O131" t="n">
         <v>1</v>
       </c>
+      <c r="P131" t="n">
+        <v>1</v>
+      </c>
       <c r="Q131" t="n">
         <v>1</v>
       </c>
@@ -8435,6 +8444,12 @@
       <c r="S131" t="n">
         <v>1</v>
       </c>
+      <c r="T131" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" t="n">
+        <v>1</v>
+      </c>
       <c r="V131" t="n">
         <v>1</v>
       </c>
@@ -8442,11 +8457,11 @@
         <v>1</v>
       </c>
       <c r="AF131" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
@@ -8458,7 +8473,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,33 +8484,21 @@
       <c r="C132" t="n">
         <v>9</v>
       </c>
-      <c r="F132" t="n">
-        <v>8</v>
-      </c>
       <c r="G132" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H132" t="n">
         <v>7</v>
       </c>
       <c r="I132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="n">
         <v>7</v>
-      </c>
-      <c r="J132" t="n">
-        <v>7</v>
-      </c>
-      <c r="K132" t="n">
-        <v>8</v>
-      </c>
-      <c r="L132" t="n">
-        <v>7.5</v>
       </c>
       <c r="M132" t="n">
         <v>7</v>
       </c>
-      <c r="O132" t="n">
-        <v>1</v>
-      </c>
       <c r="P132" t="n">
         <v>1</v>
       </c>
@@ -8505,24 +8508,21 @@
       <c r="R132" t="n">
         <v>1</v>
       </c>
-      <c r="S132" t="n">
-        <v>1</v>
-      </c>
       <c r="T132" t="n">
         <v>1</v>
       </c>
-      <c r="U132" t="n">
-        <v>1</v>
-      </c>
       <c r="V132" t="n">
         <v>1</v>
       </c>
+      <c r="Z132" t="n">
+        <v>1</v>
+      </c>
       <c r="AF132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,6 +1345,9 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
@@ -1356,14 +1359,20 @@
       <c r="H12" t="n">
         <v>2</v>
       </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1374,6 +1383,9 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
@@ -1388,7 +1400,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1400,7 +1412,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1414,32 +1426,29 @@
       <c r="D13" t="n">
         <v>2</v>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1450,6 +1459,9 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
@@ -1460,6 +1472,9 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
@@ -1479,7 +1494,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,35 +1503,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
         <v>4.5</v>
       </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
@@ -1526,26 +1529,11 @@
       <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -1554,14 +1542,14 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1575,8 +1563,8 @@
       <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="n">
-        <v>8</v>
+      <c r="E15" t="n">
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
@@ -1584,10 +1572,19 @@
       <c r="H15" t="n">
         <v>7</v>
       </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
       <c r="J15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
@@ -1596,11 +1593,20 @@
       <c r="Q15" t="n">
         <v>1</v>
       </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
       <c r="AF15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -1616,7 +1622,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1625,71 +1631,53 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" t="n">
         <v>6</v>
       </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
       <c r="G16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>6</v>
       </c>
-      <c r="H16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>5</v>
-      </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1698,41 +1686,53 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
         <v>6</v>
       </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K17" t="n">
         <v>8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>7.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>1</v>
+      <c r="M17" t="n">
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
       <c r="AF17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1753,35 +1753,53 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
         <v>5</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M18" t="n">
         <v>2.5</v>
       </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
@@ -1795,68 +1813,53 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
       <c r="L19" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -1864,9 +1867,6 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
@@ -1880,11 +1880,11 @@
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Calor latente</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1905,28 +1905,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H20" t="n">
         <v>7</v>
       </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7</v>
+      <c r="O20" t="n">
+        <v>1</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -1934,36 +1928,24 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
       <c r="AF20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calor latente</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1972,20 +1954,38 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
         <v>7</v>
       </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
@@ -1995,8 +1995,20 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
       <c r="AF21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -2005,14 +2017,14 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2033,13 +2045,16 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
       <c r="J22" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -2048,7 +2063,7 @@
         <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -2062,6 +2077,9 @@
       <c r="Q22" t="n">
         <v>1</v>
       </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
@@ -2074,24 +2092,27 @@
       <c r="V22" t="n">
         <v>1</v>
       </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
       <c r="AF22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2100,16 +2121,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -2118,19 +2139,16 @@
         <v>2</v>
       </c>
       <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4</v>
-      </c>
       <c r="M23" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
@@ -2150,20 +2168,14 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2172,14 +2184,14 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2188,37 +2200,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2229,9 +2232,6 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
@@ -2242,23 +2242,23 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2267,28 +2267,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
       </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2299,7 +2305,13 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
       <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
@@ -2313,7 +2325,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -2325,7 +2337,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2339,6 +2351,9 @@
       <c r="D26" t="n">
         <v>4</v>
       </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
@@ -2346,10 +2361,10 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
@@ -2363,6 +2378,9 @@
       <c r="M26" t="n">
         <v>2.5</v>
       </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2388,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2404,7 +2422,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2413,83 +2431,83 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
       </c>
       <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
         <v>5</v>
       </c>
-      <c r="L27" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>4</v>
-      </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2498,83 +2516,77 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" t="n">
         <v>7</v>
       </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>5</v>
-      </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2591,9 +2603,6 @@
       <c r="F29" t="n">
         <v>8</v>
       </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
       <c r="H29" t="n">
         <v>7</v>
       </c>
@@ -2601,13 +2610,13 @@
         <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
         <v>7</v>
@@ -2615,9 +2624,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
@@ -2653,7 +2659,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2670,27 +2676,30 @@
       <c r="F30" t="n">
         <v>8</v>
       </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" t="n">
-        <v>6</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4</v>
-      </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
@@ -2698,9 +2707,6 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
@@ -2726,7 +2732,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2735,31 +2741,40 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>4.5</v>
       </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2776,18 +2791,24 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -2799,7 +2820,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2808,40 +2829,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>4.5</v>
       </c>
-      <c r="K32" t="n">
-        <v>3</v>
-      </c>
       <c r="L32" t="n">
         <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2852,26 +2861,17 @@
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2880,14 +2880,14 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2896,65 +2896,59 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>6</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
         <v>7</v>
       </c>
-      <c r="J33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>4</v>
+      <c r="K33" t="n">
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>4.5</v>
       </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="n">
+      <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2963,29 +2957,50 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
@@ -2995,11 +3010,17 @@
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
       <c r="AF34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -3015,7 +3036,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3027,37 +3048,25 @@
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
+        <v>7</v>
+      </c>
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="J35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" t="n">
-        <v>4</v>
-      </c>
       <c r="M35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -3068,12 +3077,6 @@
       <c r="Q35" t="n">
         <v>1</v>
       </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1</v>
-      </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
@@ -3083,20 +3086,17 @@
       <c r="V35" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1</v>
-      </c>
       <c r="AF35" t="n">
         <v>2</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4561,47 +4561,80 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" t="n">
         <v>5</v>
       </c>
-      <c r="D57" t="n">
+      <c r="I57" t="n">
         <v>5</v>
       </c>
-      <c r="G57" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I57" t="n">
-        <v>8</v>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7.5</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
       </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
       <c r="R57" t="n">
         <v>1</v>
       </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
       <c r="AF57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4610,62 +4643,35 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
-      </c>
-      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I58" t="n">
         <v>8</v>
       </c>
-      <c r="G58" t="n">
-        <v>6</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1</v>
-      </c>
       <c r="V58" t="n">
         <v>1</v>
       </c>
-      <c r="Z58" t="n">
-        <v>1</v>
-      </c>
       <c r="AF58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
@@ -4677,7 +4683,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4692,7 +4698,7 @@
         <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G59" t="n">
         <v>6</v>
@@ -4701,7 +4707,10 @@
         <v>4</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4</v>
       </c>
       <c r="L59" t="n">
         <v>7.5</v>
@@ -4721,10 +4730,16 @@
       <c r="R59" t="n">
         <v>1</v>
       </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
       <c r="U59" t="n">
         <v>1</v>
       </c>
       <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
@@ -4744,7 +4759,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4759,28 +4774,22 @@
         <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" t="n">
-        <v>7</v>
-      </c>
-      <c r="K60" t="n">
         <v>7</v>
       </c>
       <c r="L60" t="n">
         <v>7.5</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -4792,12 +4801,6 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="n">
-        <v>1</v>
-      </c>
-      <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
@@ -4823,7 +4826,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4840,23 +4843,53 @@
       <c r="F61" t="n">
         <v>8</v>
       </c>
+      <c r="G61" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" t="n">
+        <v>5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>8</v>
+      </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
       <c r="K61" t="n">
         <v>7</v>
       </c>
+      <c r="L61" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M61" t="n">
         <v>7</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
       <c r="V61" t="n">
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -4865,14 +4898,14 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4881,67 +4914,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F62" t="n">
         <v>8</v>
       </c>
-      <c r="G62" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K62" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M62" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>1</v>
-      </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
-      <c r="U62" t="n">
-        <v>1</v>
-      </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4950,14 +4947,14 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4970,18 +4967,21 @@
       </c>
       <c r="D63" t="n">
         <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>4.5</v>
@@ -4989,8 +4989,14 @@
       <c r="K63" t="n">
         <v>3</v>
       </c>
+      <c r="L63" t="n">
+        <v>4</v>
+      </c>
       <c r="M63" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -5010,15 +5016,18 @@
       <c r="T63" t="n">
         <v>1</v>
       </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
@@ -5030,7 +5039,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5039,25 +5048,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J64" t="n">
         <v>4.5</v>
@@ -5065,14 +5071,8 @@
       <c r="K64" t="n">
         <v>3</v>
       </c>
-      <c r="L64" t="n">
-        <v>4</v>
-      </c>
       <c r="M64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5092,18 +5092,15 @@
       <c r="T64" t="n">
         <v>1</v>
       </c>
-      <c r="U64" t="n">
-        <v>1</v>
-      </c>
       <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -5115,7 +5112,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5124,30 +5121,33 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K65" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" t="n">
         <v>4</v>
       </c>
       <c r="M65" t="n">
@@ -5174,11 +5174,14 @@
       <c r="T65" t="n">
         <v>1</v>
       </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5194,7 +5197,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5203,34 +5206,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
-      </c>
-      <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
-      </c>
-      <c r="J66" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -5241,33 +5232,33 @@
       <c r="R66" t="n">
         <v>1</v>
       </c>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
+      <c r="Z66" t="n">
+        <v>1</v>
+      </c>
       <c r="AF66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5276,31 +5267,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>6</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7</v>
+      </c>
+      <c r="I67" t="n">
         <v>8</v>
-      </c>
-      <c r="G67" t="n">
-        <v>2</v>
-      </c>
-      <c r="H67" t="n">
-        <v>2</v>
-      </c>
-      <c r="I67" t="n">
-        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>2.5</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
         <v>2.5</v>
@@ -5330,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5346,7 +5337,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5355,25 +5346,28 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" t="n">
         <v>2.5</v>
       </c>
-      <c r="G68" t="n">
-        <v>2</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L68" t="n">
-        <v>4</v>
+      <c r="K68" t="n">
+        <v>3</v>
       </c>
       <c r="M68" t="n">
         <v>2.5</v>
@@ -5387,24 +5381,24 @@
       <c r="Q68" t="n">
         <v>1</v>
       </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
       <c r="S68" t="n">
         <v>1</v>
       </c>
-      <c r="U68" t="n">
+      <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="V68" t="n">
         <v>1</v>
       </c>
-      <c r="Z68" t="n">
-        <v>1</v>
-      </c>
       <c r="AF68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
@@ -5416,7 +5410,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5430,8 +5424,11 @@
       <c r="D69" t="n">
         <v>2</v>
       </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G69" t="n">
         <v>2</v>
@@ -5449,7 +5446,10 @@
         <v>3</v>
       </c>
       <c r="M69" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
@@ -5470,9 +5470,6 @@
         <v>1</v>
       </c>
       <c r="V69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z69" t="n">
         <v>1</v>
       </c>
       <c r="AF69" t="n">
@@ -5492,7 +5489,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5501,43 +5498,52 @@
         </is>
       </c>
       <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L70" t="n">
         <v>4</v>
-      </c>
-      <c r="D70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" t="n">
-        <v>6</v>
-      </c>
-      <c r="H70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I70" t="n">
-        <v>5</v>
-      </c>
-      <c r="K70" t="n">
-        <v>6</v>
       </c>
       <c r="M70" t="n">
         <v>2.5</v>
       </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
       <c r="P70" t="n">
         <v>1</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" t="n">
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
         <v>1</v>
       </c>
       <c r="V70" t="n">
         <v>1</v>
       </c>
+      <c r="Z70" t="n">
+        <v>1</v>
+      </c>
       <c r="AF70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5553,7 +5559,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5562,31 +5568,31 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K71" t="n">
-        <v>7</v>
-      </c>
-      <c r="L71" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -5594,6 +5600,9 @@
       <c r="P71" t="n">
         <v>1</v>
       </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
       <c r="R71" t="n">
         <v>1</v>
       </c>
@@ -5603,14 +5612,14 @@
       <c r="T71" t="n">
         <v>1</v>
       </c>
-      <c r="U71" t="n">
-        <v>1</v>
-      </c>
       <c r="V71" t="n">
         <v>1</v>
       </c>
+      <c r="Z71" t="n">
+        <v>1</v>
+      </c>
       <c r="AF71" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -5626,7 +5635,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5640,30 +5649,21 @@
       <c r="D72" t="n">
         <v>4</v>
       </c>
-      <c r="F72" t="n">
-        <v>8</v>
-      </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I72" t="n">
         <v>5</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
+        <v>6</v>
+      </c>
+      <c r="M72" t="n">
         <v>2.5</v>
       </c>
-      <c r="K72" t="n">
-        <v>3</v>
-      </c>
-      <c r="M72" t="n">
-        <v>7</v>
-      </c>
-      <c r="O72" t="n">
-        <v>1</v>
-      </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
@@ -5673,9 +5673,6 @@
       <c r="R72" t="n">
         <v>1</v>
       </c>
-      <c r="S72" t="n">
-        <v>1</v>
-      </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
@@ -5683,62 +5680,56 @@
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>8</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
-      </c>
-      <c r="H73" t="n">
+        <v>6</v>
+      </c>
+      <c r="I73" t="n">
+        <v>8</v>
+      </c>
+      <c r="J73" t="n">
         <v>7</v>
       </c>
-      <c r="I73" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" t="n">
-        <v>4.5</v>
+      <c r="K73" t="n">
+        <v>7</v>
       </c>
       <c r="L73" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M73" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N73" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5746,15 +5737,15 @@
       <c r="P73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>1</v>
-      </c>
       <c r="R73" t="n">
         <v>1</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
       </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
@@ -5762,11 +5753,11 @@
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -5778,32 +5769,56 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8</v>
       </c>
       <c r="G74" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.5</v>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M74" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
@@ -5811,23 +5826,23 @@
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gravedad: atracción hacia la Tierra</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5836,34 +5851,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
         <v>8</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>7</v>
-      </c>
-      <c r="K75" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M75" t="n">
         <v>2.5</v>
@@ -5886,9 +5898,6 @@
       <c r="S75" t="n">
         <v>1</v>
       </c>
-      <c r="T75" t="n">
-        <v>1</v>
-      </c>
       <c r="U75" t="n">
         <v>1</v>
       </c>
@@ -5896,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -5905,14 +5914,14 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5921,31 +5930,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
-      </c>
-      <c r="F76" t="n">
-        <v>8</v>
-      </c>
-      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" t="n">
         <v>4</v>
       </c>
-      <c r="J76" t="n">
-        <v>7</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
+      <c r="M76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -5954,14 +5963,14 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5970,19 +5979,43 @@
         </is>
       </c>
       <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
+      <c r="K77" t="n">
         <v>5</v>
       </c>
-      <c r="D77" t="n">
-        <v>5</v>
-      </c>
-      <c r="G77" t="n">
+      <c r="L77" t="n">
         <v>6</v>
       </c>
-      <c r="H77" t="n">
-        <v>4</v>
-      </c>
       <c r="M77" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -5990,11 +6023,23 @@
       <c r="Q77" t="n">
         <v>1</v>
       </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
+      </c>
       <c r="V77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -6003,29 +6048,47 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Aplicaciones de las leyes de Newton</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>8</v>
+      </c>
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I78" t="n">
         <v>4</v>
       </c>
-      <c r="D78" t="n">
-        <v>4</v>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
@@ -6034,19 +6097,19 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Observación astronómica en distintas longitudes de onda</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6055,24 +6118,42 @@
       <c r="D79" t="n">
         <v>5</v>
       </c>
+      <c r="G79" t="n">
+        <v>6</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4</v>
+      </c>
+      <c r="M79" t="n">
+        <v>7</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
       <c r="AF79" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Campo eléctrico</t>
+          <t>Aplicaciones de las leyes de Newton</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6081,25 +6162,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
-      </c>
-      <c r="F80" t="n">
-        <v>8</v>
-      </c>
-      <c r="G80" t="n">
-        <v>6</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6115,7 +6184,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Capacitancia y condensadores</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6146,7 +6215,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Campo eléctrico</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6155,19 +6224,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" t="n">
-        <v>2</v>
-      </c>
-      <c r="T82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="n">
+        <v>8</v>
+      </c>
+      <c r="G82" t="n">
+        <v>6</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" t="n">
         <v>1</v>
       </c>
       <c r="AF82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6183,7 +6258,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Capacitancia y condensadores</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6192,32 +6267,17 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
-      </c>
-      <c r="G83" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I83" t="n">
-        <v>7</v>
-      </c>
-      <c r="M83" t="n">
-        <v>7</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1</v>
-      </c>
-      <c r="R83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D83" t="n">
+        <v>5</v>
       </c>
       <c r="AF83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -6229,7 +6289,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cuantización de la energía</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6238,13 +6298,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6260,7 +6326,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Desintegración radiactiva</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6269,28 +6335,28 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
-      </c>
-      <c r="E85" t="n">
-        <v>8</v>
-      </c>
-      <c r="F85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G85" t="n">
         <v>8.5</v>
       </c>
-      <c r="N85" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
+      <c r="I85" t="n">
+        <v>7</v>
+      </c>
+      <c r="M85" t="n">
+        <v>7</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
       </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
       <c r="AF85" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -6306,7 +6372,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Cuantización de la energía</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6315,20 +6381,17 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
-      </c>
-      <c r="E86" t="n">
-        <v>8</v>
-      </c>
-      <c r="N86" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D86" t="n">
+        <v>7</v>
       </c>
       <c r="AF86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -6340,7 +6403,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Desintegración radiactiva</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6349,17 +6412,32 @@
         </is>
       </c>
       <c r="C87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="n">
         <v>8</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
       </c>
       <c r="AF87" t="n">
         <v>11</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -6371,7 +6449,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Defecto de masa y energía de enlace nuclear</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6380,16 +6458,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
-      </c>
-      <c r="F88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="n">
         <v>8</v>
       </c>
-      <c r="O88" t="n">
+      <c r="N88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -6405,7 +6483,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Espejos esféricos</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6414,56 +6492,29 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
-      </c>
-      <c r="F89" t="n">
         <v>8</v>
       </c>
-      <c r="H89" t="n">
-        <v>5</v>
-      </c>
-      <c r="J89" t="n">
-        <v>7</v>
-      </c>
-      <c r="L89" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M89" t="n">
-        <v>7</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>1</v>
-      </c>
-      <c r="S89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" t="n">
-        <v>1</v>
+      <c r="D89" t="n">
+        <v>8</v>
       </c>
       <c r="AF89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
           <t>posterior</t>
-        </is>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Fisión y fusión nuclear</t>
+          <t>Defecto de masa y energía de enlace nuclear</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6472,24 +6523,12 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
-      <c r="L90" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M90" t="n">
-        <v>7</v>
-      </c>
       <c r="O90" t="n">
-        <v>1</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1</v>
-      </c>
-      <c r="V90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
@@ -6509,7 +6548,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Fotón y efecto fotoeléctrico</t>
+          <t>Espejos esféricos</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6520,16 +6559,34 @@
       <c r="C91" t="n">
         <v>10</v>
       </c>
-      <c r="E91" t="n">
+      <c r="F91" t="n">
         <v>8</v>
       </c>
-      <c r="G91" t="n">
-        <v>6</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" t="n">
+      <c r="H91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
+      </c>
+      <c r="L91" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>7</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
@@ -6542,14 +6599,14 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Inducción electromagnética: Faraday y Lenz</t>
+          <t>Fisión y fusión nuclear</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6558,19 +6615,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
-      </c>
-      <c r="D92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
       </c>
-      <c r="G92" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I92" t="n">
-        <v>5</v>
+      <c r="L92" t="n">
+        <v>7.5</v>
       </c>
       <c r="M92" t="n">
         <v>7</v>
@@ -6578,21 +6629,18 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="P92" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" t="n">
+      <c r="U92" t="n">
         <v>1</v>
       </c>
       <c r="V92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -6604,7 +6652,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ley de Coulomb</t>
+          <t>Fotón y efecto fotoeléctrico</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6613,59 +6661,38 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
-      </c>
-      <c r="D93" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="n">
         <v>8</v>
       </c>
       <c r="G93" t="n">
         <v>6</v>
       </c>
-      <c r="I93" t="n">
-        <v>7</v>
-      </c>
-      <c r="J93" t="n">
-        <v>7</v>
-      </c>
-      <c r="M93" t="n">
-        <v>7</v>
-      </c>
-      <c r="O93" t="n">
+      <c r="N93" t="n">
         <v>1</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
       </c>
-      <c r="R93" t="n">
-        <v>1</v>
-      </c>
-      <c r="S93" t="n">
-        <v>1</v>
-      </c>
-      <c r="V93" t="n">
-        <v>1</v>
-      </c>
       <c r="AF93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Leyes de Kepler</t>
+          <t>Inducción electromagnética: Faraday y Lenz</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6679,8 +6706,32 @@
       <c r="D94" t="n">
         <v>4</v>
       </c>
+      <c r="F94" t="n">
+        <v>8</v>
+      </c>
+      <c r="G94" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>5</v>
+      </c>
+      <c r="M94" t="n">
+        <v>7</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="n">
+        <v>1</v>
+      </c>
       <c r="AF94" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -6696,7 +6747,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
+          <t>Ley de Coulomb</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6705,7 +6756,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" t="n">
+        <v>8</v>
       </c>
       <c r="G95" t="n">
         <v>6</v>
@@ -6713,30 +6770,45 @@
       <c r="I95" t="n">
         <v>7</v>
       </c>
+      <c r="J95" t="n">
+        <v>7</v>
+      </c>
+      <c r="M95" t="n">
+        <v>7</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
       <c r="R95" t="n">
         <v>1</v>
       </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="n">
+        <v>1</v>
+      </c>
       <c r="AF95" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Modelo estándar de partículas</t>
+          <t>Leyes de Kepler</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6745,10 +6817,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF96" t="n">
         <v>11</v>
@@ -6767,7 +6839,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Núcleo atómico e isótopos</t>
+          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6778,16 +6850,16 @@
       <c r="C97" t="n">
         <v>11</v>
       </c>
-      <c r="F97" t="n">
-        <v>8</v>
-      </c>
       <c r="G97" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O97" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="I97" t="n">
+        <v>7</v>
       </c>
       <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
         <v>1</v>
       </c>
       <c r="AF97" t="n">
@@ -6807,7 +6879,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro</t>
+          <t>Modelo estándar de partículas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6816,59 +6888,29 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
-      </c>
-      <c r="F98" t="n">
-        <v>8</v>
-      </c>
-      <c r="G98" t="n">
-        <v>6</v>
-      </c>
-      <c r="H98" t="n">
         <v>7</v>
       </c>
-      <c r="L98" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M98" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
-      <c r="P98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>1</v>
-      </c>
-      <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>1</v>
+      <c r="D98" t="n">
+        <v>7</v>
       </c>
       <c r="AF98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
           <t>posterior</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ondas de radio y telecomunicaciones</t>
+          <t>Núcleo atómico e isótopos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6879,25 +6921,16 @@
       <c r="C99" t="n">
         <v>11</v>
       </c>
+      <c r="F99" t="n">
+        <v>8</v>
+      </c>
       <c r="G99" t="n">
         <v>8.5</v>
       </c>
-      <c r="H99" t="n">
-        <v>7</v>
-      </c>
-      <c r="M99" t="n">
-        <v>4.5</v>
+      <c r="O99" t="n">
+        <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>1</v>
-      </c>
-      <c r="V99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z99" t="n">
         <v>1</v>
       </c>
       <c r="AF99" t="n">
@@ -6917,7 +6950,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Energía potencial y potencial eléctrico</t>
+          <t>Ondas electromagnéticas y espectro</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6926,41 +6959,59 @@
         </is>
       </c>
       <c r="C100" t="n">
+        <v>10</v>
+      </c>
+      <c r="F100" t="n">
         <v>8</v>
       </c>
-      <c r="D100" t="n">
-        <v>8</v>
-      </c>
       <c r="G100" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H100" t="n">
         <v>7</v>
       </c>
+      <c r="L100" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M100" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
       <c r="P100" t="n">
         <v>1</v>
       </c>
       <c r="Q100" t="n">
         <v>1</v>
       </c>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>1</v>
+      </c>
       <c r="AF100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6971,20 +7022,14 @@
       <c r="C101" t="n">
         <v>11</v>
       </c>
-      <c r="F101" t="n">
-        <v>8</v>
-      </c>
       <c r="G101" t="n">
         <v>8.5</v>
       </c>
       <c r="H101" t="n">
         <v>7</v>
       </c>
-      <c r="L101" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O101" t="n">
-        <v>1</v>
+      <c r="M101" t="n">
+        <v>4.5</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
@@ -6992,7 +7037,7 @@
       <c r="Q101" t="n">
         <v>1</v>
       </c>
-      <c r="U101" t="n">
+      <c r="V101" t="n">
         <v>1</v>
       </c>
       <c r="Z101" t="n">
@@ -7015,7 +7060,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Radiación térmica y cuerpo negro</t>
+          <t>Energía potencial y potencial eléctrico</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7024,38 +7069,29 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8</v>
+      </c>
+      <c r="G102" t="n">
+        <v>8.5</v>
       </c>
       <c r="H102" t="n">
         <v>7</v>
       </c>
-      <c r="J102" t="n">
-        <v>7</v>
-      </c>
-      <c r="K102" t="n">
-        <v>6</v>
-      </c>
-      <c r="L102" t="n">
-        <v>7.5</v>
+      <c r="P102" t="n">
+        <v>1</v>
       </c>
       <c r="Q102" t="n">
         <v>1</v>
       </c>
-      <c r="S102" t="n">
-        <v>1</v>
-      </c>
-      <c r="T102" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
       <c r="AF102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
@@ -7067,7 +7103,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Rapidez de la luz</t>
+          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7076,10 +7112,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F103" t="n">
+        <v>8</v>
       </c>
       <c r="G103" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H103" t="n">
         <v>7</v>
@@ -7087,8 +7126,8 @@
       <c r="L103" t="n">
         <v>7.5</v>
       </c>
-      <c r="M103" t="n">
-        <v>7</v>
+      <c r="O103" t="n">
+        <v>1</v>
       </c>
       <c r="P103" t="n">
         <v>1</v>
@@ -7097,9 +7136,6 @@
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>1</v>
-      </c>
-      <c r="V103" t="n">
         <v>1</v>
       </c>
       <c r="Z103" t="n">
@@ -7122,7 +7158,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Reflexión interna total</t>
+          <t>Radiación térmica y cuerpo negro</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7131,15 +7167,30 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
-      </c>
-      <c r="D104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H104" t="n">
         <v>7</v>
       </c>
+      <c r="J104" t="n">
+        <v>7</v>
+      </c>
+      <c r="K104" t="n">
+        <v>6</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7.5</v>
+      </c>
       <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
@@ -7147,7 +7198,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
@@ -7159,7 +7210,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Segunda ley de la termodinámica</t>
+          <t>Rapidez de la luz</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7168,23 +7219,41 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
-      </c>
-      <c r="D105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H105" t="n">
+        <v>7</v>
+      </c>
+      <c r="L105" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M105" t="n">
+        <v>7</v>
       </c>
       <c r="P105" t="n">
         <v>1</v>
       </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" t="n">
+        <v>1</v>
+      </c>
+      <c r="V105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>1</v>
+      </c>
       <c r="AF105" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
@@ -7196,7 +7265,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Semiconductores y electrónica básica</t>
+          <t>Reflexión interna total</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7205,20 +7274,23 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
-      </c>
-      <c r="J106" t="n">
+        <v>8</v>
+      </c>
+      <c r="D106" t="n">
+        <v>8</v>
+      </c>
+      <c r="H106" t="n">
         <v>7</v>
       </c>
-      <c r="S106" t="n">
+      <c r="Q106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -7230,7 +7302,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Superposición e interferencia de ondas</t>
+          <t>Segunda ley de la termodinámica</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7239,20 +7311,23 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D107" t="n">
+        <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
       <c r="AF107" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
@@ -7264,7 +7339,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Semiconductores y electrónica básica</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7273,41 +7348,20 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
-      </c>
-      <c r="D108" t="n">
-        <v>8</v>
-      </c>
-      <c r="G108" t="n">
-        <v>6</v>
-      </c>
-      <c r="H108" t="n">
+        <v>9</v>
+      </c>
+      <c r="J108" t="n">
         <v>7</v>
       </c>
-      <c r="J108" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M108" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>1</v>
-      </c>
       <c r="S108" t="n">
         <v>1</v>
       </c>
-      <c r="V108" t="n">
-        <v>1</v>
-      </c>
       <c r="AF108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
@@ -7319,7 +7373,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Viscosidad y régimen de flujo</t>
+          <t>Superposición e interferencia de ondas</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7328,16 +7382,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
-      </c>
-      <c r="K109" t="n">
-        <v>7</v>
-      </c>
-      <c r="T109" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6</v>
+      </c>
+      <c r="P109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
@@ -7353,69 +7407,84 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Aceleración y fuerza centrípeta</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>8</v>
+      </c>
+      <c r="D110" t="n">
+        <v>8</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6</v>
+      </c>
+      <c r="H110" t="n">
+        <v>7</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M110" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
           <t>sin_referente</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>5</v>
-      </c>
-      <c r="D110" t="n">
-        <v>5</v>
-      </c>
-      <c r="M110" t="n">
-        <v>7</v>
-      </c>
-      <c r="V110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF110" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>sin_referente</t>
-        </is>
-      </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Colisiones elásticas e inelásticas</t>
+          <t>Viscosidad y régimen de flujo</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
-      </c>
-      <c r="D111" t="n">
-        <v>8</v>
-      </c>
-      <c r="G111" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P111" t="n">
+        <v>9</v>
+      </c>
+      <c r="K111" t="n">
+        <v>7</v>
+      </c>
+      <c r="T111" t="n">
         <v>1</v>
       </c>
       <c r="AF111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
@@ -7427,7 +7496,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Aceleración y fuerza centrípeta</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7436,10 +7505,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D112" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="M112" t="n">
+        <v>7</v>
+      </c>
+      <c r="V112" t="n">
+        <v>1</v>
       </c>
       <c r="AF112" t="n">
         <v>8</v>
@@ -7458,7 +7533,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Colisiones elásticas e inelásticas</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7467,31 +7542,19 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
-      </c>
-      <c r="H113" t="n">
-        <v>4</v>
-      </c>
-      <c r="J113" t="n">
-        <v>7</v>
-      </c>
-      <c r="K113" t="n">
         <v>8</v>
       </c>
-      <c r="Q113" t="n">
-        <v>1</v>
-      </c>
-      <c r="S113" t="n">
-        <v>1</v>
-      </c>
-      <c r="T113" t="n">
+      <c r="G113" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P113" t="n">
         <v>1</v>
       </c>
       <c r="AF113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -7500,14 +7563,14 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7516,13 +7579,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF114" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -7538,7 +7601,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7547,25 +7610,31 @@
         </is>
       </c>
       <c r="C115" t="n">
+        <v>5</v>
+      </c>
+      <c r="D115" t="n">
+        <v>5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="J115" t="n">
+        <v>7</v>
+      </c>
+      <c r="K115" t="n">
         <v>8</v>
       </c>
-      <c r="D115" t="n">
-        <v>8</v>
-      </c>
-      <c r="H115" t="n">
-        <v>7</v>
-      </c>
-      <c r="M115" t="n">
-        <v>7</v>
-      </c>
       <c r="Q115" t="n">
         <v>1</v>
       </c>
-      <c r="V115" t="n">
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="n">
         <v>1</v>
       </c>
       <c r="AF115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
@@ -7574,14 +7643,14 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Movimiento armónico simple</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7590,25 +7659,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
-        <v>8</v>
-      </c>
-      <c r="F116" t="n">
-        <v>8</v>
-      </c>
-      <c r="I116" t="n">
-        <v>4</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
-      <c r="R116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF116" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -7624,7 +7681,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Movimiento circular y variables angulares</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7633,31 +7690,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
-      </c>
-      <c r="G117" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K117" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="H117" t="n">
+        <v>7</v>
       </c>
       <c r="M117" t="n">
         <v>7</v>
       </c>
-      <c r="P117" t="n">
-        <v>1</v>
-      </c>
-      <c r="T117" t="n">
+      <c r="Q117" t="n">
         <v>1</v>
       </c>
       <c r="V117" t="n">
         <v>1</v>
       </c>
       <c r="AF117" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
@@ -7666,14 +7717,14 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cinemática en dos dimensiones y proyectiles</t>
+          <t>Movimiento armónico simple</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7687,10 +7738,16 @@
       <c r="D118" t="n">
         <v>8</v>
       </c>
-      <c r="G118" t="n">
-        <v>6</v>
-      </c>
-      <c r="P118" t="n">
+      <c r="F118" t="n">
+        <v>8</v>
+      </c>
+      <c r="I118" t="n">
+        <v>4</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" t="n">
         <v>1</v>
       </c>
       <c r="AF118" t="n">
@@ -7710,7 +7767,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Niveles de energía atómicos y espectros</t>
+          <t>Movimiento circular y variables angulares</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7727,11 +7784,23 @@
       <c r="G119" t="n">
         <v>8.5</v>
       </c>
+      <c r="K119" t="n">
+        <v>3</v>
+      </c>
+      <c r="M119" t="n">
+        <v>7</v>
+      </c>
       <c r="P119" t="n">
         <v>1</v>
       </c>
+      <c r="T119" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1</v>
+      </c>
       <c r="AF119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -7740,14 +7809,14 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ondas estacionarias y armónicos</t>
+          <t>Cinemática en dos dimensiones y proyectiles</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7761,16 +7830,10 @@
       <c r="D120" t="n">
         <v>8</v>
       </c>
-      <c r="H120" t="n">
-        <v>7</v>
-      </c>
-      <c r="M120" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>1</v>
-      </c>
-      <c r="V120" t="n">
+      <c r="G120" t="n">
+        <v>6</v>
+      </c>
+      <c r="P120" t="n">
         <v>1</v>
       </c>
       <c r="AF120" t="n">
@@ -7790,7 +7853,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Órbitas y satélites</t>
+          <t>Niveles de energía atómicos y espectros</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7799,10 +7862,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D121" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
       </c>
       <c r="AF121" t="n">
         <v>10</v>
@@ -7821,7 +7890,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Ondas estacionarias y armónicos</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7830,25 +7899,25 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D122" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H122" t="n">
         <v>7</v>
       </c>
-      <c r="K122" t="n">
-        <v>5</v>
+      <c r="M122" t="n">
+        <v>7</v>
       </c>
       <c r="Q122" t="n">
         <v>1</v>
       </c>
-      <c r="T122" t="n">
+      <c r="V122" t="n">
         <v>1</v>
       </c>
       <c r="AF122" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
@@ -7864,7 +7933,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Órbitas y satélites</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7873,37 +7942,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
-      </c>
-      <c r="G123" t="n">
-        <v>6</v>
-      </c>
-      <c r="H123" t="n">
-        <v>7</v>
-      </c>
-      <c r="I123" t="n">
         <v>8</v>
       </c>
-      <c r="J123" t="n">
-        <v>7</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>1</v>
-      </c>
-      <c r="R123" t="n">
-        <v>1</v>
-      </c>
-      <c r="S123" t="n">
-        <v>1</v>
-      </c>
       <c r="AF123" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -7912,14 +7957,14 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad</t>
+          <t>Hidrodinámica: continuidad y Bernoulli</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7933,10 +7978,16 @@
       <c r="D124" t="n">
         <v>6</v>
       </c>
-      <c r="M124" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V124" t="n">
+      <c r="H124" t="n">
+        <v>7</v>
+      </c>
+      <c r="K124" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1</v>
+      </c>
+      <c r="T124" t="n">
         <v>1</v>
       </c>
       <c r="AF124" t="n">
@@ -7956,123 +8007,99 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Espejos planos e imágenes</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C125" t="n">
+        <v>5</v>
+      </c>
+      <c r="D125" t="n">
+        <v>5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6</v>
+      </c>
+      <c r="H125" t="n">
         <v>7</v>
       </c>
-      <c r="D125" t="n">
+      <c r="I125" t="n">
+        <v>8</v>
+      </c>
+      <c r="J125" t="n">
         <v>7</v>
       </c>
-      <c r="H125" t="n">
-        <v>3</v>
-      </c>
-      <c r="J125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L125" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M125" t="n">
-        <v>7</v>
+      <c r="P125" t="n">
+        <v>1</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
       </c>
+      <c r="R125" t="n">
+        <v>1</v>
+      </c>
       <c r="S125" t="n">
         <v>1</v>
       </c>
-      <c r="U125" t="n">
-        <v>1</v>
-      </c>
-      <c r="V125" t="n">
-        <v>1</v>
-      </c>
       <c r="AF125" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
-      </c>
-      <c r="F126" t="n">
-        <v>8</v>
-      </c>
-      <c r="H126" t="n">
-        <v>5</v>
-      </c>
-      <c r="I126" t="n">
         <v>6</v>
       </c>
-      <c r="J126" t="n">
-        <v>4.5</v>
+      <c r="D126" t="n">
+        <v>6</v>
       </c>
       <c r="M126" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O126" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>1</v>
-      </c>
-      <c r="R126" t="n">
-        <v>1</v>
-      </c>
-      <c r="S126" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="V126" t="n">
         <v>1</v>
       </c>
-      <c r="Z126" t="n">
-        <v>1</v>
-      </c>
       <c r="AF126" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8081,25 +8108,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
-      </c>
-      <c r="F127" t="n">
-        <v>8</v>
-      </c>
-      <c r="G127" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D127" t="n">
+        <v>7</v>
       </c>
       <c r="H127" t="n">
-        <v>7</v>
-      </c>
-      <c r="I127" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
-        <v>7</v>
-      </c>
-      <c r="K127" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="L127" t="n">
         <v>7.5</v>
@@ -8107,24 +8125,12 @@
       <c r="M127" t="n">
         <v>7</v>
       </c>
-      <c r="O127" t="n">
-        <v>1</v>
-      </c>
-      <c r="P127" t="n">
-        <v>1</v>
-      </c>
       <c r="Q127" t="n">
         <v>1</v>
       </c>
-      <c r="R127" t="n">
-        <v>1</v>
-      </c>
       <c r="S127" t="n">
         <v>1</v>
       </c>
-      <c r="T127" t="n">
-        <v>1</v>
-      </c>
       <c r="U127" t="n">
         <v>1</v>
       </c>
@@ -8132,23 +8138,23 @@
         <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Masa y peso</t>
+          <t>Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8157,47 +8163,26 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
-      </c>
-      <c r="D128" t="n">
-        <v>2</v>
-      </c>
-      <c r="E128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F128" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G128" t="n">
+        <v>8</v>
+      </c>
+      <c r="H128" t="n">
+        <v>5</v>
+      </c>
+      <c r="I128" t="n">
         <v>6</v>
       </c>
-      <c r="H128" t="n">
-        <v>2</v>
-      </c>
-      <c r="I128" t="n">
-        <v>2</v>
-      </c>
       <c r="J128" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K128" t="n">
-        <v>5</v>
-      </c>
-      <c r="L128" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M128" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N128" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="P128" t="n">
-        <v>1</v>
-      </c>
       <c r="Q128" t="n">
         <v>1</v>
       </c>
@@ -8207,33 +8192,30 @@
       <c r="S128" t="n">
         <v>1</v>
       </c>
-      <c r="T128" t="n">
-        <v>1</v>
-      </c>
-      <c r="U128" t="n">
-        <v>1</v>
-      </c>
       <c r="V128" t="n">
         <v>1</v>
       </c>
+      <c r="Z128" t="n">
+        <v>1</v>
+      </c>
       <c r="AF128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>El ojo y los instrumentos ópticos</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8242,10 +8224,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
-      </c>
-      <c r="D129" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F129" t="n">
         <v>8</v>
@@ -8254,16 +8233,22 @@
         <v>6</v>
       </c>
       <c r="H129" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="I129" t="n">
+        <v>7</v>
       </c>
       <c r="J129" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K129" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="L129" t="n">
+        <v>7.5</v>
       </c>
       <c r="M129" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>
@@ -8274,24 +8259,27 @@
       <c r="Q129" t="n">
         <v>1</v>
       </c>
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
       <c r="S129" t="n">
         <v>1</v>
       </c>
       <c r="T129" t="n">
         <v>1</v>
       </c>
+      <c r="U129" t="n">
+        <v>1</v>
+      </c>
       <c r="V129" t="n">
         <v>1</v>
       </c>
-      <c r="Z129" t="n">
-        <v>1</v>
-      </c>
       <c r="AF129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
@@ -8303,7 +8291,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Masa y peso</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8317,29 +8305,35 @@
       <c r="D130" t="n">
         <v>2</v>
       </c>
+      <c r="E130" t="n">
+        <v>2</v>
+      </c>
       <c r="F130" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G130" t="n">
         <v>6</v>
       </c>
       <c r="H130" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J130" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K130" t="n">
         <v>5</v>
       </c>
       <c r="L130" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M130" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
       </c>
       <c r="O130" t="n">
         <v>1</v>
@@ -8365,11 +8359,8 @@
       <c r="V130" t="n">
         <v>1</v>
       </c>
-      <c r="Z130" t="n">
-        <v>1</v>
-      </c>
       <c r="AF130" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
@@ -8378,14 +8369,14 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>El ojo y los instrumentos ópticos</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8394,40 +8385,28 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>7</v>
-      </c>
-      <c r="E131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F131" t="n">
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H131" t="n">
         <v>5</v>
       </c>
-      <c r="I131" t="n">
-        <v>6</v>
-      </c>
       <c r="J131" t="n">
         <v>4.5</v>
       </c>
       <c r="K131" t="n">
         <v>3</v>
       </c>
-      <c r="L131" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M131" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N131" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O131" t="n">
         <v>1</v>
@@ -8438,18 +8417,12 @@
       <c r="Q131" t="n">
         <v>1</v>
       </c>
-      <c r="R131" t="n">
-        <v>1</v>
-      </c>
       <c r="S131" t="n">
         <v>1</v>
       </c>
       <c r="T131" t="n">
         <v>1</v>
       </c>
-      <c r="U131" t="n">
-        <v>1</v>
-      </c>
       <c r="V131" t="n">
         <v>1</v>
       </c>
@@ -8457,11 +8430,11 @@
         <v>1</v>
       </c>
       <c r="AF131" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
@@ -8473,7 +8446,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8482,47 +8455,74 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D132" t="n">
+        <v>7</v>
+      </c>
+      <c r="E132" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" t="n">
+        <v>8</v>
       </c>
       <c r="G132" t="n">
         <v>8.5</v>
       </c>
       <c r="H132" t="n">
+        <v>5</v>
+      </c>
+      <c r="I132" t="n">
+        <v>6</v>
+      </c>
+      <c r="J132" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3</v>
+      </c>
+      <c r="L132" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M132" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" t="n">
+        <v>1</v>
+      </c>
+      <c r="V132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF132" t="n">
         <v>7</v>
       </c>
-      <c r="I132" t="n">
-        <v>3</v>
-      </c>
-      <c r="K132" t="n">
-        <v>7</v>
-      </c>
-      <c r="M132" t="n">
-        <v>7</v>
-      </c>
-      <c r="P132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>1</v>
-      </c>
-      <c r="R132" t="n">
-        <v>1</v>
-      </c>
-      <c r="T132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>10</v>
-      </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -1896,7 +1896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calor latente</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1905,20 +1905,38 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>7</v>
       </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
@@ -1928,8 +1946,20 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
       <c r="AF20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1938,14 +1968,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Calor latente</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1954,38 +1984,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" t="n">
         <v>7</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
@@ -1995,20 +2007,8 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2045,16 +2045,13 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
       <c r="J22" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -2063,7 +2060,7 @@
         <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -2077,9 +2074,6 @@
       <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
@@ -2092,27 +2086,24 @@
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2121,34 +2112,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
         <v>3</v>
       </c>
-      <c r="F23" t="n">
+      <c r="J23" t="n">
         <v>2.5</v>
       </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.5</v>
+      <c r="K23" t="n">
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
@@ -2168,14 +2162,20 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2200,28 +2200,37 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
       <c r="M24" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2232,6 +2241,9 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
@@ -2242,23 +2254,23 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2267,34 +2279,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
       </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
-      <c r="K25" t="n">
-        <v>5</v>
-      </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2305,13 +2311,7 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
       <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -2337,7 +2337,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2351,9 +2351,6 @@
       <c r="D26" t="n">
         <v>4</v>
       </c>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
@@ -2361,10 +2358,10 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
@@ -2378,9 +2375,6 @@
       <c r="M26" t="n">
         <v>2.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2406,7 +2400,7 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2422,7 +2416,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2431,83 +2425,83 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
         <v>5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>7</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
       </c>
       <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
         <v>4</v>
       </c>
-      <c r="L27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>5</v>
-      </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2516,77 +2510,83 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
         <v>4.5</v>
       </c>
-      <c r="K28" t="n">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
         <v>5</v>
       </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>6</v>
-      </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2603,6 +2603,9 @@
       <c r="F29" t="n">
         <v>8</v>
       </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
       <c r="H29" t="n">
         <v>7</v>
       </c>
@@ -2610,13 +2613,13 @@
         <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
         <v>7</v>
@@ -2624,6 +2627,9 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
@@ -2659,7 +2665,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2676,30 +2682,27 @@
       <c r="F30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
         <v>6</v>
       </c>
-      <c r="H30" t="n">
-        <v>5</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="J30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
-      </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
@@ -2707,6 +2710,9 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
@@ -2732,7 +2738,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2741,40 +2747,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>4.5</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>3</v>
       </c>
-      <c r="L31" t="n">
-        <v>4</v>
-      </c>
       <c r="M31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2791,24 +2788,18 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -2820,7 +2811,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2829,28 +2820,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>4.5</v>
       </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
       <c r="L32" t="n">
         <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2861,17 +2864,26 @@
       <c r="Q32" t="n">
         <v>1</v>
       </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
       <c r="AF32" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2880,14 +2892,14 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2896,59 +2908,65 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>6</v>
       </c>
-      <c r="I33" t="n">
-        <v>5</v>
+      <c r="H33" t="n">
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2</v>
+        <v>4.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4</v>
       </c>
       <c r="M33" t="n">
         <v>4.5</v>
       </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2957,70 +2975,43 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
         <v>8</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -3036,7 +3027,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,25 +3039,37 @@
         <v>2</v>
       </c>
       <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -3077,6 +3080,12 @@
       <c r="Q35" t="n">
         <v>1</v>
       </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
@@ -3086,24 +3095,27 @@
       <c r="V35" t="n">
         <v>1</v>
       </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
       <c r="AF35" t="n">
         <v>2</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fricción y resistencia del aire</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3112,38 +3124,29 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
         <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>7</v>
+      </c>
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="J36" t="n">
+      <c r="M36" t="n">
         <v>7</v>
       </c>
-      <c r="K36" t="n">
-        <v>5</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
@@ -3153,9 +3156,6 @@
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
@@ -3166,23 +3166,23 @@
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3191,31 +3191,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>7</v>
       </c>
+      <c r="K37" t="n">
+        <v>5</v>
+      </c>
       <c r="L37" t="n">
         <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -3226,12 +3232,12 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
@@ -3239,23 +3245,23 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3264,13 +3270,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
@@ -3279,25 +3282,19 @@
         <v>6</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -3314,9 +3311,6 @@
       <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
       <c r="U38" t="n">
         <v>1</v>
       </c>
@@ -3324,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3340,7 +3334,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3349,28 +3343,34 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
       </c>
       <c r="G39" t="n">
         <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3</v>
       </c>
       <c r="M39" t="n">
         <v>2.5</v>
@@ -3378,6 +3378,9 @@
       <c r="N39" t="n">
         <v>1</v>
       </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
@@ -3393,11 +3396,14 @@
       <c r="T39" t="n">
         <v>1</v>
       </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3413,7 +3419,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3422,44 +3428,59 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>6</v>
       </c>
+      <c r="H40" t="n">
+        <v>7</v>
+      </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
         <v>7</v>
       </c>
+      <c r="K40" t="n">
+        <v>4</v>
+      </c>
       <c r="M40" t="n">
-        <v>7</v>
-      </c>
-      <c r="O40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3471,7 +3492,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3480,65 +3501,44 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
-      </c>
-      <c r="D41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
         <v>7</v>
       </c>
       <c r="J41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2</v>
-      </c>
-      <c r="L41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N41" t="n">
+        <v>7</v>
+      </c>
+      <c r="O41" t="n">
         <v>1</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
       <c r="V41" t="n">
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,30 +3559,36 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
         <v>7</v>
       </c>
       <c r="J42" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K42" t="n">
         <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3</v>
       </c>
       <c r="M42" t="n">
         <v>2.5</v>
       </c>
-      <c r="O42" t="n">
+      <c r="N42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
@@ -3591,21 +3597,27 @@
       <c r="Q42" t="n">
         <v>1</v>
       </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -3617,7 +3629,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3626,28 +3638,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
       </c>
       <c r="M43" t="n">
         <v>2.5</v>
@@ -3661,24 +3670,21 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="R43" t="n">
-        <v>1</v>
-      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="U43" t="n">
+      <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3690,7 +3696,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Magnitudes escalares y vectoriales</t>
+          <t>Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3699,26 +3705,44 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" t="n">
-        <v>6</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
       </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
@@ -3728,14 +3752,20 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3744,14 +3774,14 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3760,25 +3790,31 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
         <v>8</v>
       </c>
-      <c r="D45" t="n">
-        <v>8</v>
-      </c>
-      <c r="F45" t="n">
-        <v>5</v>
-      </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3789,17 +3825,20 @@
       <c r="Q45" t="n">
         <v>1</v>
       </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
       <c r="S45" t="n">
         <v>1</v>
       </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
-      <c r="Z45" t="n">
-        <v>1</v>
-      </c>
       <c r="AF45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3815,7 +3854,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Magnitudes escalares y vectoriales</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3824,59 +3863,47 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" t="n">
         <v>3</v>
       </c>
-      <c r="H46" t="n">
-        <v>2</v>
-      </c>
       <c r="I46" t="n">
+        <v>6</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
         <v>5</v>
       </c>
-      <c r="J46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K46" t="n">
-        <v>3</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2</v>
-      </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -3888,7 +3915,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3897,28 +3924,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M47" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3926,20 +3953,17 @@
       <c r="Q47" t="n">
         <v>1</v>
       </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
       <c r="S47" t="n">
         <v>1</v>
       </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
       <c r="AF47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -3955,7 +3979,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3969,20 +3993,29 @@
       <c r="D48" t="n">
         <v>2</v>
       </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
         <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.5</v>
       </c>
       <c r="K48" t="n">
         <v>3</v>
       </c>
-      <c r="L48" t="n">
-        <v>3</v>
+      <c r="M48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3993,13 +4026,13 @@
       <c r="R48" t="n">
         <v>1</v>
       </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z48" t="n">
+      <c r="V48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
@@ -4007,7 +4040,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -4019,7 +4052,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4028,16 +4061,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -4046,20 +4076,14 @@
         <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K49" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="L49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
         <v>2.5</v>
       </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
@@ -4072,9 +4096,6 @@
       <c r="S49" t="n">
         <v>1</v>
       </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
       <c r="U49" t="n">
         <v>1</v>
       </c>
@@ -4082,23 +4103,23 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4112,32 +4133,20 @@
       <c r="D50" t="n">
         <v>2</v>
       </c>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
-      <c r="F50" t="n">
-        <v>2.5</v>
-      </c>
       <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
         <v>6</v>
       </c>
-      <c r="H50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.5</v>
+      <c r="K50" t="n">
+        <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -4145,13 +4154,16 @@
       <c r="Q50" t="n">
         <v>1</v>
       </c>
-      <c r="S50" t="n">
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
+      <c r="Z50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
@@ -4159,7 +4171,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -4171,7 +4183,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4180,13 +4192,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
-      </c>
-      <c r="E51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
         <v>8</v>
@@ -4195,25 +4204,22 @@
         <v>6</v>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K51" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" t="n">
         <v>4</v>
       </c>
-      <c r="L51" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M51" t="n">
-        <v>7</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
@@ -4239,27 +4245,24 @@
       <c r="V51" t="n">
         <v>1</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1</v>
-      </c>
       <c r="AF51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4268,31 +4271,55 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G52" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L52" t="n">
         <v>4</v>
       </c>
+      <c r="M52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
-      <c r="T52" t="n">
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4308,7 +4335,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4317,35 +4344,74 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
         <v>8</v>
       </c>
-      <c r="D53" t="n">
-        <v>8</v>
-      </c>
       <c r="G53" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
         <v>7</v>
       </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
       <c r="J53" t="n">
         <v>7</v>
       </c>
+      <c r="K53" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M53" t="n">
+        <v>7</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
       <c r="S53" t="n">
         <v>1</v>
       </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1</v>
+      </c>
       <c r="AF53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -4357,7 +4423,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4366,55 +4432,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F54" t="n">
+        <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
-      </c>
-      <c r="M54" t="n">
-        <v>7</v>
-      </c>
-      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4430,7 +4472,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4439,27 +4481,27 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" t="n">
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>6</v>
-      </c>
-      <c r="M55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H55" t="n">
         <v>7</v>
       </c>
-      <c r="N55" t="n">
-        <v>1</v>
+      <c r="J55" t="n">
+        <v>7</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
-      <c r="V55" t="n">
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
@@ -4479,7 +4521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4488,33 +4530,33 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
         <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>4.5</v>
       </c>
       <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" t="n">
         <v>7</v>
       </c>
-      <c r="M56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O56" t="n">
+      <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="P56" t="n">
@@ -4536,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4552,7 +4594,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4566,75 +4608,42 @@
       <c r="D57" t="n">
         <v>2</v>
       </c>
-      <c r="F57" t="n">
+      <c r="E57" t="n">
         <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>6</v>
       </c>
-      <c r="H57" t="n">
-        <v>5</v>
-      </c>
-      <c r="I57" t="n">
-        <v>5</v>
-      </c>
-      <c r="J57" t="n">
-        <v>7</v>
-      </c>
-      <c r="K57" t="n">
-        <v>5</v>
-      </c>
-      <c r="L57" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M57" t="n">
         <v>7</v>
       </c>
-      <c r="O57" t="n">
+      <c r="N57" t="n">
         <v>1</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="Z57" t="n">
-        <v>1</v>
-      </c>
       <c r="AF57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4643,27 +4652,27 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>8.5</v>
+        <v>8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
-      </c>
-      <c r="M58" t="n">
+        <v>4</v>
+      </c>
+      <c r="J58" t="n">
         <v>7</v>
       </c>
-      <c r="P58" t="n">
+      <c r="O58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="V58" t="n">
+      <c r="S58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
@@ -4683,7 +4692,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4692,10 +4701,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
         <v>8</v>
@@ -4704,16 +4713,16 @@
         <v>6</v>
       </c>
       <c r="H59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4.5</v>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
-      </c>
-      <c r="L59" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M59" t="n">
         <v>2.5</v>
@@ -4730,20 +4739,17 @@
       <c r="R59" t="n">
         <v>1</v>
       </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
-      <c r="U59" t="n">
-        <v>1</v>
-      </c>
       <c r="V59" t="n">
         <v>1</v>
       </c>
-      <c r="Z59" t="n">
-        <v>1</v>
-      </c>
       <c r="AF59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4759,7 +4765,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4768,28 +4774,34 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G60" t="n">
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" t="n">
         <v>7</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5</v>
       </c>
       <c r="L60" t="n">
         <v>7.5</v>
       </c>
       <c r="M60" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -4803,30 +4815,39 @@
       <c r="R60" t="n">
         <v>1</v>
       </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
+      <c r="Z60" t="n">
+        <v>1</v>
+      </c>
       <c r="AF60" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4835,65 +4856,35 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
-      </c>
-      <c r="F61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
-      </c>
-      <c r="H61" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="I61" t="n">
         <v>8</v>
       </c>
-      <c r="J61" t="n">
-        <v>7</v>
-      </c>
-      <c r="K61" t="n">
-        <v>7</v>
-      </c>
-      <c r="L61" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M61" t="n">
         <v>7</v>
       </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
       <c r="P61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
       <c r="R61" t="n">
         <v>1</v>
       </c>
-      <c r="S61" t="n">
-        <v>1</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
       <c r="V61" t="n">
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4905,7 +4896,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4922,23 +4913,50 @@
       <c r="F62" t="n">
         <v>8</v>
       </c>
+      <c r="G62" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" t="n">
+        <v>4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3</v>
+      </c>
       <c r="K62" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.5</v>
       </c>
       <c r="M62" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
+      <c r="Z62" t="n">
+        <v>1</v>
+      </c>
       <c r="AF62" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4947,14 +4965,14 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4963,41 +4981,29 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" t="n">
         <v>4</v>
       </c>
-      <c r="F63" t="n">
-        <v>8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2</v>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M63" t="n">
         <v>2.5</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
@@ -5010,12 +5016,6 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
@@ -5060,19 +5060,22 @@
         <v>6</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I64" t="n">
         <v>8</v>
       </c>
       <c r="J64" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="L64" t="n">
+        <v>7.5</v>
       </c>
       <c r="M64" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5092,15 +5095,18 @@
       <c r="T64" t="n">
         <v>1</v>
       </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
       <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -5112,7 +5118,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5121,67 +5127,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
-      <c r="G65" t="n">
-        <v>2</v>
-      </c>
-      <c r="H65" t="n">
-        <v>3</v>
-      </c>
-      <c r="I65" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K65" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
-      <c r="U65" t="n">
-        <v>1</v>
-      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5190,14 +5160,14 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5206,22 +5176,43 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K66" t="n">
         <v>3</v>
       </c>
-      <c r="K66" t="n">
-        <v>7</v>
+      <c r="L66" t="n">
+        <v>4</v>
       </c>
       <c r="M66" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -5232,33 +5223,36 @@
       <c r="R66" t="n">
         <v>1</v>
       </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
-      <c r="Z66" t="n">
-        <v>1</v>
-      </c>
       <c r="AF66" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5267,37 +5261,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
         <v>6</v>
       </c>
       <c r="H67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
         <v>8</v>
       </c>
       <c r="J67" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -5325,7 +5313,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
@@ -5337,7 +5325,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5351,27 +5339,36 @@
       <c r="D68" t="n">
         <v>4</v>
       </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K68" t="n">
         <v>3</v>
       </c>
+      <c r="L68" t="n">
+        <v>4</v>
+      </c>
       <c r="M68" t="n">
         <v>2.5</v>
       </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
@@ -5388,6 +5385,9 @@
         <v>1</v>
       </c>
       <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
         <v>1</v>
       </c>
       <c r="V68" t="n">
@@ -5410,7 +5410,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5419,40 +5419,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
-      </c>
-      <c r="D69" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
@@ -5463,33 +5445,33 @@
       <c r="R69" t="n">
         <v>1</v>
       </c>
-      <c r="S69" t="n">
-        <v>1</v>
-      </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>1</v>
       </c>
+      <c r="Z69" t="n">
+        <v>1</v>
+      </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5498,29 +5480,38 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
       </c>
       <c r="F70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>7</v>
+      </c>
+      <c r="I70" t="n">
+        <v>8</v>
+      </c>
+      <c r="J70" t="n">
         <v>2.5</v>
       </c>
-      <c r="G70" t="n">
-        <v>2</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L70" t="n">
+      <c r="K70" t="n">
         <v>4</v>
       </c>
       <c r="M70" t="n">
         <v>2.5</v>
       </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
@@ -5530,24 +5521,24 @@
       <c r="Q70" t="n">
         <v>1</v>
       </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
       <c r="S70" t="n">
         <v>1</v>
       </c>
-      <c r="U70" t="n">
+      <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="V70" t="n">
         <v>1</v>
       </c>
-      <c r="Z70" t="n">
-        <v>1</v>
-      </c>
       <c r="AF70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -5559,7 +5550,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5568,10 +5559,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F71" t="n">
         <v>5</v>
@@ -5583,7 +5574,7 @@
         <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J71" t="n">
         <v>2.5</v>
@@ -5592,7 +5583,7 @@
         <v>3</v>
       </c>
       <c r="M71" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -5615,11 +5606,8 @@
       <c r="V71" t="n">
         <v>1</v>
       </c>
-      <c r="Z71" t="n">
-        <v>1</v>
-      </c>
       <c r="AF71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -5635,7 +5623,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5644,26 +5632,41 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2.5</v>
       </c>
       <c r="K72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M72" t="n">
         <v>2.5</v>
       </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
@@ -5673,6 +5676,9 @@
       <c r="R72" t="n">
         <v>1</v>
       </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
@@ -5680,11 +5686,11 @@
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
@@ -5696,7 +5702,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5705,31 +5711,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
-      </c>
-      <c r="I73" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>7</v>
-      </c>
-      <c r="K73" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L73" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M73" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5737,27 +5740,27 @@
       <c r="P73" t="n">
         <v>1</v>
       </c>
-      <c r="R73" t="n">
+      <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
       </c>
-      <c r="T73" t="n">
-        <v>1</v>
-      </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
       <c r="V73" t="n">
         <v>1</v>
       </c>
+      <c r="Z73" t="n">
+        <v>1</v>
+      </c>
       <c r="AF73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -5769,7 +5772,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5778,76 +5781,52 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>6</v>
+      </c>
+      <c r="H74" t="n">
         <v>4</v>
-      </c>
-      <c r="D74" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" t="n">
-        <v>8</v>
-      </c>
-      <c r="G74" t="n">
-        <v>3</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2</v>
-      </c>
-      <c r="I74" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K74" t="n">
-        <v>3</v>
       </c>
       <c r="M74" t="n">
         <v>7</v>
       </c>
-      <c r="O74" t="n">
-        <v>1</v>
-      </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
-      <c r="S74" t="n">
-        <v>1</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1</v>
-      </c>
       <c r="V74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -5856,33 +5835,27 @@
       <c r="D75" t="n">
         <v>2</v>
       </c>
-      <c r="E75" t="n">
-        <v>2</v>
-      </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
         <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
         <v>2</v>
       </c>
       <c r="J75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" t="n">
         <v>4.5</v>
       </c>
-      <c r="L75" t="n">
-        <v>4</v>
-      </c>
-      <c r="M75" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1</v>
-      </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
@@ -5898,18 +5871,21 @@
       <c r="S75" t="n">
         <v>1</v>
       </c>
-      <c r="U75" t="n">
+      <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="V75" t="n">
         <v>1</v>
       </c>
+      <c r="Z75" t="n">
+        <v>1</v>
+      </c>
       <c r="AF75" t="n">
         <v>2</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -5921,25 +5897,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
         <v>6</v>
       </c>
+      <c r="H76" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>5</v>
+      </c>
       <c r="K76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M76" t="n">
         <v>2.5</v>
@@ -5947,6 +5929,12 @@
       <c r="P76" t="n">
         <v>1</v>
       </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
@@ -5954,65 +5942,56 @@
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Gravedad: atracción hacia la Tierra</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
-      </c>
-      <c r="E77" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F77" t="n">
         <v>8</v>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
-      </c>
-      <c r="H77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J77" t="n">
         <v>7</v>
       </c>
       <c r="K77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L77" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -6020,9 +5999,6 @@
       <c r="P77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
-        <v>1</v>
-      </c>
       <c r="R77" t="n">
         <v>1</v>
       </c>
@@ -6039,52 +6015,76 @@
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
       </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="M78" t="n">
         <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
       <c r="R78" t="n">
         <v>1</v>
       </c>
       <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
@@ -6092,68 +6092,50 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Aplicaciones de las leyes de Newton</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
-      </c>
-      <c r="G79" t="n">
-        <v>6</v>
-      </c>
-      <c r="H79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="n">
-        <v>7</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>1</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1</v>
-      </c>
       <c r="AF79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Aplicaciones de las leyes de Newton</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6162,13 +6144,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6184,7 +6166,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Observación astronómica en distintas longitudes de onda</t>
+          <t>Campo eléctrico</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6193,13 +6175,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8</v>
+      </c>
+      <c r="G81" t="n">
+        <v>6</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
       </c>
       <c r="AF81" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
@@ -6215,7 +6209,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Campo eléctrico</t>
+          <t>Capacitancia y condensadores</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6224,25 +6218,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
-      </c>
-      <c r="F82" t="n">
-        <v>8</v>
-      </c>
-      <c r="G82" t="n">
-        <v>6</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6258,7 +6240,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Capacitancia y condensadores</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6267,13 +6249,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
       </c>
       <c r="AF83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
@@ -6289,7 +6277,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6298,23 +6286,32 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2</v>
-      </c>
-      <c r="K84" t="n">
-        <v>2</v>
-      </c>
-      <c r="T84" t="n">
+        <v>9</v>
+      </c>
+      <c r="G84" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I84" t="n">
+        <v>7</v>
+      </c>
+      <c r="M84" t="n">
+        <v>7</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" t="n">
         <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -6326,7 +6323,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Cuantización de la energía</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6335,32 +6332,17 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
-      </c>
-      <c r="G85" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I85" t="n">
         <v>7</v>
       </c>
-      <c r="M85" t="n">
+      <c r="D85" t="n">
         <v>7</v>
       </c>
-      <c r="P85" t="n">
-        <v>1</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
       <c r="AF85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -6372,7 +6354,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cuantización de la energía</t>
+          <t>Desintegración radiactiva</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6381,17 +6363,32 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
-      </c>
-      <c r="D86" t="n">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
+        <v>8</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+      <c r="G86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
       </c>
       <c r="AF86" t="n">
         <v>11</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -6403,7 +6400,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Desintegración radiactiva</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6417,23 +6414,11 @@
       <c r="E87" t="n">
         <v>8</v>
       </c>
-      <c r="F87" t="n">
-        <v>8</v>
-      </c>
-      <c r="G87" t="n">
-        <v>8.5</v>
-      </c>
       <c r="N87" t="n">
         <v>1</v>
       </c>
-      <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
       <c r="AF87" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -6449,7 +6434,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6458,20 +6443,17 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
-      </c>
-      <c r="E88" t="n">
         <v>8</v>
       </c>
-      <c r="N88" t="n">
-        <v>1</v>
+      <c r="D88" t="n">
+        <v>8</v>
       </c>
       <c r="AF88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
@@ -6483,7 +6465,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6492,13 +6474,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -5424,9 +5424,6 @@
       <c r="G69" t="n">
         <v>8.5</v>
       </c>
-      <c r="H69" t="n">
-        <v>7</v>
-      </c>
       <c r="I69" t="n">
         <v>3</v>
       </c>
@@ -5439,9 +5436,6 @@
       <c r="P69" t="n">
         <v>1</v>
       </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
       <c r="R69" t="n">
         <v>1</v>
       </c>
@@ -5464,7 +5458,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
@@ -7424,9 +7418,6 @@
       <c r="G110" t="n">
         <v>6</v>
       </c>
-      <c r="H110" t="n">
-        <v>7</v>
-      </c>
       <c r="J110" t="n">
         <v>2.5</v>
       </c>
@@ -7436,13 +7427,13 @@
       <c r="P110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>1</v>
-      </c>
       <c r="S110" t="n">
         <v>1</v>
       </c>
       <c r="V110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -909,9 +909,6 @@
       <c r="J6" t="n">
         <v>7</v>
       </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
       <c r="L6" t="n">
         <v>7.5</v>
       </c>
@@ -933,9 +930,6 @@
       <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
@@ -985,9 +979,6 @@
       <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
       <c r="M7" t="n">
         <v>7</v>
       </c>
@@ -1000,9 +991,6 @@
       <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
@@ -1053,7 +1041,7 @@
         <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>7.5</v>
@@ -1138,7 +1126,7 @@
         <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
@@ -1193,7 +1181,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>Energía potencial gravitatoria y elástica</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,10 +1190,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
@@ -1222,8 +1210,11 @@
       <c r="J10" t="n">
         <v>7</v>
       </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
@@ -1238,6 +1229,9 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="n">
@@ -1260,7 +1254,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1269,55 +1263,61 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>7</v>
       </c>
       <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1347,32 +1347,29 @@
       <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1383,6 +1380,9 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
@@ -1393,6 +1393,9 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
@@ -1412,7 +1415,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1421,35 +1424,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
       </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O13" t="n">
         <v>1</v>
       </c>
@@ -1459,26 +1450,11 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1487,14 +1463,14 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1508,8 +1484,8 @@
       <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="F14" t="n">
-        <v>8</v>
+      <c r="E14" t="n">
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -1517,10 +1493,19 @@
       <c r="H14" t="n">
         <v>7</v>
       </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
       <c r="J14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
@@ -1529,11 +1514,20 @@
       <c r="Q14" t="n">
         <v>1</v>
       </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -1549,7 +1543,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1558,71 +1552,53 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" t="n">
         <v>6</v>
       </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
       <c r="G15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
         <v>6</v>
       </c>
-      <c r="H15" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>7</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>5</v>
-      </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1631,41 +1607,53 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K16" t="n">
         <v>8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>7.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
+      <c r="M16" t="n">
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
       <c r="AF16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -1677,7 +1665,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1686,35 +1674,53 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
         <v>5</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M17" t="n">
         <v>2.5</v>
       </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
@@ -1728,68 +1734,53 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
       <c r="L18" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -1797,9 +1788,6 @@
       <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
@@ -1813,11 +1801,11 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -1829,7 +1817,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1838,28 +1826,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>7</v>
       </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
       <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -1867,12 +1867,12 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
@@ -1880,11 +1880,11 @@
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Calor latente</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1905,38 +1905,20 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H20" t="n">
         <v>7</v>
       </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
@@ -1946,20 +1928,8 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1968,14 +1938,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calor latente</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1984,20 +1954,38 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
         <v>7</v>
       </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
@@ -2007,8 +1995,20 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
       <c r="AF21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2045,22 +2045,25 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
       <c r="J22" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -2074,6 +2077,9 @@
       <c r="Q22" t="n">
         <v>1</v>
       </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
@@ -2086,24 +2092,27 @@
       <c r="V22" t="n">
         <v>1</v>
       </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
       <c r="AF22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2112,16 +2121,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -2130,19 +2139,16 @@
         <v>2</v>
       </c>
       <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4</v>
-      </c>
       <c r="M23" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
@@ -2162,20 +2168,14 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2200,37 +2200,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2241,9 +2232,6 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
@@ -2254,23 +2242,23 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2279,28 +2267,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
       </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2311,7 +2305,13 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
       <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -2337,7 +2337,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2351,6 +2351,9 @@
       <c r="D26" t="n">
         <v>4</v>
       </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
@@ -2358,10 +2361,10 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
@@ -2375,6 +2378,9 @@
       <c r="M26" t="n">
         <v>2.5</v>
       </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2400,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2416,7 +2422,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2425,83 +2431,83 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
       </c>
       <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
         <v>5</v>
       </c>
-      <c r="L27" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>4</v>
-      </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,83 +2516,77 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" t="n">
         <v>7</v>
       </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>5</v>
-      </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2603,9 +2603,6 @@
       <c r="F29" t="n">
         <v>8</v>
       </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
       <c r="H29" t="n">
         <v>7</v>
       </c>
@@ -2613,13 +2610,13 @@
         <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
         <v>7</v>
@@ -2627,9 +2624,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
@@ -2665,7 +2659,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2682,27 +2676,30 @@
       <c r="F30" t="n">
         <v>8</v>
       </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" t="n">
-        <v>6</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4</v>
-      </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
@@ -2710,9 +2707,6 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
@@ -2738,7 +2732,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Energía cinética</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2747,33 +2741,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
         <v>4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3</v>
       </c>
       <c r="M31" t="n">
         <v>4.5</v>
       </c>
-      <c r="O31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="P31" t="n">
@@ -2788,18 +2782,18 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -2844,7 +2838,7 @@
         <v>4.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2887,7 +2881,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -3060,7 +3054,7 @@
         <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -3139,7 +3133,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
         <v>3</v>
@@ -3170,7 +3164,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -4009,7 +4003,7 @@
         <v>2.5</v>
       </c>
       <c r="K48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
         <v>4.5</v>
@@ -4213,7 +4207,7 @@
         <v>4.5</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -4255,7 +4249,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4545,7 @@
         <v>4.5</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
         <v>7</v>
@@ -4722,7 +4716,7 @@
         <v>4.5</v>
       </c>
       <c r="K59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>2.5</v>
@@ -5282,7 +5276,7 @@
         <v>4.5</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
         <v>4.5</v>
@@ -5786,6 +5780,9 @@
       <c r="H74" t="n">
         <v>4</v>
       </c>
+      <c r="K74" t="n">
+        <v>4</v>
+      </c>
       <c r="M74" t="n">
         <v>7</v>
       </c>
@@ -5795,6 +5792,9 @@
       <c r="Q74" t="n">
         <v>1</v>
       </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
       <c r="V74" t="n">
         <v>1</v>
       </c>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -6055,7 +6055,7 @@
         <v>2.5</v>
       </c>
       <c r="K78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
         <v>7</v>
@@ -6477,7 +6477,7 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M89" t="n">
         <v>2.5</v>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH132"/>
+  <dimension ref="A1:AH129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6203,7 +6203,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Capacitancia y condensadores</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6212,13 +6212,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
       </c>
       <c r="AF82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6234,7 +6240,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6243,23 +6249,32 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
-      </c>
-      <c r="D83" t="n">
-        <v>2</v>
-      </c>
-      <c r="K83" t="n">
-        <v>2</v>
-      </c>
-      <c r="T83" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I83" t="n">
+        <v>7</v>
+      </c>
+      <c r="M83" t="n">
+        <v>7</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
         <v>1</v>
       </c>
       <c r="AF83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -6271,7 +6286,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Desintegración radiactiva</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6280,28 +6295,28 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E84" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
       </c>
       <c r="G84" t="n">
         <v>8.5</v>
       </c>
-      <c r="I84" t="n">
-        <v>7</v>
-      </c>
-      <c r="M84" t="n">
-        <v>7</v>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
       </c>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
-      <c r="V84" t="n">
-        <v>1</v>
-      </c>
       <c r="AF84" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6317,7 +6332,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cuantización de la energía</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6326,17 +6341,20 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
-      </c>
-      <c r="D85" t="n">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>8</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -6348,7 +6366,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Desintegración radiactiva</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6357,32 +6375,17 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
-      </c>
-      <c r="E86" t="n">
         <v>8</v>
       </c>
-      <c r="F86" t="n">
+      <c r="D86" t="n">
         <v>8</v>
-      </c>
-      <c r="G86" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1</v>
       </c>
       <c r="AF86" t="n">
         <v>11</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -6394,7 +6397,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6403,32 +6406,47 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
-      </c>
-      <c r="E87" t="n">
-        <v>8</v>
-      </c>
-      <c r="N87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6</v>
+      </c>
+      <c r="K87" t="n">
+        <v>2</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+      <c r="V87" t="n">
         <v>1</v>
       </c>
       <c r="AF87" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Defecto de masa y energía de enlace nuclear</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6437,17 +6455,20 @@
         </is>
       </c>
       <c r="C88" t="n">
+        <v>11</v>
+      </c>
+      <c r="F88" t="n">
         <v>8</v>
       </c>
-      <c r="D88" t="n">
-        <v>8</v>
+      <c r="O88" t="n">
+        <v>1</v>
       </c>
       <c r="AF88" t="n">
         <v>11</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
@@ -6459,7 +6480,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Espejos esféricos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6468,47 +6489,56 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
-      </c>
-      <c r="D89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="n">
-        <v>6</v>
-      </c>
-      <c r="K89" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F89" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
+      <c r="L89" t="n">
+        <v>7.5</v>
       </c>
       <c r="M89" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P89" t="n">
-        <v>1</v>
-      </c>
-      <c r="T89" t="n">
+        <v>7</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
         <v>1</v>
       </c>
       <c r="V89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Defecto de masa y energía de enlace nuclear</t>
+          <t>Fisión y fusión nuclear</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6522,7 +6552,19 @@
       <c r="F90" t="n">
         <v>8</v>
       </c>
+      <c r="L90" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>7</v>
+      </c>
       <c r="O90" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
+      </c>
+      <c r="V90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
@@ -6542,7 +6584,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Espejos esféricos</t>
+          <t>Fotón y efecto fotoeléctrico</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6553,34 +6595,16 @@
       <c r="C91" t="n">
         <v>10</v>
       </c>
-      <c r="F91" t="n">
+      <c r="E91" t="n">
         <v>8</v>
       </c>
-      <c r="H91" t="n">
-        <v>5</v>
-      </c>
-      <c r="J91" t="n">
-        <v>7</v>
-      </c>
-      <c r="L91" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M91" t="n">
-        <v>7</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>1</v>
-      </c>
-      <c r="S91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
+      <c r="G91" t="n">
+        <v>6</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
@@ -6593,14 +6617,14 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Fisión y fusión nuclear</t>
+          <t>Inducción electromagnética: Faraday y Lenz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6609,13 +6633,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
       </c>
-      <c r="L92" t="n">
-        <v>7.5</v>
+      <c r="G92" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5</v>
       </c>
       <c r="M92" t="n">
         <v>7</v>
@@ -6623,18 +6653,21 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="U92" t="n">
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
         <v>1</v>
       </c>
       <c r="V92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -6646,7 +6679,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Fotón y efecto fotoeléctrico</t>
+          <t>Ley de Coulomb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6655,38 +6688,59 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" t="n">
         <v>8</v>
       </c>
       <c r="G93" t="n">
         <v>6</v>
       </c>
-      <c r="N93" t="n">
+      <c r="I93" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" t="n">
+        <v>7</v>
+      </c>
+      <c r="M93" t="n">
+        <v>7</v>
+      </c>
+      <c r="O93" t="n">
         <v>1</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
       </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1</v>
+      </c>
       <c r="AF93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Inducción electromagnética: Faraday y Lenz</t>
+          <t>Leyes de Kepler</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6700,32 +6754,8 @@
       <c r="D94" t="n">
         <v>4</v>
       </c>
-      <c r="F94" t="n">
-        <v>8</v>
-      </c>
-      <c r="G94" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I94" t="n">
-        <v>5</v>
-      </c>
-      <c r="M94" t="n">
-        <v>7</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
-      <c r="R94" t="n">
-        <v>1</v>
-      </c>
-      <c r="V94" t="n">
-        <v>1</v>
-      </c>
       <c r="AF94" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -6741,7 +6771,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ley de Coulomb</t>
+          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6750,13 +6780,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
-      </c>
-      <c r="D95" t="n">
-        <v>3</v>
-      </c>
-      <c r="F95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G95" t="n">
         <v>6</v>
@@ -6764,45 +6788,30 @@
       <c r="I95" t="n">
         <v>7</v>
       </c>
-      <c r="J95" t="n">
-        <v>7</v>
-      </c>
-      <c r="M95" t="n">
-        <v>7</v>
-      </c>
-      <c r="O95" t="n">
-        <v>1</v>
-      </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
       <c r="R95" t="n">
         <v>1</v>
       </c>
-      <c r="S95" t="n">
-        <v>1</v>
-      </c>
-      <c r="V95" t="n">
-        <v>1</v>
-      </c>
       <c r="AF95" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Leyes de Kepler</t>
+          <t>Núcleo atómico e isótopos</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6811,17 +6820,26 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
-      </c>
-      <c r="D96" t="n">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
       </c>
       <c r="AF96" t="n">
         <v>11</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
@@ -6833,7 +6851,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
+          <t>Ondas electromagnéticas y espectro</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6842,22 +6860,43 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>8</v>
       </c>
       <c r="G97" t="n">
         <v>6</v>
       </c>
-      <c r="I97" t="n">
+      <c r="H97" t="n">
         <v>7</v>
       </c>
+      <c r="L97" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
       <c r="P97" t="n">
         <v>1</v>
       </c>
-      <c r="R97" t="n">
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z97" t="n">
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -6866,14 +6905,14 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Modelo estándar de partículas</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6882,17 +6921,35 @@
         </is>
       </c>
       <c r="C98" t="n">
+        <v>11</v>
+      </c>
+      <c r="G98" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H98" t="n">
         <v>7</v>
       </c>
-      <c r="D98" t="n">
-        <v>7</v>
+      <c r="M98" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1</v>
       </c>
       <c r="AF98" t="n">
         <v>11</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
@@ -6904,7 +6961,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Núcleo atómico e isótopos</t>
+          <t>Energía potencial y potencial eléctrico</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6913,18 +6970,21 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>11</v>
-      </c>
-      <c r="F99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="n">
         <v>8</v>
       </c>
       <c r="G99" t="n">
         <v>8.5</v>
       </c>
-      <c r="O99" t="n">
-        <v>1</v>
+      <c r="H99" t="n">
+        <v>7</v>
       </c>
       <c r="P99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="n">
         <v>1</v>
       </c>
       <c r="AF99" t="n">
@@ -6932,7 +6992,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
@@ -6944,7 +7004,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro</t>
+          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6953,13 +7013,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F100" t="n">
         <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H100" t="n">
         <v>7</v>
@@ -6967,9 +7027,6 @@
       <c r="L100" t="n">
         <v>7.5</v>
       </c>
-      <c r="M100" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O100" t="n">
         <v>1</v>
       </c>
@@ -6982,14 +7039,11 @@
       <c r="U100" t="n">
         <v>1</v>
       </c>
-      <c r="V100" t="n">
-        <v>1</v>
-      </c>
       <c r="Z100" t="n">
         <v>1</v>
       </c>
       <c r="AF100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
@@ -6998,14 +7052,14 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ondas de radio y telecomunicaciones</t>
+          <t>Radiación térmica y cuerpo negro</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7014,31 +7068,34 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
-      </c>
-      <c r="G101" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="H101" t="n">
         <v>7</v>
       </c>
-      <c r="M101" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P101" t="n">
-        <v>1</v>
+      <c r="J101" t="n">
+        <v>7</v>
+      </c>
+      <c r="K101" t="n">
+        <v>6</v>
+      </c>
+      <c r="L101" t="n">
+        <v>7.5</v>
       </c>
       <c r="Q101" t="n">
         <v>1</v>
       </c>
-      <c r="V101" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z101" t="n">
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
         <v>1</v>
       </c>
       <c r="AF101" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -7054,7 +7111,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Energía potencial y potencial eléctrico</t>
+          <t>Rapidez de la luz</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7063,21 +7120,33 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
-      </c>
-      <c r="D102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G102" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H102" t="n">
         <v>7</v>
       </c>
+      <c r="L102" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M102" t="n">
+        <v>7</v>
+      </c>
       <c r="P102" t="n">
         <v>1</v>
       </c>
       <c r="Q102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z102" t="n">
         <v>1</v>
       </c>
       <c r="AF102" t="n">
@@ -7085,7 +7154,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
@@ -7097,7 +7166,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
+          <t>Reflexión interna total</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7106,37 +7175,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
-      </c>
-      <c r="F103" t="n">
-        <v>8</v>
-      </c>
-      <c r="G103" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="H103" t="n">
         <v>7</v>
       </c>
-      <c r="L103" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
-      <c r="P103" t="n">
-        <v>1</v>
-      </c>
       <c r="Q103" t="n">
         <v>1</v>
       </c>
-      <c r="U103" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>1</v>
-      </c>
       <c r="AF103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
@@ -7152,7 +7200,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Radiación térmica y cuerpo negro</t>
+          <t>Segunda ley de la termodinámica</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7161,38 +7209,23 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
-      </c>
-      <c r="H104" t="n">
-        <v>7</v>
-      </c>
-      <c r="J104" t="n">
-        <v>7</v>
-      </c>
-      <c r="K104" t="n">
-        <v>6</v>
-      </c>
-      <c r="L104" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>1</v>
-      </c>
-      <c r="S104" t="n">
-        <v>1</v>
-      </c>
-      <c r="T104" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
@@ -7204,7 +7237,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Rapidez de la luz</t>
+          <t>Semiconductores y electrónica básica</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7213,37 +7246,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
-      </c>
-      <c r="G105" t="n">
-        <v>6</v>
-      </c>
-      <c r="H105" t="n">
+        <v>9</v>
+      </c>
+      <c r="J105" t="n">
         <v>7</v>
       </c>
-      <c r="L105" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M105" t="n">
-        <v>7</v>
-      </c>
-      <c r="P105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>1</v>
-      </c>
-      <c r="U105" t="n">
-        <v>1</v>
-      </c>
-      <c r="V105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z105" t="n">
+      <c r="S105" t="n">
         <v>1</v>
       </c>
       <c r="AF105" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
@@ -7259,7 +7271,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Reflexión interna total</t>
+          <t>Superposición e interferencia de ondas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7268,23 +7280,20 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
-      </c>
-      <c r="D106" t="n">
-        <v>8</v>
-      </c>
-      <c r="H106" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q106" t="n">
+        <v>10</v>
+      </c>
+      <c r="G106" t="n">
+        <v>6</v>
+      </c>
+      <c r="P106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -7296,7 +7305,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Segunda ley de la termodinámica</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7305,19 +7314,34 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G107" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M107" t="n">
+        <v>4.5</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="V107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1</v>
+      </c>
       <c r="AF107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -7333,7 +7357,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Semiconductores y electrónica básica</t>
+          <t>Viscosidad y régimen de flujo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7344,10 +7368,10 @@
       <c r="C108" t="n">
         <v>9</v>
       </c>
-      <c r="J108" t="n">
+      <c r="K108" t="n">
         <v>7</v>
       </c>
-      <c r="S108" t="n">
+      <c r="T108" t="n">
         <v>1</v>
       </c>
       <c r="AF108" t="n">
@@ -7367,46 +7391,49 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Superposición e interferencia de ondas</t>
+          <t>Aceleración y fuerza centrípeta</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
-      </c>
-      <c r="G109" t="n">
-        <v>6</v>
-      </c>
-      <c r="P109" t="n">
+        <v>5</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+      <c r="M109" t="n">
+        <v>7</v>
+      </c>
+      <c r="V109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Colisiones elásticas e inelásticas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -7416,24 +7443,9 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>6</v>
-      </c>
-      <c r="J110" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M110" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="S110" t="n">
-        <v>1</v>
-      </c>
-      <c r="V110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">
@@ -7453,41 +7465,38 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Viscosidad y régimen de flujo</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
-      </c>
-      <c r="K111" t="n">
-        <v>7</v>
-      </c>
-      <c r="T111" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
       </c>
       <c r="AF111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Aceleración y fuerza centrípeta</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7501,14 +7510,26 @@
       <c r="D112" t="n">
         <v>5</v>
       </c>
-      <c r="M112" t="n">
+      <c r="H112" t="n">
+        <v>4</v>
+      </c>
+      <c r="J112" t="n">
         <v>7</v>
       </c>
-      <c r="V112" t="n">
+      <c r="K112" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
         <v>1</v>
       </c>
       <c r="AF112" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -7517,14 +7538,14 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Colisiones elásticas e inelásticas</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7533,19 +7554,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D113" t="n">
-        <v>8</v>
-      </c>
-      <c r="G113" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -7554,14 +7569,14 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7575,6 +7590,18 @@
       <c r="D114" t="n">
         <v>8</v>
       </c>
+      <c r="H114" t="n">
+        <v>7</v>
+      </c>
+      <c r="M114" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1</v>
+      </c>
       <c r="AF114" t="n">
         <v>8</v>
       </c>
@@ -7592,7 +7619,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Movimiento armónico simple</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7601,32 +7628,26 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
-      </c>
-      <c r="H115" t="n">
+        <v>8</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8</v>
+      </c>
+      <c r="I115" t="n">
         <v>4</v>
       </c>
-      <c r="J115" t="n">
-        <v>7</v>
-      </c>
-      <c r="K115" t="n">
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="n">
         <v>8</v>
       </c>
-      <c r="Q115" t="n">
-        <v>1</v>
-      </c>
-      <c r="S115" t="n">
-        <v>1</v>
-      </c>
-      <c r="T115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF115" t="n">
-        <v>5</v>
-      </c>
       <c r="AG115" t="inlineStr">
         <is>
           <t>sin_referente</t>
@@ -7634,14 +7655,14 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Movimiento circular y variables angulares</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7655,6 +7676,24 @@
       <c r="D116" t="n">
         <v>5</v>
       </c>
+      <c r="G116" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" t="n">
+        <v>7</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="n">
+        <v>1</v>
+      </c>
       <c r="AF116" t="n">
         <v>5</v>
       </c>
@@ -7665,14 +7704,14 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Cinemática en dos dimensiones y proyectiles</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7686,16 +7725,10 @@
       <c r="D117" t="n">
         <v>8</v>
       </c>
-      <c r="H117" t="n">
-        <v>7</v>
-      </c>
-      <c r="M117" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>1</v>
-      </c>
-      <c r="V117" t="n">
+      <c r="G117" t="n">
+        <v>6</v>
+      </c>
+      <c r="P117" t="n">
         <v>1</v>
       </c>
       <c r="AF117" t="n">
@@ -7715,7 +7748,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Movimiento armónico simple</t>
+          <t>Niveles de energía atómicos y espectros</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7724,25 +7757,19 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D118" t="n">
-        <v>8</v>
-      </c>
-      <c r="F118" t="n">
-        <v>8</v>
-      </c>
-      <c r="I118" t="n">
-        <v>4</v>
-      </c>
-      <c r="O118" t="n">
-        <v>1</v>
-      </c>
-      <c r="R118" t="n">
+        <v>5</v>
+      </c>
+      <c r="G118" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P118" t="n">
         <v>1</v>
       </c>
       <c r="AF118" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
@@ -7751,14 +7778,14 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Movimiento circular y variables angulares</t>
+          <t>Ondas estacionarias y armónicos</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7767,31 +7794,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
-      </c>
-      <c r="G119" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K119" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="H119" t="n">
+        <v>7</v>
       </c>
       <c r="M119" t="n">
         <v>7</v>
       </c>
-      <c r="P119" t="n">
-        <v>1</v>
-      </c>
-      <c r="T119" t="n">
+      <c r="Q119" t="n">
         <v>1</v>
       </c>
       <c r="V119" t="n">
         <v>1</v>
       </c>
       <c r="AF119" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -7800,14 +7821,14 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cinemática en dos dimensiones y proyectiles</t>
+          <t>Órbitas y satélites</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7821,14 +7842,8 @@
       <c r="D120" t="n">
         <v>8</v>
       </c>
-      <c r="G120" t="n">
-        <v>6</v>
-      </c>
-      <c r="P120" t="n">
-        <v>1</v>
-      </c>
       <c r="AF120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -7837,14 +7852,14 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Niveles de energía atómicos y espectros</t>
+          <t>Hidrodinámica: continuidad y Bernoulli</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7853,19 +7868,25 @@
         </is>
       </c>
       <c r="C121" t="n">
+        <v>6</v>
+      </c>
+      <c r="D121" t="n">
+        <v>6</v>
+      </c>
+      <c r="H121" t="n">
+        <v>7</v>
+      </c>
+      <c r="K121" t="n">
         <v>5</v>
       </c>
-      <c r="D121" t="n">
-        <v>5</v>
-      </c>
-      <c r="G121" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P121" t="n">
+      <c r="Q121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="n">
         <v>1</v>
       </c>
       <c r="AF121" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -7874,14 +7895,14 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ondas estacionarias y armónicos</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7890,21 +7911,33 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D122" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>6</v>
       </c>
       <c r="H122" t="n">
         <v>7</v>
       </c>
-      <c r="M122" t="n">
+      <c r="I122" t="n">
+        <v>8</v>
+      </c>
+      <c r="J122" t="n">
         <v>7</v>
       </c>
+      <c r="P122" t="n">
+        <v>1</v>
+      </c>
       <c r="Q122" t="n">
         <v>1</v>
       </c>
-      <c r="V122" t="n">
+      <c r="R122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S122" t="n">
         <v>1</v>
       </c>
       <c r="AF122" t="n">
@@ -7917,14 +7950,14 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Órbitas y satélites</t>
+          <t>Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7933,13 +7966,19 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V123" t="n">
+        <v>1</v>
       </c>
       <c r="AF123" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -7948,83 +7987,95 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H124" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L124" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M124" t="n">
         <v>7</v>
       </c>
-      <c r="K124" t="n">
-        <v>5</v>
-      </c>
       <c r="Q124" t="n">
         <v>1</v>
       </c>
-      <c r="T124" t="n">
+      <c r="S124" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" t="n">
+        <v>1</v>
+      </c>
+      <c r="V124" t="n">
         <v>1</v>
       </c>
       <c r="AF124" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C125" t="n">
+        <v>10</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8</v>
+      </c>
+      <c r="H125" t="n">
         <v>5</v>
       </c>
-      <c r="D125" t="n">
-        <v>5</v>
-      </c>
-      <c r="G125" t="n">
+      <c r="I125" t="n">
         <v>6</v>
       </c>
-      <c r="H125" t="n">
-        <v>7</v>
-      </c>
-      <c r="I125" t="n">
-        <v>8</v>
-      </c>
       <c r="J125" t="n">
-        <v>7</v>
-      </c>
-      <c r="P125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O125" t="n">
         <v>1</v>
       </c>
       <c r="Q125" t="n">
@@ -8036,61 +8087,106 @@
       <c r="S125" t="n">
         <v>1</v>
       </c>
+      <c r="V125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>1</v>
+      </c>
       <c r="AF125" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C126" t="n">
+        <v>9</v>
+      </c>
+      <c r="F126" t="n">
+        <v>8</v>
+      </c>
+      <c r="G126" t="n">
         <v>6</v>
       </c>
-      <c r="D126" t="n">
-        <v>6</v>
+      <c r="H126" t="n">
+        <v>7</v>
+      </c>
+      <c r="I126" t="n">
+        <v>7</v>
+      </c>
+      <c r="J126" t="n">
+        <v>7</v>
+      </c>
+      <c r="K126" t="n">
+        <v>8</v>
+      </c>
+      <c r="L126" t="n">
+        <v>7.5</v>
       </c>
       <c r="M126" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1</v>
       </c>
       <c r="V126" t="n">
         <v>1</v>
       </c>
       <c r="AF126" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Espejos planos e imágenes</t>
+          <t>Masa y peso</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8099,29 +8195,59 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G127" t="n">
+        <v>6</v>
       </c>
       <c r="H127" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
       </c>
       <c r="J127" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>5</v>
       </c>
       <c r="L127" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M127" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
       </c>
       <c r="Q127" t="n">
         <v>1</v>
       </c>
+      <c r="R127" t="n">
+        <v>1</v>
+      </c>
       <c r="S127" t="n">
         <v>1</v>
       </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
       <c r="U127" t="n">
         <v>1</v>
       </c>
@@ -8129,23 +8255,23 @@
         <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>El ojo y los instrumentos ópticos</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8154,33 +8280,42 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3</v>
       </c>
       <c r="F128" t="n">
         <v>8</v>
       </c>
+      <c r="G128" t="n">
+        <v>6</v>
+      </c>
       <c r="H128" t="n">
         <v>5</v>
       </c>
-      <c r="I128" t="n">
-        <v>6</v>
-      </c>
       <c r="J128" t="n">
         <v>4.5</v>
       </c>
+      <c r="K128" t="n">
+        <v>3</v>
+      </c>
       <c r="M128" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
       </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
       <c r="Q128" t="n">
         <v>1</v>
       </c>
-      <c r="R128" t="n">
-        <v>1</v>
-      </c>
       <c r="S128" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" t="n">
         <v>1</v>
       </c>
       <c r="V128" t="n">
@@ -8194,7 +8329,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
@@ -8206,7 +8341,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8215,308 +8350,77 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D129" t="n">
+        <v>7</v>
+      </c>
+      <c r="E129" t="n">
+        <v>4</v>
       </c>
       <c r="F129" t="n">
         <v>8</v>
       </c>
       <c r="G129" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H129" t="n">
+        <v>5</v>
+      </c>
+      <c r="I129" t="n">
         <v>6</v>
       </c>
-      <c r="H129" t="n">
-        <v>7</v>
-      </c>
-      <c r="I129" t="n">
-        <v>7</v>
-      </c>
       <c r="J129" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K129" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L129" t="n">
         <v>7.5</v>
       </c>
       <c r="M129" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="n">
         <v>7</v>
       </c>
-      <c r="O129" t="n">
-        <v>1</v>
-      </c>
-      <c r="P129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>1</v>
-      </c>
-      <c r="R129" t="n">
-        <v>1</v>
-      </c>
-      <c r="S129" t="n">
-        <v>1</v>
-      </c>
-      <c r="T129" t="n">
-        <v>1</v>
-      </c>
-      <c r="U129" t="n">
-        <v>1</v>
-      </c>
-      <c r="V129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>11</v>
-      </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Masa y peso</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>2</v>
-      </c>
-      <c r="D130" t="n">
-        <v>2</v>
-      </c>
-      <c r="E130" t="n">
-        <v>2</v>
-      </c>
-      <c r="F130" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G130" t="n">
-        <v>6</v>
-      </c>
-      <c r="H130" t="n">
-        <v>2</v>
-      </c>
-      <c r="I130" t="n">
-        <v>2</v>
-      </c>
-      <c r="J130" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K130" t="n">
-        <v>5</v>
-      </c>
-      <c r="L130" t="n">
-        <v>6</v>
-      </c>
-      <c r="M130" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N130" t="n">
-        <v>1</v>
-      </c>
-      <c r="O130" t="n">
-        <v>1</v>
-      </c>
-      <c r="P130" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>1</v>
-      </c>
-      <c r="R130" t="n">
-        <v>1</v>
-      </c>
-      <c r="S130" t="n">
-        <v>1</v>
-      </c>
-      <c r="T130" t="n">
-        <v>1</v>
-      </c>
-      <c r="U130" t="n">
-        <v>1</v>
-      </c>
-      <c r="V130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>alineado</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>El ojo y los instrumentos ópticos</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>3</v>
-      </c>
-      <c r="D131" t="n">
-        <v>3</v>
-      </c>
-      <c r="F131" t="n">
-        <v>8</v>
-      </c>
-      <c r="G131" t="n">
-        <v>6</v>
-      </c>
-      <c r="H131" t="n">
-        <v>5</v>
-      </c>
-      <c r="J131" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K131" t="n">
-        <v>3</v>
-      </c>
-      <c r="M131" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O131" t="n">
-        <v>1</v>
-      </c>
-      <c r="P131" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>1</v>
-      </c>
-      <c r="S131" t="n">
-        <v>1</v>
-      </c>
-      <c r="T131" t="n">
-        <v>1</v>
-      </c>
-      <c r="V131" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Refracción de la luz</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>7</v>
-      </c>
-      <c r="D132" t="n">
-        <v>7</v>
-      </c>
-      <c r="E132" t="n">
-        <v>4</v>
-      </c>
-      <c r="F132" t="n">
-        <v>8</v>
-      </c>
-      <c r="G132" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H132" t="n">
-        <v>5</v>
-      </c>
-      <c r="I132" t="n">
-        <v>6</v>
-      </c>
-      <c r="J132" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K132" t="n">
-        <v>3</v>
-      </c>
-      <c r="L132" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M132" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N132" t="n">
-        <v>1</v>
-      </c>
-      <c r="O132" t="n">
-        <v>1</v>
-      </c>
-      <c r="P132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>1</v>
-      </c>
-      <c r="R132" t="n">
-        <v>1</v>
-      </c>
-      <c r="S132" t="n">
-        <v>1</v>
-      </c>
-      <c r="T132" t="n">
-        <v>1</v>
-      </c>
-      <c r="U132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>alineado</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
         <is>
           <t>tardio</t>
         </is>
@@ -8533,7 +8437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -13964,132 +13868,6 @@
       </c>
       <c r="J129">
         <f>Datos!B129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130">
-        <f>Datos!A130</f>
-        <v/>
-      </c>
-      <c r="B130">
-        <f>IF(Datos!C130="","",Datos!C130)</f>
-        <v/>
-      </c>
-      <c r="C130">
-        <f>COUNT(Datos!E130:M130)</f>
-        <v/>
-      </c>
-      <c r="D130">
-        <f>IF(C130=0,"",MEDIAN(Datos!E130:M130))</f>
-        <v/>
-      </c>
-      <c r="E130">
-        <f>COUNT(Datos!W130:AE130)</f>
-        <v/>
-      </c>
-      <c r="F130">
-        <f>IF(OR(B130="",D130=""),"",B130-D130)</f>
-        <v/>
-      </c>
-      <c r="G130">
-        <f>IF(Datos!D130="","",Datos!D130)</f>
-        <v/>
-      </c>
-      <c r="H130">
-        <f>COUNT(Datos!N130:V130)</f>
-        <v/>
-      </c>
-      <c r="I130">
-        <f>IF(B130="",IF(C130&gt;=5,"falta en SV",""),IF(G130="",IF(B130&gt;8,IF(C130&gt;=5,"SV tarde","despues del tramo"),IF(H130&gt;=5,"no retomado en 2-8","previo")),IF(B130&lt;2,"retomado",IF(AND(C130&lt;=1,E130&gt;=3),"solo especializacion",IF(F130="","coherente",IF(F130&lt;=-1.5,"SV adelantado",IF(F130&gt;=2,"SV tarde","coherente")))))))</f>
-        <v/>
-      </c>
-      <c r="J130">
-        <f>Datos!B130</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131">
-        <f>Datos!A131</f>
-        <v/>
-      </c>
-      <c r="B131">
-        <f>IF(Datos!C131="","",Datos!C131)</f>
-        <v/>
-      </c>
-      <c r="C131">
-        <f>COUNT(Datos!E131:M131)</f>
-        <v/>
-      </c>
-      <c r="D131">
-        <f>IF(C131=0,"",MEDIAN(Datos!E131:M131))</f>
-        <v/>
-      </c>
-      <c r="E131">
-        <f>COUNT(Datos!W131:AE131)</f>
-        <v/>
-      </c>
-      <c r="F131">
-        <f>IF(OR(B131="",D131=""),"",B131-D131)</f>
-        <v/>
-      </c>
-      <c r="G131">
-        <f>IF(Datos!D131="","",Datos!D131)</f>
-        <v/>
-      </c>
-      <c r="H131">
-        <f>COUNT(Datos!N131:V131)</f>
-        <v/>
-      </c>
-      <c r="I131">
-        <f>IF(B131="",IF(C131&gt;=5,"falta en SV",""),IF(G131="",IF(B131&gt;8,IF(C131&gt;=5,"SV tarde","despues del tramo"),IF(H131&gt;=5,"no retomado en 2-8","previo")),IF(B131&lt;2,"retomado",IF(AND(C131&lt;=1,E131&gt;=3),"solo especializacion",IF(F131="","coherente",IF(F131&lt;=-1.5,"SV adelantado",IF(F131&gt;=2,"SV tarde","coherente")))))))</f>
-        <v/>
-      </c>
-      <c r="J131">
-        <f>Datos!B131</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132">
-        <f>Datos!A132</f>
-        <v/>
-      </c>
-      <c r="B132">
-        <f>IF(Datos!C132="","",Datos!C132)</f>
-        <v/>
-      </c>
-      <c r="C132">
-        <f>COUNT(Datos!E132:M132)</f>
-        <v/>
-      </c>
-      <c r="D132">
-        <f>IF(C132=0,"",MEDIAN(Datos!E132:M132))</f>
-        <v/>
-      </c>
-      <c r="E132">
-        <f>COUNT(Datos!W132:AE132)</f>
-        <v/>
-      </c>
-      <c r="F132">
-        <f>IF(OR(B132="",D132=""),"",B132-D132)</f>
-        <v/>
-      </c>
-      <c r="G132">
-        <f>IF(Datos!D132="","",Datos!D132)</f>
-        <v/>
-      </c>
-      <c r="H132">
-        <f>COUNT(Datos!N132:V132)</f>
-        <v/>
-      </c>
-      <c r="I132">
-        <f>IF(B132="",IF(C132&gt;=5,"falta en SV",""),IF(G132="",IF(B132&gt;8,IF(C132&gt;=5,"SV tarde","despues del tramo"),IF(H132&gt;=5,"no retomado en 2-8","previo")),IF(B132&lt;2,"retomado",IF(AND(C132&lt;=1,E132&gt;=3),"solo especializacion",IF(F132="","coherente",IF(F132&lt;=-1.5,"SV adelantado",IF(F132&gt;=2,"SV tarde","coherente")))))))</f>
-        <v/>
-      </c>
-      <c r="J132">
-        <f>Datos!B132</f>
         <v/>
       </c>
     </row>
@@ -14129,7 +13907,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B132,A2)</f>
+        <f>COUNTIF(Datos!B2:B129,A2)</f>
         <v/>
       </c>
     </row>
@@ -14140,7 +13918,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B132,A3)</f>
+        <f>COUNTIF(Datos!B2:B129,A3)</f>
         <v/>
       </c>
     </row>
@@ -14151,7 +13929,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B132,A4)</f>
+        <f>COUNTIF(Datos!B2:B129,A4)</f>
         <v/>
       </c>
     </row>
@@ -14162,7 +13940,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B132,A5)</f>
+        <f>COUNTIF(Datos!B2:B129,A5)</f>
         <v/>
       </c>
     </row>
@@ -14173,7 +13951,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B132,A6)</f>
+        <f>COUNTIF(Datos!B2:B129,A6)</f>
         <v/>
       </c>
     </row>
@@ -14184,7 +13962,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B132,A7)</f>
+        <f>COUNTIF(Datos!B2:B129,A7)</f>
         <v/>
       </c>
     </row>
@@ -14195,7 +13973,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(Datos!B2:B132,A8)</f>
+        <f>COUNTIF(Datos!B2:B129,A8)</f>
         <v/>
       </c>
     </row>

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -673,7 +673,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Caída libre</t>
+          <t>Circuito eléctrico simple</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -682,19 +682,43 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>7</v>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -702,11 +726,23 @@
       <c r="Q3" t="n">
         <v>1</v>
       </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
       <c r="AF3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -722,7 +758,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Color y dispersión de la luz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -731,10 +767,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -743,19 +779,19 @@
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="K4" t="n">
-        <v>5</v>
+      <c r="L4" t="n">
+        <v>7.5</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -772,14 +808,17 @@
       <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
       <c r="AF4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -795,7 +834,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Circuito eléctrico simple</t>
+          <t>Conservación de la energía mecánica</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -804,67 +843,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
       <c r="J5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
         <v>5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -880,7 +889,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Color y dispersión de la luz</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -901,19 +910,22 @@
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>7.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -928,6 +940,9 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
@@ -956,7 +971,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Conservación de la energía mecánica</t>
+          <t>Disipación de energía y eficiencia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -965,37 +980,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>8.5</v>
       </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
       <c r="I7" t="n">
         <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
       </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
       <c r="AF7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1011,7 +1059,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Densidad</t>
+          <t>Energía potencial gravitatoria y elástica</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1020,36 +1068,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="O8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
@@ -1067,17 +1112,11 @@
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
       <c r="V8" t="n">
         <v>1</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1093,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Disipación de energía y eficiencia</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,45 +1146,24 @@
       <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
       <c r="G9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
         <v>7</v>
       </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
         <v>4.5</v>
       </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
@@ -1155,13 +1173,7 @@
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
       <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
@@ -1181,7 +1193,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1190,55 +1202,61 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
       </c>
       <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
         <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1254,7 +1272,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1268,32 +1286,29 @@
       <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1304,6 +1319,9 @@
       <c r="Q11" t="n">
         <v>1</v>
       </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
@@ -1314,6 +1332,9 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
@@ -1333,7 +1354,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,35 +1363,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
         <v>4.5</v>
       </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
@@ -1380,26 +1389,11 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1408,14 +1402,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1429,8 +1423,8 @@
       <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="F13" t="n">
-        <v>8</v>
+      <c r="E13" t="n">
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
@@ -1438,10 +1432,19 @@
       <c r="H13" t="n">
         <v>7</v>
       </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="P13" t="n">
@@ -1450,11 +1453,20 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1470,7 +1482,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1479,71 +1491,53 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" t="n">
         <v>6</v>
       </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
       <c r="G14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
         <v>6</v>
       </c>
-      <c r="H14" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>5</v>
-      </c>
       <c r="AG14" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1552,41 +1546,53 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K15" t="n">
         <v>8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>7.5</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
+      <c r="M15" t="n">
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="n">
         <v>1</v>
       </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
       <c r="AF15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -1598,7 +1604,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1607,35 +1613,53 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M16" t="n">
         <v>2.5</v>
       </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
@@ -1649,68 +1673,53 @@
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="F17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
       <c r="L17" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1718,9 +1727,6 @@
       <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
@@ -1734,11 +1740,11 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1750,7 +1756,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,28 +1765,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>7</v>
       </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
       <c r="J18" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -1788,12 +1806,12 @@
       <c r="Q18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
@@ -1801,11 +1819,11 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -1817,7 +1835,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Calor latente</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1826,38 +1844,20 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H19" t="n">
         <v>7</v>
       </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
@@ -1867,20 +1867,8 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -1889,14 +1877,14 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calor latente</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1905,20 +1893,38 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
         <v>7</v>
       </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
@@ -1926,6 +1932,18 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
@@ -1938,14 +1956,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1966,22 +1984,25 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
@@ -1995,6 +2016,9 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
@@ -2007,24 +2031,27 @@
       <c r="V21" t="n">
         <v>1</v>
       </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2033,16 +2060,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -2051,19 +2078,16 @@
         <v>2</v>
       </c>
       <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="J22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4</v>
-      </c>
       <c r="M22" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -2083,20 +2107,14 @@
       <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -2105,14 +2123,14 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2121,37 +2139,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2162,9 +2171,6 @@
       <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
@@ -2175,23 +2181,23 @@
         <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2200,28 +2206,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>7</v>
       </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
       <c r="J24" t="n">
         <v>7</v>
       </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2232,7 +2244,13 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
       <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
@@ -2246,7 +2264,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -2258,7 +2276,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2272,6 +2290,9 @@
       <c r="D25" t="n">
         <v>4</v>
       </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
@@ -2279,10 +2300,10 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
@@ -2296,6 +2317,9 @@
       <c r="M25" t="n">
         <v>2.5</v>
       </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
@@ -2321,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2337,7 +2361,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2346,83 +2370,83 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
       </c>
       <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
         <v>5</v>
       </c>
-      <c r="L26" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>4</v>
-      </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2431,83 +2455,77 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
         <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5</v>
+      </c>
+      <c r="M27" t="n">
         <v>7</v>
       </c>
-      <c r="K27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
         <v>6</v>
       </c>
-      <c r="M27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>5</v>
-      </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2524,9 +2542,6 @@
       <c r="F28" t="n">
         <v>8</v>
       </c>
-      <c r="G28" t="n">
-        <v>4</v>
-      </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
@@ -2534,13 +2549,13 @@
         <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
         <v>7</v>
@@ -2548,9 +2563,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
@@ -2586,7 +2598,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2603,27 +2615,30 @@
       <c r="F29" t="n">
         <v>8</v>
       </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L29" t="n">
         <v>3</v>
       </c>
-      <c r="J29" t="n">
-        <v>7</v>
-      </c>
-      <c r="K29" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" t="n">
-        <v>4</v>
-      </c>
       <c r="M29" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
@@ -2631,9 +2646,6 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
@@ -2659,7 +2671,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Energía cinética</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2668,33 +2680,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
         <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
       </c>
       <c r="M30" t="n">
         <v>4.5</v>
       </c>
-      <c r="O30" t="n">
+      <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="P30" t="n">
@@ -2709,18 +2721,18 @@
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="U30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -2732,7 +2744,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2747,29 +2759,38 @@
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
         <v>4</v>
       </c>
-      <c r="I31" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4</v>
-      </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
@@ -2785,15 +2806,21 @@
       <c r="T31" t="n">
         <v>1</v>
       </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -2805,7 +2832,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2814,40 +2841,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>4.5</v>
       </c>
-      <c r="K32" t="n">
-        <v>2</v>
-      </c>
       <c r="L32" t="n">
         <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2858,42 +2873,33 @@
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2902,28 +2908,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2934,33 +2952,42 @@
       <c r="Q33" t="n">
         <v>1</v>
       </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
       <c r="U33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
       <c r="AF33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2969,43 +2996,49 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
-      <c r="I34" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
         <v>7</v>
       </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4.5</v>
+      <c r="O34" t="n">
+        <v>1</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -3014,14 +3047,14 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3030,10 +3063,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -3045,19 +3078,16 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="n">
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
         <v>2.5</v>
@@ -3074,9 +3104,6 @@
       <c r="Q35" t="n">
         <v>1</v>
       </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
@@ -3089,27 +3116,24 @@
       <c r="V35" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1</v>
-      </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3118,10 +3142,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -3130,16 +3154,19 @@
         <v>6</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
@@ -3150,7 +3177,10 @@
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="T36" t="n">
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
@@ -3160,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -3169,14 +3199,14 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fricción y resistencia del aire</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3185,10 +3215,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -3197,19 +3227,22 @@
         <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
         <v>3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7</v>
-      </c>
-      <c r="K37" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6</v>
       </c>
       <c r="M37" t="n">
         <v>2.5</v>
@@ -3226,6 +3259,9 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
@@ -3239,23 +3275,23 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3264,10 +3300,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
@@ -3275,20 +3308,14 @@
       <c r="G38" t="n">
         <v>6</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>7</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" t="n">
-        <v>6</v>
-      </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -3296,27 +3323,21 @@
       <c r="P38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -3328,7 +3349,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3337,25 +3358,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
         <v>2.5</v>
@@ -3372,9 +3390,6 @@
       <c r="N39" t="n">
         <v>1</v>
       </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
@@ -3397,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3413,7 +3428,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3422,13 +3437,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
       </c>
       <c r="G40" t="n">
         <v>6</v>
@@ -3436,19 +3451,16 @@
       <c r="H40" t="n">
         <v>7</v>
       </c>
-      <c r="I40" t="n">
-        <v>8</v>
-      </c>
       <c r="J40" t="n">
         <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
         <v>2.5</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>1</v>
       </c>
       <c r="P40" t="n">
@@ -3457,9 +3469,6 @@
       <c r="Q40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
@@ -3470,11 +3479,11 @@
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3486,7 +3495,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
+          <t>Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3495,22 +3504,40 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
       </c>
+      <c r="K41" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6</v>
+      </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -3518,33 +3545,39 @@
       <c r="P41" t="n">
         <v>1</v>
       </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
       <c r="V41" t="n">
         <v>1</v>
       </c>
-      <c r="AF41" t="n">
-        <v>9</v>
-      </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3558,8 +3591,8 @@
       <c r="D42" t="n">
         <v>3</v>
       </c>
-      <c r="E42" t="n">
-        <v>3</v>
+      <c r="F42" t="n">
+        <v>8</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -3568,21 +3601,18 @@
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
-        <v>2</v>
-      </c>
       <c r="L42" t="n">
         <v>3</v>
       </c>
       <c r="M42" t="n">
         <v>2.5</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
@@ -3595,9 +3625,6 @@
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
@@ -3623,7 +3650,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3659,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -3646,14 +3673,20 @@
       <c r="H43" t="n">
         <v>7</v>
       </c>
+      <c r="I43" t="n">
+        <v>7</v>
+      </c>
       <c r="J43" t="n">
         <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.5</v>
       </c>
       <c r="M43" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3664,21 +3697,27 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3690,7 +3729,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gravedad: atracción hacia la Tierra</t>
+          <t>Magnitudes escalares y vectoriales</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3699,44 +3738,26 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" t="n">
         <v>3</v>
       </c>
-      <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" t="n">
-        <v>8</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2</v>
-      </c>
       <c r="I44" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" t="n">
         <v>6</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
       </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
@@ -3746,20 +3767,14 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="n">
-        <v>1</v>
-      </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3768,14 +3783,14 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3784,55 +3799,46 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
         <v>8</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L45" t="n">
-        <v>3</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>3</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3848,7 +3854,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Magnitudes escalares y vectoriales</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3857,25 +3863,34 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
         <v>5</v>
       </c>
-      <c r="D46" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>6</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3</v>
-      </c>
-      <c r="I46" t="n">
-        <v>6</v>
+      <c r="J46" t="n">
+        <v>2.5</v>
       </c>
       <c r="K46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3886,6 +3901,9 @@
       <c r="R46" t="n">
         <v>1</v>
       </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
@@ -3893,11 +3911,11 @@
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -3909,7 +3927,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3918,28 +3936,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
-      </c>
-      <c r="F47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3947,17 +3965,20 @@
       <c r="Q47" t="n">
         <v>1</v>
       </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
       <c r="S47" t="n">
         <v>1</v>
       </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
-      <c r="Z47" t="n">
-        <v>1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -3973,7 +3994,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3987,29 +4008,20 @@
       <c r="D48" t="n">
         <v>2</v>
       </c>
-      <c r="F48" t="n">
-        <v>8</v>
-      </c>
       <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" t="n">
         <v>3</v>
       </c>
-      <c r="H48" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
+      <c r="L48" t="n">
+        <v>3</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -4020,13 +4032,13 @@
       <c r="R48" t="n">
         <v>1</v>
       </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
-      <c r="V48" t="n">
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
@@ -4034,7 +4046,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -4046,7 +4058,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4055,13 +4067,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -4070,14 +4085,20 @@
         <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
         <v>2.5</v>
       </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
@@ -4090,6 +4111,9 @@
       <c r="S49" t="n">
         <v>1</v>
       </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
       <c r="U49" t="n">
         <v>1</v>
       </c>
@@ -4097,11 +4121,11 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -4113,7 +4137,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4127,20 +4151,32 @@
       <c r="D50" t="n">
         <v>2</v>
       </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
         <v>2</v>
       </c>
-      <c r="I50" t="n">
-        <v>6</v>
-      </c>
-      <c r="K50" t="n">
-        <v>3</v>
+      <c r="J50" t="n">
+        <v>2.5</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -4148,16 +4184,13 @@
       <c r="Q50" t="n">
         <v>1</v>
       </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" t="n">
+      <c r="S50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>1</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="V50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
@@ -4165,7 +4198,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -4177,7 +4210,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4186,65 +4219,35 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F51" t="n">
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
-      </c>
-      <c r="L51" t="n">
         <v>4</v>
       </c>
-      <c r="M51" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -4256,7 +4259,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4265,37 +4268,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L52" t="n">
-        <v>4</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4306,18 +4291,12 @@
       <c r="S52" t="n">
         <v>1</v>
       </c>
-      <c r="U52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1</v>
-      </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -4329,7 +4308,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4338,34 +4317,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
-      </c>
-      <c r="L53" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
         <v>7</v>
@@ -4373,9 +4346,6 @@
       <c r="N53" t="n">
         <v>1</v>
       </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
@@ -4391,17 +4361,11 @@
       <c r="T53" t="n">
         <v>1</v>
       </c>
-      <c r="U53" t="n">
-        <v>1</v>
-      </c>
       <c r="V53" t="n">
         <v>1</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1</v>
-      </c>
       <c r="AF53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4417,7 +4381,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4426,27 +4390,27 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
         <v>8</v>
       </c>
-      <c r="D54" t="n">
-        <v>8</v>
-      </c>
-      <c r="F54" t="n">
-        <v>8</v>
-      </c>
       <c r="G54" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K54" t="n">
-        <v>4</v>
-      </c>
-      <c r="O54" t="n">
+        <v>6</v>
+      </c>
+      <c r="M54" t="n">
+        <v>7</v>
+      </c>
+      <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
@@ -4454,7 +4418,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -4466,7 +4430,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4480,19 +4444,19 @@
       <c r="D55" t="n">
         <v>8</v>
       </c>
-      <c r="G55" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>7</v>
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>7</v>
       </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
         <v>1</v>
       </c>
       <c r="S55" t="n">
@@ -4515,7 +4479,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4524,22 +4488,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
         <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J56" t="n">
         <v>4.5</v>
@@ -4548,9 +4512,9 @@
         <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>7</v>
-      </c>
-      <c r="N56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O56" t="n">
         <v>1</v>
       </c>
       <c r="P56" t="n">
@@ -4572,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4588,7 +4552,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4602,42 +4566,75 @@
       <c r="D57" t="n">
         <v>2</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>6</v>
       </c>
+      <c r="H57" t="n">
+        <v>5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M57" t="n">
         <v>7</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>1</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
       <c r="AF57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4646,27 +4643,27 @@
         </is>
       </c>
       <c r="C58" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I58" t="n">
         <v>8</v>
       </c>
-      <c r="D58" t="n">
-        <v>8</v>
-      </c>
-      <c r="F58" t="n">
-        <v>8</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="M58" t="n">
         <v>7</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="S58" t="n">
+      <c r="V58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
@@ -4686,7 +4683,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4695,10 +4692,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
         <v>8</v>
@@ -4707,16 +4704,16 @@
         <v>6</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I59" t="n">
-        <v>8</v>
-      </c>
-      <c r="J59" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7.5</v>
       </c>
       <c r="M59" t="n">
         <v>2.5</v>
@@ -4733,17 +4730,20 @@
       <c r="R59" t="n">
         <v>1</v>
       </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
       <c r="V59" t="n">
         <v>1</v>
       </c>
+      <c r="Z59" t="n">
+        <v>1</v>
+      </c>
       <c r="AF59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4768,34 +4768,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
-      </c>
-      <c r="J60" t="n">
         <v>7</v>
-      </c>
-      <c r="K60" t="n">
-        <v>5</v>
       </c>
       <c r="L60" t="n">
         <v>7.5</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -4809,39 +4803,30 @@
       <c r="R60" t="n">
         <v>1</v>
       </c>
-      <c r="S60" t="n">
-        <v>1</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
-      <c r="Z60" t="n">
-        <v>1</v>
-      </c>
       <c r="AF60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4850,35 +4835,65 @@
         </is>
       </c>
       <c r="C61" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" t="n">
         <v>5</v>
-      </c>
-      <c r="D61" t="n">
-        <v>5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>8.5</v>
       </c>
       <c r="I61" t="n">
         <v>8</v>
       </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
+      <c r="K61" t="n">
+        <v>7</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M61" t="n">
         <v>7</v>
       </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
       <c r="P61" t="n">
         <v>1</v>
       </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
       <c r="R61" t="n">
         <v>1</v>
       </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
       <c r="V61" t="n">
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4890,7 +4905,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4907,50 +4922,23 @@
       <c r="F62" t="n">
         <v>8</v>
       </c>
-      <c r="G62" t="n">
-        <v>6</v>
-      </c>
-      <c r="H62" t="n">
-        <v>4</v>
-      </c>
-      <c r="I62" t="n">
-        <v>3</v>
-      </c>
       <c r="K62" t="n">
-        <v>4</v>
-      </c>
-      <c r="L62" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M62" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
-      <c r="U62" t="n">
-        <v>1</v>
-      </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
-      <c r="Z62" t="n">
-        <v>1</v>
-      </c>
       <c r="AF62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4959,14 +4947,14 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4975,29 +4963,41 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="n">
         <v>4</v>
-      </c>
-      <c r="I63" t="n">
-        <v>7</v>
-      </c>
-      <c r="L63" t="n">
-        <v>7.5</v>
       </c>
       <c r="M63" t="n">
         <v>2.5</v>
       </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
@@ -5010,6 +5010,12 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
@@ -5017,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5033,7 +5039,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5042,10 +5048,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
@@ -5054,22 +5060,19 @@
         <v>6</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
         <v>8</v>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
-      </c>
-      <c r="L64" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5089,30 +5092,27 @@
       <c r="T64" t="n">
         <v>1</v>
       </c>
-      <c r="U64" t="n">
-        <v>1</v>
-      </c>
       <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5121,31 +5121,67 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K65" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="L65" t="n">
+        <v>4</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5154,14 +5190,14 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5170,83 +5206,53 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>3</v>
-      </c>
-      <c r="L66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
         <v>1</v>
       </c>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
-      <c r="U66" t="n">
-        <v>1</v>
-      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
+      <c r="Z66" t="n">
+        <v>1</v>
+      </c>
       <c r="AF66" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5255,31 +5261,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G67" t="n">
         <v>6</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I67" t="n">
         <v>8</v>
       </c>
       <c r="J67" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -5307,7 +5319,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
@@ -5319,7 +5331,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5333,36 +5345,27 @@
       <c r="D68" t="n">
         <v>4</v>
       </c>
-      <c r="E68" t="n">
-        <v>4</v>
-      </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J68" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K68" t="n">
         <v>3</v>
       </c>
-      <c r="L68" t="n">
-        <v>4</v>
-      </c>
       <c r="M68" t="n">
         <v>2.5</v>
       </c>
-      <c r="N68" t="n">
-        <v>1</v>
-      </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
@@ -5379,9 +5382,6 @@
         <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
-      </c>
-      <c r="U68" t="n">
         <v>1</v>
       </c>
       <c r="V68" t="n">
@@ -5404,7 +5404,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5413,53 +5413,77 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2</v>
       </c>
       <c r="I69" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K69" t="n">
         <v>3</v>
       </c>
-      <c r="K69" t="n">
-        <v>7</v>
-      </c>
       <c r="M69" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
       <c r="R69" t="n">
         <v>1</v>
       </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>1</v>
       </c>
-      <c r="Z69" t="n">
-        <v>1</v>
-      </c>
       <c r="AF69" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5468,38 +5492,29 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
-      </c>
-      <c r="E70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>7</v>
-      </c>
-      <c r="I70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L70" t="n">
         <v>4</v>
       </c>
       <c r="M70" t="n">
         <v>2.5</v>
       </c>
-      <c r="N70" t="n">
-        <v>1</v>
-      </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
@@ -5509,24 +5524,24 @@
       <c r="Q70" t="n">
         <v>1</v>
       </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
       <c r="S70" t="n">
         <v>1</v>
       </c>
-      <c r="T70" t="n">
+      <c r="U70" t="n">
         <v>1</v>
       </c>
       <c r="V70" t="n">
         <v>1</v>
       </c>
+      <c r="Z70" t="n">
+        <v>1</v>
+      </c>
       <c r="AF70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -5538,7 +5553,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5547,59 +5562,41 @@
         </is>
       </c>
       <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" t="n">
         <v>4</v>
       </c>
-      <c r="D71" t="n">
+      <c r="K71" t="n">
         <v>4</v>
       </c>
-      <c r="F71" t="n">
+      <c r="M71" t="n">
+        <v>7</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
         <v>5</v>
       </c>
-      <c r="G71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2</v>
-      </c>
-      <c r="I71" t="n">
-        <v>6</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K71" t="n">
-        <v>3</v>
-      </c>
-      <c r="M71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>1</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1</v>
-      </c>
-      <c r="S71" t="n">
-        <v>1</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>4</v>
-      </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -5611,7 +5608,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5625,11 +5622,8 @@
       <c r="D72" t="n">
         <v>2</v>
       </c>
-      <c r="E72" t="n">
-        <v>2</v>
-      </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G72" t="n">
         <v>2</v>
@@ -5647,10 +5641,7 @@
         <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N72" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5673,12 +5664,15 @@
       <c r="V72" t="n">
         <v>1</v>
       </c>
+      <c r="Z72" t="n">
+        <v>1</v>
+      </c>
       <c r="AF72" t="n">
         <v>2</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
@@ -5690,7 +5684,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5699,52 +5693,43 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L73" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>6</v>
       </c>
       <c r="M73" t="n">
         <v>2.5</v>
       </c>
-      <c r="O73" t="n">
-        <v>1</v>
-      </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
-      <c r="S73" t="n">
-        <v>1</v>
-      </c>
-      <c r="U73" t="n">
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="V73" t="n">
         <v>1</v>
       </c>
-      <c r="Z73" t="n">
-        <v>1</v>
-      </c>
       <c r="AF73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -5760,7 +5745,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5769,41 +5754,59 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8</v>
       </c>
       <c r="G74" t="n">
         <v>6</v>
       </c>
-      <c r="H74" t="n">
-        <v>4</v>
+      <c r="I74" t="n">
+        <v>8</v>
+      </c>
+      <c r="J74" t="n">
+        <v>7</v>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L74" t="n">
+        <v>7.5</v>
       </c>
       <c r="M74" t="n">
         <v>7</v>
       </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
         <v>1</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
       <c r="V74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
@@ -5815,7 +5818,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5824,31 +5827,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
+        <v>8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
         <v>5</v>
-      </c>
-      <c r="G75" t="n">
-        <v>2</v>
-      </c>
-      <c r="H75" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" t="n">
-        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>2.5</v>
       </c>
       <c r="K75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -5871,141 +5871,90 @@
       <c r="V75" t="n">
         <v>1</v>
       </c>
-      <c r="Z75" t="n">
-        <v>1</v>
-      </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Aceleración y fuerza centrípeta</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G76" t="n">
-        <v>6</v>
-      </c>
-      <c r="H76" t="n">
         <v>5</v>
       </c>
-      <c r="I76" t="n">
-        <v>5</v>
-      </c>
-      <c r="K76" t="n">
-        <v>6</v>
-      </c>
       <c r="M76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Caída libre</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
-      </c>
-      <c r="F77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
-      </c>
-      <c r="I77" t="n">
-        <v>8</v>
+        <v>8.5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7</v>
       </c>
       <c r="J77" t="n">
         <v>7</v>
       </c>
-      <c r="K77" t="n">
-        <v>7</v>
-      </c>
-      <c r="L77" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M77" t="n">
-        <v>7</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
-      <c r="R77" t="n">
+      <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1</v>
-      </c>
-      <c r="V77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
@@ -6013,7 +5962,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -6025,37 +5974,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I78" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" t="n">
         <v>5</v>
-      </c>
-      <c r="J78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K78" t="n">
-        <v>2</v>
       </c>
       <c r="M78" t="n">
         <v>7</v>
@@ -6082,11 +6031,11 @@
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -6098,26 +6047,44 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Aplicaciones de las leyes de Newton</t>
+          <t>Desintegración radiactiva</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>8</v>
+      </c>
+      <c r="F79" t="n">
+        <v>8</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
@@ -6129,19 +6096,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Observación astronómica en distintas longitudes de onda</t>
+          <t>Fisión y fusión nuclear</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F80" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1</v>
       </c>
       <c r="AF80" t="n">
         <v>11</v>
@@ -6160,71 +6145,107 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Campo eléctrico</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="n">
         <v>6</v>
-      </c>
-      <c r="D81" t="n">
-        <v>6</v>
-      </c>
-      <c r="F81" t="n">
-        <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>6</v>
       </c>
-      <c r="O81" t="n">
+      <c r="H81" t="n">
+        <v>7</v>
+      </c>
+      <c r="I81" t="n">
+        <v>8</v>
+      </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
+      <c r="K81" t="n">
+        <v>4</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N81" t="n">
         <v>1</v>
       </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
+      <c r="Q81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1</v>
+      </c>
       <c r="AF81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" t="n">
-        <v>2</v>
-      </c>
-      <c r="T82" t="n">
+        <v>8</v>
+      </c>
+      <c r="H82" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" t="n">
         <v>1</v>
       </c>
       <c r="AF82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6240,53 +6261,95 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" t="n">
+        <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H83" t="n">
+        <v>7</v>
       </c>
       <c r="I83" t="n">
+        <v>3</v>
+      </c>
+      <c r="J83" t="n">
         <v>7</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4</v>
+      </c>
+      <c r="L83" t="n">
+        <v>7.5</v>
       </c>
       <c r="M83" t="n">
         <v>7</v>
       </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
       <c r="P83" t="n">
         <v>1</v>
       </c>
+      <c r="Q83" t="n">
+        <v>1</v>
+      </c>
       <c r="R83" t="n">
         <v>1</v>
       </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
+      </c>
       <c r="V83" t="n">
         <v>1</v>
       </c>
+      <c r="Z83" t="n">
+        <v>1</v>
+      </c>
       <c r="AF83" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Desintegración radiactiva</t>
+          <t>Aplicaciones de las leyes de Newton</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6295,44 +6358,29 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
-      </c>
-      <c r="E84" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF84" t="n">
         <v>8</v>
       </c>
-      <c r="F84" t="n">
-        <v>8</v>
-      </c>
-      <c r="G84" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>11</v>
-      </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6341,20 +6389,17 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
-      </c>
-      <c r="E85" t="n">
-        <v>8</v>
-      </c>
-      <c r="N85" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
       </c>
       <c r="AF85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -6366,7 +6411,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Campo eléctrico</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6375,13 +6420,25 @@
         </is>
       </c>
       <c r="C86" t="n">
+        <v>6</v>
+      </c>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="n">
         <v>8</v>
       </c>
-      <c r="D86" t="n">
-        <v>8</v>
+      <c r="G86" t="n">
+        <v>6</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -6397,7 +6454,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6411,26 +6468,14 @@
       <c r="D87" t="n">
         <v>2</v>
       </c>
-      <c r="G87" t="n">
-        <v>6</v>
-      </c>
       <c r="K87" t="n">
         <v>2</v>
       </c>
-      <c r="M87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
-      <c r="V87" t="n">
-        <v>1</v>
-      </c>
       <c r="AF87" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -6439,14 +6484,14 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Defecto de masa y energía de enlace nuclear</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6455,16 +6500,28 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
-      </c>
-      <c r="F88" t="n">
-        <v>8</v>
-      </c>
-      <c r="O88" t="n">
+        <v>9</v>
+      </c>
+      <c r="G88" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>7</v>
+      </c>
+      <c r="M88" t="n">
+        <v>7</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -6480,7 +6537,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Espejos esféricos</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6491,34 +6548,10 @@
       <c r="C89" t="n">
         <v>10</v>
       </c>
-      <c r="F89" t="n">
+      <c r="E89" t="n">
         <v>8</v>
       </c>
-      <c r="H89" t="n">
-        <v>5</v>
-      </c>
-      <c r="J89" t="n">
-        <v>7</v>
-      </c>
-      <c r="L89" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M89" t="n">
-        <v>7</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>1</v>
-      </c>
-      <c r="S89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" t="n">
+      <c r="N89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
@@ -6531,14 +6564,14 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Fisión y fusión nuclear</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6547,32 +6580,17 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
-      </c>
-      <c r="F90" t="n">
         <v>8</v>
       </c>
-      <c r="L90" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M90" t="n">
-        <v>7</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1</v>
-      </c>
-      <c r="V90" t="n">
-        <v>1</v>
+      <c r="D90" t="n">
+        <v>8</v>
       </c>
       <c r="AF90" t="n">
         <v>11</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
@@ -6584,7 +6602,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Fotón y efecto fotoeléctrico</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6593,38 +6611,47 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
-      </c>
-      <c r="E91" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
       </c>
       <c r="G91" t="n">
         <v>6</v>
       </c>
-      <c r="N91" t="n">
-        <v>1</v>
+      <c r="K91" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.5</v>
       </c>
       <c r="P91" t="n">
         <v>1</v>
       </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1</v>
+      </c>
       <c r="AF91" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Inducción electromagnética: Faraday y Lenz</t>
+          <t>Defecto de masa y energía de enlace nuclear</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6633,41 +6660,20 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
-      </c>
-      <c r="D92" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
       </c>
-      <c r="G92" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I92" t="n">
-        <v>5</v>
-      </c>
-      <c r="M92" t="n">
-        <v>7</v>
-      </c>
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="P92" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" t="n">
-        <v>1</v>
-      </c>
-      <c r="V92" t="n">
-        <v>1</v>
-      </c>
       <c r="AF92" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -6679,7 +6685,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ley de Coulomb</t>
+          <t>Espejos esféricos</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6688,59 +6694,56 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
-      </c>
-      <c r="D93" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
         <v>8</v>
       </c>
-      <c r="G93" t="n">
-        <v>6</v>
-      </c>
-      <c r="I93" t="n">
-        <v>7</v>
+      <c r="H93" t="n">
+        <v>5</v>
       </c>
       <c r="J93" t="n">
         <v>7</v>
       </c>
+      <c r="L93" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M93" t="n">
         <v>7</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="P93" t="n">
-        <v>1</v>
-      </c>
-      <c r="R93" t="n">
+      <c r="Q93" t="n">
         <v>1</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
       </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
       <c r="V93" t="n">
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Leyes de Kepler</t>
+          <t>Fotón y efecto fotoeléctrico</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6749,17 +6752,26 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
-      </c>
-      <c r="D94" t="n">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="E94" t="n">
+        <v>8</v>
+      </c>
+      <c r="G94" t="n">
+        <v>6</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
@@ -6771,7 +6783,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
+          <t>Inducción electromagnética: Faraday y Lenz</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6780,18 +6792,33 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>8</v>
       </c>
       <c r="G95" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I95" t="n">
+        <v>5</v>
+      </c>
+      <c r="M95" t="n">
         <v>7</v>
       </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
       <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="n">
         <v>1</v>
       </c>
       <c r="AF95" t="n">
@@ -6799,7 +6826,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
@@ -6811,7 +6838,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Núcleo atómico e isótopos</t>
+          <t>Ley de Coulomb</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6820,13 +6847,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3</v>
       </c>
       <c r="F96" t="n">
         <v>8</v>
       </c>
       <c r="G96" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I96" t="n">
+        <v>7</v>
+      </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
+      <c r="M96" t="n">
+        <v>7</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -6834,24 +6873,33 @@
       <c r="P96" t="n">
         <v>1</v>
       </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1</v>
+      </c>
       <c r="AF96" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro</t>
+          <t>Leyes de Kepler</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6860,59 +6908,29 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
-      </c>
-      <c r="F97" t="n">
-        <v>8</v>
-      </c>
-      <c r="G97" t="n">
-        <v>6</v>
-      </c>
-      <c r="H97" t="n">
-        <v>7</v>
-      </c>
-      <c r="L97" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M97" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O97" t="n">
-        <v>1</v>
-      </c>
-      <c r="P97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" t="n">
-        <v>1</v>
-      </c>
-      <c r="V97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D97" t="n">
+        <v>4</v>
       </c>
       <c r="AF97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
           <t>posterior</t>
-        </is>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ondas de radio y telecomunicaciones</t>
+          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6924,24 +6942,15 @@
         <v>11</v>
       </c>
       <c r="G98" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H98" t="n">
+        <v>6</v>
+      </c>
+      <c r="I98" t="n">
         <v>7</v>
       </c>
-      <c r="M98" t="n">
-        <v>4.5</v>
-      </c>
       <c r="P98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z98" t="n">
+      <c r="R98" t="n">
         <v>1</v>
       </c>
       <c r="AF98" t="n">
@@ -6961,7 +6970,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Energía potencial y potencial eléctrico</t>
+          <t>Núcleo atómico e isótopos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6970,21 +6979,18 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" t="n">
+        <v>9</v>
+      </c>
+      <c r="F99" t="n">
         <v>8</v>
       </c>
       <c r="G99" t="n">
         <v>8.5</v>
       </c>
-      <c r="H99" t="n">
-        <v>7</v>
+      <c r="O99" t="n">
+        <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q99" t="n">
         <v>1</v>
       </c>
       <c r="AF99" t="n">
@@ -6992,7 +6998,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
@@ -7004,7 +7010,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
+          <t>Ondas electromagnéticas y espectro</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7013,13 +7019,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F100" t="n">
         <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H100" t="n">
         <v>7</v>
@@ -7027,6 +7033,9 @@
       <c r="L100" t="n">
         <v>7.5</v>
       </c>
+      <c r="M100" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O100" t="n">
         <v>1</v>
       </c>
@@ -7039,11 +7048,14 @@
       <c r="U100" t="n">
         <v>1</v>
       </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
       <c r="Z100" t="n">
         <v>1</v>
       </c>
       <c r="AF100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
@@ -7052,14 +7064,14 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Radiación térmica y cuerpo negro</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7068,34 +7080,31 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G101" t="n">
+        <v>8.5</v>
       </c>
       <c r="H101" t="n">
         <v>7</v>
       </c>
-      <c r="J101" t="n">
-        <v>7</v>
-      </c>
-      <c r="K101" t="n">
-        <v>6</v>
-      </c>
-      <c r="L101" t="n">
-        <v>7.5</v>
+      <c r="M101" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
         <v>1</v>
       </c>
-      <c r="S101" t="n">
-        <v>1</v>
-      </c>
-      <c r="T101" t="n">
-        <v>1</v>
-      </c>
-      <c r="U101" t="n">
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z101" t="n">
         <v>1</v>
       </c>
       <c r="AF101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -7111,7 +7120,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Rapidez de la luz</t>
+          <t>Energía potencial y potencial eléctrico</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7120,33 +7129,21 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8</v>
       </c>
       <c r="G102" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H102" t="n">
         <v>7</v>
       </c>
-      <c r="L102" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M102" t="n">
-        <v>7</v>
-      </c>
       <c r="P102" t="n">
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
-      <c r="V102" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z102" t="n">
         <v>1</v>
       </c>
       <c r="AF102" t="n">
@@ -7154,7 +7151,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
@@ -7166,7 +7163,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Reflexión interna total</t>
+          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7175,16 +7172,37 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F103" t="n">
+        <v>8</v>
+      </c>
+      <c r="G103" t="n">
+        <v>8.5</v>
       </c>
       <c r="H103" t="n">
         <v>7</v>
       </c>
+      <c r="L103" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
       <c r="Q103" t="n">
         <v>1</v>
       </c>
+      <c r="U103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>1</v>
+      </c>
       <c r="AF103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
@@ -7200,7 +7218,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Segunda ley de la termodinámica</t>
+          <t>Radiación térmica y cuerpo negro</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7209,23 +7227,38 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
-      </c>
-      <c r="D104" t="n">
-        <v>5</v>
-      </c>
-      <c r="G104" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P104" t="n">
+        <v>10</v>
+      </c>
+      <c r="H104" t="n">
+        <v>7</v>
+      </c>
+      <c r="J104" t="n">
+        <v>7</v>
+      </c>
+      <c r="K104" t="n">
+        <v>6</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
@@ -7237,7 +7270,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Semiconductores y electrónica básica</t>
+          <t>Rapidez de la luz</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7246,16 +7279,37 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
-      </c>
-      <c r="J105" t="n">
+        <v>10</v>
+      </c>
+      <c r="G105" t="n">
+        <v>6</v>
+      </c>
+      <c r="H105" t="n">
         <v>7</v>
       </c>
-      <c r="S105" t="n">
+      <c r="L105" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M105" t="n">
+        <v>7</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" t="n">
+        <v>1</v>
+      </c>
+      <c r="V105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z105" t="n">
         <v>1</v>
       </c>
       <c r="AF105" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
@@ -7271,7 +7325,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Superposición e interferencia de ondas</t>
+          <t>Reflexión interna total</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7282,14 +7336,14 @@
       <c r="C106" t="n">
         <v>10</v>
       </c>
-      <c r="G106" t="n">
-        <v>6</v>
-      </c>
-      <c r="P106" t="n">
+      <c r="H106" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
@@ -7305,7 +7359,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Segunda ley de la termodinámica</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7314,34 +7368,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>6</v>
-      </c>
-      <c r="J107" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M107" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
-      <c r="S107" t="n">
-        <v>1</v>
-      </c>
-      <c r="V107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>1</v>
-      </c>
       <c r="AF107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -7357,7 +7396,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Viscosidad y régimen de flujo</t>
+          <t>Semiconductores y electrónica básica</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7368,10 +7407,10 @@
       <c r="C108" t="n">
         <v>9</v>
       </c>
-      <c r="K108" t="n">
+      <c r="J108" t="n">
         <v>7</v>
       </c>
-      <c r="T108" t="n">
+      <c r="S108" t="n">
         <v>1</v>
       </c>
       <c r="AF108" t="n">
@@ -7391,49 +7430,46 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Aceleración y fuerza centrípeta</t>
+          <t>Superposición e interferencia de ondas</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
-      </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="M109" t="n">
-        <v>7</v>
-      </c>
-      <c r="V109" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6</v>
+      </c>
+      <c r="P109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Colisiones elásticas e inelásticas</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -7443,9 +7479,24 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M110" t="n">
+        <v>4.5</v>
       </c>
       <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">
@@ -7465,38 +7516,41 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Viscosidad y régimen de flujo</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
-      </c>
-      <c r="D111" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="K111" t="n">
+        <v>7</v>
+      </c>
+      <c r="T111" t="n">
+        <v>1</v>
       </c>
       <c r="AF111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Colisiones elásticas e inelásticas</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7505,31 +7559,19 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
-      </c>
-      <c r="H112" t="n">
-        <v>4</v>
-      </c>
-      <c r="J112" t="n">
-        <v>7</v>
-      </c>
-      <c r="K112" t="n">
         <v>8</v>
       </c>
-      <c r="Q112" t="n">
-        <v>1</v>
-      </c>
-      <c r="S112" t="n">
-        <v>1</v>
-      </c>
-      <c r="T112" t="n">
+      <c r="G112" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P112" t="n">
         <v>1</v>
       </c>
       <c r="AF112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -7538,14 +7580,14 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7554,13 +7596,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -7576,7 +7618,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7585,25 +7627,31 @@
         </is>
       </c>
       <c r="C114" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>4</v>
+      </c>
+      <c r="J114" t="n">
+        <v>7</v>
+      </c>
+      <c r="K114" t="n">
         <v>8</v>
       </c>
-      <c r="D114" t="n">
-        <v>8</v>
-      </c>
-      <c r="H114" t="n">
-        <v>7</v>
-      </c>
-      <c r="M114" t="n">
-        <v>7</v>
-      </c>
       <c r="Q114" t="n">
         <v>1</v>
       </c>
-      <c r="V114" t="n">
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="n">
         <v>1</v>
       </c>
       <c r="AF114" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -7612,14 +7660,14 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Movimiento armónico simple</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7628,22 +7676,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
-      </c>
-      <c r="F115" t="n">
-        <v>8</v>
-      </c>
-      <c r="I115" t="n">
-        <v>4</v>
-      </c>
-      <c r="O115" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF115" t="n">
         <v>8</v>
@@ -7662,7 +7698,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Movimiento circular y variables angulares</t>
+          <t>Movimiento armónico simple</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7671,31 +7707,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
-      </c>
-      <c r="G116" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K116" t="n">
-        <v>3</v>
-      </c>
-      <c r="M116" t="n">
-        <v>7</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1</v>
-      </c>
-      <c r="T116" t="n">
-        <v>1</v>
-      </c>
-      <c r="V116" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8</v>
+      </c>
+      <c r="I116" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="R116" t="n">
         <v>1</v>
       </c>
       <c r="AF116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -7704,14 +7734,14 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cinemática en dos dimensiones y proyectiles</t>
+          <t>Movimiento circular y variables angulares</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7720,19 +7750,31 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G117" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3</v>
+      </c>
+      <c r="M117" t="n">
+        <v>7</v>
       </c>
       <c r="P117" t="n">
         <v>1</v>
       </c>
+      <c r="T117" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" t="n">
+        <v>1</v>
+      </c>
       <c r="AF117" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
@@ -7741,14 +7783,14 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Niveles de energía atómicos y espectros</t>
+          <t>Cinemática en dos dimensiones y proyectiles</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7757,19 +7799,19 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="P118" t="n">
         <v>1</v>
       </c>
       <c r="AF118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
@@ -7778,14 +7820,14 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ondas estacionarias y armónicos</t>
+          <t>Niveles de energía atómicos y espectros</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7794,25 +7836,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D119" t="n">
-        <v>8</v>
-      </c>
-      <c r="H119" t="n">
-        <v>7</v>
-      </c>
-      <c r="M119" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>1</v>
-      </c>
-      <c r="V119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF119" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -7821,14 +7854,14 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Órbitas y satélites</t>
+          <t>Ondas estacionarias y armónicos</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7842,8 +7875,20 @@
       <c r="D120" t="n">
         <v>8</v>
       </c>
+      <c r="H120" t="n">
+        <v>7</v>
+      </c>
+      <c r="M120" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="n">
+        <v>1</v>
+      </c>
       <c r="AF120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -7852,14 +7897,14 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Órbitas y satélites</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7868,25 +7913,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
-      </c>
-      <c r="H121" t="n">
-        <v>7</v>
-      </c>
-      <c r="K121" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>1</v>
-      </c>
-      <c r="T121" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AF121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -7895,14 +7928,14 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Hidrodinámica: continuidad y Bernoulli</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7911,37 +7944,25 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
-      </c>
-      <c r="G122" t="n">
         <v>6</v>
       </c>
       <c r="H122" t="n">
         <v>7</v>
       </c>
-      <c r="I122" t="n">
-        <v>8</v>
-      </c>
-      <c r="J122" t="n">
-        <v>7</v>
-      </c>
-      <c r="P122" t="n">
-        <v>1</v>
+      <c r="K122" t="n">
+        <v>5</v>
       </c>
       <c r="Q122" t="n">
         <v>1</v>
       </c>
-      <c r="R122" t="n">
-        <v>1</v>
-      </c>
-      <c r="S122" t="n">
+      <c r="T122" t="n">
         <v>1</v>
       </c>
       <c r="AF122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
@@ -7950,14 +7971,14 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7966,19 +7987,37 @@
         </is>
       </c>
       <c r="C123" t="n">
+        <v>5</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5</v>
+      </c>
+      <c r="G123" t="n">
         <v>6</v>
       </c>
-      <c r="D123" t="n">
-        <v>6</v>
-      </c>
-      <c r="M123" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V123" t="n">
+      <c r="H123" t="n">
+        <v>7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>8</v>
+      </c>
+      <c r="J123" t="n">
+        <v>7</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1</v>
+      </c>
+      <c r="S123" t="n">
         <v>1</v>
       </c>
       <c r="AF123" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -7987,69 +8026,51 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Espejos planos e imágenes</t>
+          <t>Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>7</v>
-      </c>
-      <c r="H124" t="n">
         <v>3</v>
       </c>
-      <c r="J124" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L124" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M124" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>1</v>
-      </c>
-      <c r="S124" t="n">
-        <v>1</v>
-      </c>
-      <c r="U124" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="V124" t="n">
         <v>1</v>
       </c>
       <c r="AF124" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8058,39 +8079,33 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
-      </c>
-      <c r="F125" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D125" t="n">
+        <v>7</v>
       </c>
       <c r="H125" t="n">
-        <v>5</v>
-      </c>
-      <c r="I125" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J125" t="n">
         <v>4.5</v>
       </c>
+      <c r="L125" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O125" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
       </c>
-      <c r="R125" t="n">
-        <v>1</v>
-      </c>
       <c r="S125" t="n">
         <v>1</v>
       </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
       <c r="V125" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z125" t="n">
         <v>1</v>
       </c>
       <c r="AF125" t="n">
@@ -8098,19 +8113,19 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8119,38 +8134,26 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F126" t="n">
         <v>8</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
+        <v>5</v>
+      </c>
+      <c r="I126" t="n">
         <v>6</v>
       </c>
-      <c r="H126" t="n">
-        <v>7</v>
-      </c>
-      <c r="I126" t="n">
-        <v>7</v>
-      </c>
       <c r="J126" t="n">
-        <v>7</v>
-      </c>
-      <c r="K126" t="n">
-        <v>8</v>
-      </c>
-      <c r="L126" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M126" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="P126" t="n">
-        <v>1</v>
-      </c>
       <c r="Q126" t="n">
         <v>1</v>
       </c>
@@ -8160,17 +8163,14 @@
       <c r="S126" t="n">
         <v>1</v>
       </c>
-      <c r="T126" t="n">
-        <v>1</v>
-      </c>
-      <c r="U126" t="n">
-        <v>1</v>
-      </c>
       <c r="V126" t="n">
         <v>1</v>
       </c>
+      <c r="Z126" t="n">
+        <v>1</v>
+      </c>
       <c r="AF126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>

--- a/internacional/2_8/Contraste_fisica.xlsx
+++ b/internacional/2_8/Contraste_fisica.xlsx
@@ -673,7 +673,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Circuito eléctrico simple</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -682,40 +682,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
       <c r="M3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -735,14 +726,11 @@
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -751,14 +739,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Color y dispersión de la luz</t>
+          <t>Circuito eléctrico simple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -771,27 +759,36 @@
       </c>
       <c r="D4" t="n">
         <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -808,13 +805,13 @@
       <c r="S4" t="n">
         <v>1</v>
       </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AF4" t="n">
@@ -834,7 +831,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Conservación de la energía mecánica</t>
+          <t>Color y dispersión de la luz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -843,37 +840,58 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
       </c>
+      <c r="L5" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
       <c r="AF5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -889,7 +907,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Densidad</t>
+          <t>Conservación de la energía mecánica</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -898,64 +916,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7.5</v>
       </c>
       <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -971,7 +962,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Disipación de energía y eficiencia</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -984,37 +975,31 @@
       </c>
       <c r="D7" t="n">
         <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
@@ -1059,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>Disipación de energía y eficiencia</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1068,28 +1053,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H8" t="n">
         <v>7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
@@ -1097,6 +1088,9 @@
       <c r="N8" t="n">
         <v>1</v>
       </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
@@ -1112,11 +1106,17 @@
       <c r="T8" t="n">
         <v>1</v>
       </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" t="n">
         <v>1</v>
       </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Energía potencial gravitatoria y elástica</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,29 +1141,41 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
@@ -1177,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1193,7 +1205,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1206,18 +1218,12 @@
       </c>
       <c r="D10" t="n">
         <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
+      <c r="I10" t="n">
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
@@ -1225,31 +1231,19 @@
       <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
       <c r="M10" t="n">
         <v>4.5</v>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="n">
@@ -1272,7 +1266,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1286,29 +1280,32 @@
       <c r="D11" t="n">
         <v>2</v>
       </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
         <v>4.5</v>
       </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.5</v>
+      <c r="N11" t="n">
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1319,9 +1316,6 @@
       <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
@@ -1332,9 +1326,6 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
@@ -1354,7 +1345,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1363,23 +1354,35 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
         <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>4.5</v>
       </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
@@ -1389,11 +1392,26 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
       <c r="AF12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1402,14 +1420,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,8 +1441,8 @@
       <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="n">
-        <v>6</v>
+      <c r="F13" t="n">
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
@@ -1432,41 +1450,23 @@
       <c r="H13" t="n">
         <v>7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>5</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1491,53 +1491,71 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
         <v>6</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
         <v>6</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="G14" t="n">
-        <v>8.5</v>
-      </c>
       <c r="J14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
         <v>7</v>
       </c>
-      <c r="L14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1546,53 +1564,41 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J15" t="n">
         <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8</v>
       </c>
       <c r="L15" t="n">
         <v>7.5</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.5</v>
+      <c r="O15" t="n">
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
       <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
       <c r="AF15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -1604,7 +1610,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1613,53 +1619,35 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="n">
-        <v>5</v>
-      </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M16" t="n">
         <v>2.5</v>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
@@ -1673,53 +1661,68 @@
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1727,6 +1730,9 @@
       <c r="Q17" t="n">
         <v>1</v>
       </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
@@ -1740,11 +1746,11 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1756,7 +1762,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1765,40 +1771,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
         <v>7</v>
       </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -1806,12 +1800,12 @@
       <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
@@ -1819,11 +1813,11 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -1835,7 +1829,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Calor latente</t>
+          <t>Caída libre</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1844,13 +1838,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>8.5</v>
@@ -1858,8 +1849,8 @@
       <c r="H19" t="n">
         <v>7</v>
       </c>
-      <c r="O19" t="n">
-        <v>1</v>
+      <c r="J19" t="n">
+        <v>7</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -1867,8 +1858,11 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
       <c r="AF19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -1877,14 +1871,14 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1905,22 +1899,22 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
         <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>4.5</v>
       </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
       <c r="L20" t="n">
         <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -1934,12 +1928,12 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
@@ -1947,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1956,14 +1950,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Calor latente</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1972,40 +1966,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -2016,42 +1989,24 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2060,34 +2015,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="n">
         <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>4.5</v>
       </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -2101,12 +2056,12 @@
       <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
@@ -2114,11 +2069,11 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2130,7 +2085,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2139,28 +2094,40 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2171,21 +2138,30 @@
       <c r="Q23" t="n">
         <v>1</v>
       </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -2197,7 +2173,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2206,62 +2182,62 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
         <v>5</v>
       </c>
-      <c r="L24" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>6</v>
-      </c>
       <c r="AG24" t="inlineStr">
         <is>
           <t>alineado</t>
@@ -2269,14 +2245,14 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2285,40 +2261,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
-      <c r="K25" t="n">
-        <v>5</v>
-      </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2329,15 +2293,9 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
@@ -2345,11 +2303,11 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -2361,7 +2319,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2370,83 +2328,77 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
         <v>6</v>
       </c>
-      <c r="M26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>5</v>
-      </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2460,20 +2412,23 @@
       <c r="D27" t="n">
         <v>4</v>
       </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
         <v>7</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4.5</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
@@ -2482,7 +2437,10 @@
         <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2509,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2525,7 +2483,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2534,35 +2492,47 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
         <v>7</v>
       </c>
       <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
         <v>6</v>
       </c>
-      <c r="L28" t="n">
-        <v>4</v>
-      </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
@@ -2582,23 +2552,23 @@
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2607,31 +2577,34 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>4.5</v>
       </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -2646,6 +2619,9 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
@@ -2671,7 +2647,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2680,36 +2656,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
         <v>7</v>
       </c>
-      <c r="G30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4</v>
-      </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>7</v>
       </c>
       <c r="K30" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" t="n">
         <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" t="n">
+        <v>7</v>
+      </c>
+      <c r="O30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="n">
@@ -2724,15 +2697,18 @@
       <c r="T30" t="n">
         <v>1</v>
       </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -2744,7 +2720,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2753,40 +2729,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>4.5</v>
       </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2803,20 +2770,14 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2832,7 +2793,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>Energía cinética</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2841,30 +2802,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>6</v>
       </c>
       <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" t="n">
         <v>7</v>
       </c>
-      <c r="J32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K32" t="n">
         <v>4</v>
       </c>
       <c r="M32" t="n">
         <v>4.5</v>
       </c>
-      <c r="O32" t="n">
+      <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="P32" t="n">
@@ -2873,17 +2837,20 @@
       <c r="Q32" t="n">
         <v>1</v>
       </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="U32" t="n">
+      <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2892,14 +2859,14 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2926,10 +2893,10 @@
         <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K33" t="n">
         <v>2</v>
@@ -2987,7 +2954,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2996,10 +2963,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
@@ -3008,16 +2975,16 @@
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.5</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -3028,7 +2995,7 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="T34" t="n">
+      <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
@@ -3038,23 +3005,23 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fricción y resistencia del aire</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3063,10 +3030,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -3078,16 +3045,19 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
         <v>2.5</v>
@@ -3104,6 +3074,9 @@
       <c r="Q35" t="n">
         <v>1</v>
       </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
@@ -3116,24 +3089,27 @@
       <c r="V35" t="n">
         <v>1</v>
       </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
       <c r="AF35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3142,10 +3118,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -3154,20 +3130,17 @@
         <v>6</v>
       </c>
       <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" t="n">
         <v>7</v>
       </c>
-      <c r="I36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>7</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
@@ -3177,10 +3150,7 @@
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
@@ -3190,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -3199,14 +3169,14 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3215,10 +3185,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -3227,22 +3197,19 @@
         <v>8</v>
       </c>
       <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="n">
         <v>6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3</v>
       </c>
       <c r="M37" t="n">
         <v>2.5</v>
@@ -3259,9 +3226,6 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
@@ -3275,23 +3239,23 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3300,7 +3264,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
@@ -3308,14 +3275,20 @@
       <c r="G38" t="n">
         <v>6</v>
       </c>
+      <c r="H38" t="n">
+        <v>7</v>
+      </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
       </c>
+      <c r="L38" t="n">
+        <v>6</v>
+      </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -3323,21 +3296,27 @@
       <c r="P38" t="n">
         <v>1</v>
       </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -3349,7 +3328,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3358,22 +3337,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>2.5</v>
@@ -3390,6 +3372,9 @@
       <c r="N39" t="n">
         <v>1</v>
       </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
@@ -3412,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3428,7 +3413,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,13 +3422,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>6</v>
@@ -3451,16 +3436,19 @@
       <c r="H40" t="n">
         <v>7</v>
       </c>
+      <c r="I40" t="n">
+        <v>8</v>
+      </c>
       <c r="J40" t="n">
         <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
         <v>2.5</v>
       </c>
-      <c r="O40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="P40" t="n">
@@ -3469,6 +3457,9 @@
       <c r="Q40" t="n">
         <v>1</v>
       </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
@@ -3479,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3495,7 +3486,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gravedad: atracción hacia la Tierra</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3504,40 +3495,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
-      </c>
-      <c r="D41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
       </c>
-      <c r="K41" t="n">
-        <v>5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>6</v>
-      </c>
       <c r="M41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -3545,39 +3518,33 @@
       <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
       <c r="V41" t="n">
         <v>1</v>
       </c>
+      <c r="AF41" t="n">
+        <v>9</v>
+      </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>faltante</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3591,8 +3558,8 @@
       <c r="D42" t="n">
         <v>3</v>
       </c>
-      <c r="F42" t="n">
-        <v>8</v>
+      <c r="E42" t="n">
+        <v>3</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -3601,18 +3568,21 @@
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>2.5</v>
       </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
       <c r="L42" t="n">
         <v>3</v>
       </c>
       <c r="M42" t="n">
         <v>2.5</v>
       </c>
-      <c r="O42" t="n">
+      <c r="N42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
@@ -3625,6 +3595,9 @@
         <v>1</v>
       </c>
       <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
@@ -3650,7 +3623,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3659,10 +3632,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -3673,20 +3646,14 @@
       <c r="H43" t="n">
         <v>7</v>
       </c>
-      <c r="I43" t="n">
-        <v>7</v>
-      </c>
       <c r="J43" t="n">
         <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
-      </c>
-      <c r="L43" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3697,16 +3664,10 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="R43" t="n">
-        <v>1</v>
-      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
         <v>1</v>
       </c>
       <c r="V43" t="n">
@@ -3717,7 +3678,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3729,7 +3690,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Magnitudes escalares y vectoriales</t>
+          <t>Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3738,26 +3699,44 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" t="n">
-        <v>6</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
       </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
@@ -3767,15 +3746,18 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
-      <c r="AF44" t="n">
-        <v>5</v>
-      </c>
       <c r="AG44" t="inlineStr">
         <is>
           <t>adelantado</t>
@@ -3783,14 +3765,14 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3799,25 +3781,31 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
         <v>8</v>
       </c>
-      <c r="D45" t="n">
-        <v>8</v>
-      </c>
-      <c r="F45" t="n">
-        <v>5</v>
-      </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3828,17 +3816,20 @@
       <c r="Q45" t="n">
         <v>1</v>
       </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
       <c r="S45" t="n">
         <v>1</v>
       </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
-      <c r="Z45" t="n">
-        <v>1</v>
-      </c>
       <c r="AF45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3854,7 +3845,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3863,31 +3854,34 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
         <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7.5</v>
       </c>
       <c r="M46" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3907,11 +3901,14 @@
       <c r="T46" t="n">
         <v>1</v>
       </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
       <c r="V46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3927,7 +3924,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Magnitudes escalares y vectoriales</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3936,25 +3933,22 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" t="n">
         <v>3</v>
       </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" t="n">
-        <v>2</v>
-      </c>
       <c r="I47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6</v>
       </c>
       <c r="M47" t="n">
         <v>2.5</v>
@@ -3968,21 +3962,18 @@
       <c r="R47" t="n">
         <v>1</v>
       </c>
-      <c r="S47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
+      <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3994,7 +3985,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4003,25 +3994,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>6</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3</v>
-      </c>
-      <c r="L48" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -4029,24 +4023,21 @@
       <c r="Q48" t="n">
         <v>1</v>
       </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -4058,7 +4049,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4076,26 +4067,23 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.5</v>
       </c>
-      <c r="K49" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" t="n">
-        <v>4</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
@@ -4114,9 +4102,6 @@
       <c r="T49" t="n">
         <v>1</v>
       </c>
-      <c r="U49" t="n">
-        <v>1</v>
-      </c>
       <c r="V49" t="n">
         <v>1</v>
       </c>
@@ -4125,7 +4110,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -4137,7 +4122,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4146,44 +4131,38 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
-      <c r="F50" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>2.5</v>
       </c>
       <c r="L50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
         <v>2.5</v>
       </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
       <c r="S50" t="n">
         <v>1</v>
       </c>
@@ -4194,7 +4173,7 @@
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -4210,7 +4189,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4219,35 +4198,50 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
-      </c>
-      <c r="F51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
       <c r="AF51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -4259,7 +4253,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4268,19 +4262,37 @@
         </is>
       </c>
       <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
         <v>8</v>
       </c>
-      <c r="D52" t="n">
-        <v>8</v>
-      </c>
       <c r="G52" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4288,15 +4300,27 @@
       <c r="Q52" t="n">
         <v>1</v>
       </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
       <c r="S52" t="n">
         <v>1</v>
       </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
       <c r="AF52" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -4308,7 +4332,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4325,40 +4349,40 @@
       <c r="E53" t="n">
         <v>2</v>
       </c>
+      <c r="F53" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
       </c>
-      <c r="I53" t="n">
-        <v>2</v>
-      </c>
       <c r="J53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2</v>
+        <v>2.5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
       <c r="S53" t="n">
         <v>1</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>1</v>
       </c>
       <c r="V53" t="n">
@@ -4381,7 +4405,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4390,35 +4414,74 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="n">
         <v>8</v>
       </c>
       <c r="G54" t="n">
         <v>6</v>
       </c>
+      <c r="H54" t="n">
+        <v>7</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M54" t="n">
         <v>7</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
       <c r="V54" t="n">
         <v>1</v>
       </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
       <c r="AF54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -4430,7 +4493,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4447,19 +4510,19 @@
       <c r="F55" t="n">
         <v>8</v>
       </c>
-      <c r="I55" t="n">
+      <c r="G55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K55" t="n">
         <v>4</v>
       </c>
-      <c r="J55" t="n">
-        <v>7</v>
-      </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
@@ -4467,7 +4530,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
@@ -4479,7 +4542,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4488,59 +4551,35 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
-      </c>
-      <c r="F56" t="n">
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
-      </c>
-      <c r="I56" t="n">
+        <v>7</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
         <v>8</v>
       </c>
-      <c r="J56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>5</v>
-      </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
@@ -4552,7 +4591,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4566,31 +4605,28 @@
       <c r="D57" t="n">
         <v>2</v>
       </c>
-      <c r="F57" t="n">
-        <v>8</v>
+      <c r="E57" t="n">
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K57" t="n">
-        <v>5</v>
-      </c>
-      <c r="L57" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
       </c>
-      <c r="O57" t="n">
+      <c r="N57" t="n">
         <v>1</v>
       </c>
       <c r="P57" t="n">
@@ -4608,33 +4644,27 @@
       <c r="T57" t="n">
         <v>1</v>
       </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="Z57" t="n">
-        <v>1</v>
-      </c>
       <c r="AF57" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4643,24 +4673,24 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
         <v>7</v>
       </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
       <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
         <v>1</v>
       </c>
       <c r="V58" t="n">
@@ -4683,7 +4713,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4692,62 +4722,35 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F59" t="n">
         <v>8</v>
       </c>
-      <c r="G59" t="n">
-        <v>6</v>
-      </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="I59" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>4</v>
-      </c>
-      <c r="L59" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2.5</v>
+      <c r="J59" t="n">
+        <v>7</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
       <c r="R59" t="n">
         <v>1</v>
       </c>
-      <c r="T59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z59" t="n">
+      <c r="S59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -4759,7 +4762,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4768,25 +4771,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G60" t="n">
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
-      </c>
-      <c r="L60" t="n">
-        <v>7.5</v>
+        <v>8</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2</v>
       </c>
       <c r="M60" t="n">
         <v>2.5</v>
@@ -4803,14 +4809,17 @@
       <c r="R60" t="n">
         <v>1</v>
       </c>
-      <c r="U60" t="n">
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -4826,7 +4835,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4835,10 +4844,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>8</v>
@@ -4850,13 +4859,13 @@
         <v>5</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L61" t="n">
         <v>7.5</v>
@@ -4888,24 +4897,27 @@
       <c r="V61" t="n">
         <v>1</v>
       </c>
+      <c r="Z61" t="n">
+        <v>1</v>
+      </c>
       <c r="AF61" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4914,47 +4926,47 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I62" t="n">
         <v>8</v>
-      </c>
-      <c r="K62" t="n">
-        <v>7</v>
       </c>
       <c r="M62" t="n">
         <v>7</v>
       </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="T62" t="n">
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
         <v>1</v>
       </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4963,41 +4975,32 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M63" t="n">
         <v>2.5</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
@@ -5010,9 +5013,6 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
@@ -5022,8 +5022,11 @@
       <c r="V63" t="n">
         <v>1</v>
       </c>
+      <c r="Z63" t="n">
+        <v>1</v>
+      </c>
       <c r="AF63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5039,7 +5042,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5048,31 +5051,28 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
         <v>6</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>8</v>
-      </c>
-      <c r="J64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K64" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L64" t="n">
+        <v>7.5</v>
       </c>
       <c r="M64" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5086,33 +5086,30 @@
       <c r="R64" t="n">
         <v>1</v>
       </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" t="n">
+      <c r="U64" t="n">
         <v>1</v>
       </c>
       <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5121,40 +5118,34 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J65" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L65" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -5181,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5197,7 +5188,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5206,13 +5197,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
-      </c>
-      <c r="G66" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I66" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
       </c>
       <c r="K66" t="n">
         <v>7</v>
@@ -5220,19 +5211,13 @@
       <c r="M66" t="n">
         <v>7</v>
       </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="O66" t="n">
         <v>1</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
@@ -5240,7 +5225,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
@@ -5252,7 +5237,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5261,30 +5246,33 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K67" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" t="n">
         <v>4</v>
       </c>
       <c r="M67" t="n">
@@ -5311,11 +5299,14 @@
       <c r="T67" t="n">
         <v>1</v>
       </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
       <c r="V67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5331,7 +5322,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5340,31 +5331,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H68" t="n">
         <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J68" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -5388,23 +5379,23 @@
         <v>1</v>
       </c>
       <c r="AF68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5413,13 +5404,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
         <v>8</v>
@@ -5428,17 +5419,20 @@
         <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
         <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K69" t="n">
         <v>3</v>
       </c>
+      <c r="L69" t="n">
+        <v>4</v>
+      </c>
       <c r="M69" t="n">
         <v>2.5</v>
       </c>
@@ -5463,11 +5457,14 @@
       <c r="T69" t="n">
         <v>1</v>
       </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
       <c r="V69" t="n">
         <v>1</v>
       </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -5483,7 +5480,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5492,42 +5489,27 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
-      </c>
-      <c r="D70" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L70" t="n">
-        <v>4</v>
+        <v>8.5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>7</v>
       </c>
       <c r="M70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="n">
-        <v>1</v>
-      </c>
-      <c r="U70" t="n">
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="V70" t="n">
@@ -5537,23 +5519,23 @@
         <v>1</v>
       </c>
       <c r="AF70" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5567,22 +5549,46 @@
       <c r="D71" t="n">
         <v>5</v>
       </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
       <c r="G71" t="n">
         <v>6</v>
       </c>
       <c r="H71" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="I71" t="n">
+        <v>8</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.5</v>
       </c>
       <c r="K71" t="n">
         <v>4</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
         <v>1</v>
       </c>
       <c r="T71" t="n">
@@ -5596,7 +5602,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -5608,7 +5614,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5617,10 +5623,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" t="n">
         <v>5</v>
@@ -5632,7 +5638,7 @@
         <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J72" t="n">
         <v>2.5</v>
@@ -5641,7 +5647,7 @@
         <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5664,15 +5670,12 @@
       <c r="V72" t="n">
         <v>1</v>
       </c>
-      <c r="Z72" t="n">
-        <v>1</v>
-      </c>
       <c r="AF72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
@@ -5684,7 +5687,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5693,26 +5696,41 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="n">
+        <v>8</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2.5</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
         <v>2.5</v>
       </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
@@ -5722,6 +5740,9 @@
       <c r="R73" t="n">
         <v>1</v>
       </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
@@ -5729,11 +5750,11 @@
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -5745,7 +5766,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5754,31 +5775,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>6</v>
-      </c>
-      <c r="I74" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>7</v>
-      </c>
-      <c r="K74" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L74" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -5786,27 +5804,27 @@
       <c r="P74" t="n">
         <v>1</v>
       </c>
-      <c r="R74" t="n">
+      <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
       </c>
-      <c r="T74" t="n">
-        <v>1</v>
-      </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
       <c r="V74" t="n">
         <v>1</v>
       </c>
+      <c r="Z74" t="n">
+        <v>1</v>
+      </c>
       <c r="AF74" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
@@ -5818,7 +5836,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5827,44 +5845,29 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
-      </c>
-      <c r="F75" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" t="n">
-        <v>5</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M75" t="n">
         <v>7</v>
       </c>
-      <c r="O75" t="n">
-        <v>1</v>
-      </c>
       <c r="P75" t="n">
         <v>1</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
-      <c r="S75" t="n">
-        <v>1</v>
-      </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
@@ -5872,81 +5875,126 @@
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aceleración y fuerza centrípeta</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
         <v>5</v>
       </c>
-      <c r="D76" t="n">
-        <v>5</v>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
       </c>
       <c r="V76" t="n">
         <v>1</v>
       </c>
+      <c r="Z76" t="n">
+        <v>1</v>
+      </c>
       <c r="AF76" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Caída libre</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" t="n">
         <v>5</v>
       </c>
-      <c r="D77" t="n">
+      <c r="I77" t="n">
         <v>5</v>
       </c>
-      <c r="G77" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H77" t="n">
-        <v>7</v>
-      </c>
-      <c r="J77" t="n">
-        <v>7</v>
+      <c r="K77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.5</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -5954,11 +6002,17 @@
       <c r="Q77" t="n">
         <v>1</v>
       </c>
-      <c r="S77" t="n">
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="V77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -5974,19 +6028,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
@@ -5994,17 +6048,17 @@
       <c r="G78" t="n">
         <v>6</v>
       </c>
-      <c r="H78" t="n">
-        <v>7</v>
-      </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J78" t="n">
         <v>7</v>
       </c>
       <c r="K78" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="L78" t="n">
+        <v>7.5</v>
       </c>
       <c r="M78" t="n">
         <v>7</v>
@@ -6015,9 +6069,6 @@
       <c r="P78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
       <c r="R78" t="n">
         <v>1</v>
       </c>
@@ -6027,51 +6078,60 @@
       <c r="T78" t="n">
         <v>1</v>
       </c>
+      <c r="U78" t="n">
+        <v>1</v>
+      </c>
       <c r="V78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Desintegración radiactiva</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
-      </c>
-      <c r="D79" t="n">
-        <v>5</v>
-      </c>
-      <c r="E79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F79" t="n">
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N79" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>7</v>
       </c>
       <c r="O79" t="n">
         <v>1</v>
@@ -6079,57 +6139,60 @@
       <c r="P79" t="n">
         <v>1</v>
       </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
       <c r="AF79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fisión y fusión nuclear</t>
+          <t>Aceleración y fuerza centrípeta</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>8</v>
-      </c>
-      <c r="F80" t="n">
-        <v>8</v>
-      </c>
-      <c r="L80" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M80" t="n">
         <v>7</v>
       </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1</v>
-      </c>
       <c r="V80" t="n">
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6145,12 +6208,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Aplicaciones de las leyes de Newton</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6159,93 +6222,39 @@
       <c r="D81" t="n">
         <v>4</v>
       </c>
-      <c r="E81" t="n">
-        <v>6</v>
-      </c>
-      <c r="G81" t="n">
-        <v>6</v>
-      </c>
-      <c r="H81" t="n">
-        <v>7</v>
-      </c>
-      <c r="I81" t="n">
+      <c r="AF81" t="n">
         <v>8</v>
       </c>
-      <c r="J81" t="n">
-        <v>7</v>
-      </c>
-      <c r="K81" t="n">
-        <v>4</v>
-      </c>
-      <c r="M81" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>1</v>
-      </c>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
-      <c r="S81" t="n">
-        <v>1</v>
-      </c>
-      <c r="T81" t="n">
-        <v>1</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>5</v>
-      </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>8</v>
-      </c>
-      <c r="H82" t="n">
-        <v>7</v>
-      </c>
-      <c r="M82" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6261,22 +6270,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Campo eléctrico</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
-      </c>
-      <c r="E83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F83" t="n">
         <v>8</v>
@@ -6284,72 +6290,30 @@
       <c r="G83" t="n">
         <v>6</v>
       </c>
-      <c r="H83" t="n">
-        <v>7</v>
-      </c>
-      <c r="I83" t="n">
-        <v>3</v>
-      </c>
-      <c r="J83" t="n">
-        <v>7</v>
-      </c>
-      <c r="K83" t="n">
-        <v>4</v>
-      </c>
-      <c r="L83" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M83" t="n">
-        <v>7</v>
-      </c>
-      <c r="N83" t="n">
-        <v>1</v>
-      </c>
       <c r="O83" t="n">
         <v>1</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>1</v>
-      </c>
-      <c r="R83" t="n">
-        <v>1</v>
-      </c>
-      <c r="S83" t="n">
-        <v>1</v>
-      </c>
-      <c r="T83" t="n">
-        <v>1</v>
-      </c>
-      <c r="U83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>1</v>
-      </c>
       <c r="AF83" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Aplicaciones de las leyes de Newton</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6358,13 +6322,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6373,14 +6343,14 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Observación astronómica en distintas longitudes de onda</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6389,17 +6359,32 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
-      </c>
-      <c r="D85" t="n">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7</v>
+      </c>
+      <c r="M85" t="n">
+        <v>7</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -6411,7 +6396,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Campo eléctrico</t>
+          <t>Desintegración radiactiva</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6420,16 +6405,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E86" t="n">
+        <v>8</v>
       </c>
       <c r="F86" t="n">
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -6438,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -6454,7 +6445,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6463,15 +6454,12 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2</v>
-      </c>
-      <c r="K87" t="n">
-        <v>2</v>
-      </c>
-      <c r="T87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="n">
+        <v>8</v>
+      </c>
+      <c r="N87" t="n">
         <v>1</v>
       </c>
       <c r="AF87" t="n">
@@ -6479,7 +6467,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -6491,7 +6479,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6500,32 +6488,17 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
-      </c>
-      <c r="G88" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I88" t="n">
-        <v>7</v>
-      </c>
-      <c r="M88" t="n">
-        <v>7</v>
-      </c>
-      <c r="P88" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D88" t="n">
+        <v>8</v>
       </c>
       <c r="AF88" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
@@ -6537,7 +6510,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6546,32 +6519,47 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
-      </c>
-      <c r="E89" t="n">
-        <v>8</v>
-      </c>
-      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Defecto de masa y energía de enlace nuclear</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6580,17 +6568,20 @@
         </is>
       </c>
       <c r="C90" t="n">
+        <v>11</v>
+      </c>
+      <c r="F90" t="n">
         <v>8</v>
       </c>
-      <c r="D90" t="n">
-        <v>8</v>
+      <c r="O90" t="n">
+        <v>1</v>
       </c>
       <c r="AF90" t="n">
         <v>11</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
@@ -6602,7 +6593,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Espejos esféricos</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6611,47 +6602,56 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>6</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
+      </c>
+      <c r="L91" t="n">
+        <v>7.5</v>
       </c>
       <c r="M91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="T91" t="n">
+        <v>7</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
         <v>1</v>
       </c>
       <c r="V91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Defecto de masa y energía de enlace nuclear</t>
+          <t>Fisión y fusión nuclear</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6660,12 +6660,27 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
       </c>
+      <c r="L92" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M92" t="n">
+        <v>7</v>
+      </c>
       <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">
@@ -6673,7 +6688,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -6685,7 +6700,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Espejos esféricos</t>
+          <t>Fotón y efecto fotoeléctrico</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6696,34 +6711,16 @@
       <c r="C93" t="n">
         <v>10</v>
       </c>
-      <c r="F93" t="n">
+      <c r="E93" t="n">
         <v>8</v>
       </c>
-      <c r="H93" t="n">
-        <v>5</v>
-      </c>
-      <c r="J93" t="n">
-        <v>7</v>
-      </c>
-      <c r="L93" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M93" t="n">
-        <v>7</v>
-      </c>
-      <c r="O93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>1</v>
-      </c>
-      <c r="S93" t="n">
-        <v>1</v>
-      </c>
-      <c r="U93" t="n">
-        <v>1</v>
-      </c>
-      <c r="V93" t="n">
+      <c r="G93" t="n">
+        <v>6</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
         <v>1</v>
       </c>
       <c r="AF93" t="n">
@@ -6736,14 +6733,14 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fotón y efecto fotoeléctrico</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6752,26 +6749,29 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
-      </c>
-      <c r="E94" t="n">
         <v>8</v>
       </c>
-      <c r="G94" t="n">
-        <v>6</v>
-      </c>
-      <c r="N94" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" t="n">
+      <c r="D94" t="n">
+        <v>8</v>
+      </c>
+      <c r="H94" t="n">
+        <v>7</v>
+      </c>
+      <c r="M94" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="n">
         <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
